--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -466,11 +466,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -521,6 +523,16 @@
           <t>FCST/예산</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>소사업 매출(백만)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>FCST+소사업(백만)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -549,6 +561,12 @@
       <c r="H3" s="4" t="n">
         <v>85.2</v>
       </c>
+      <c r="I3" s="4" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>2736.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -577,6 +595,12 @@
       <c r="H4" s="4" t="n">
         <v>53.9</v>
       </c>
+      <c r="I4" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>385.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -605,6 +629,12 @@
       <c r="H5" s="4" t="n">
         <v>83.7</v>
       </c>
+      <c r="I5" s="4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>518.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -633,6 +663,12 @@
       <c r="H6" s="4" t="n">
         <v>86.40000000000001</v>
       </c>
+      <c r="I6" s="4" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>1167.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -661,6 +697,12 @@
       <c r="H7" s="4" t="n">
         <v>83.09999999999999</v>
       </c>
+      <c r="I7" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>713.8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -689,6 +731,12 @@
       <c r="H8" s="4" t="n">
         <v>84.59999999999999</v>
       </c>
+      <c r="I8" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>338.8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -717,6 +765,12 @@
       <c r="H9" s="4" t="n">
         <v>98</v>
       </c>
+      <c r="I9" s="4" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>4063.3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -745,6 +799,12 @@
       <c r="H10" s="4" t="n">
         <v>83.59999999999999</v>
       </c>
+      <c r="I10" s="4" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>1894.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -773,6 +833,12 @@
       <c r="H11" s="4" t="n">
         <v>86.40000000000001</v>
       </c>
+      <c r="I11" s="4" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>3407.8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -801,6 +867,12 @@
       <c r="H12" s="4" t="n">
         <v>92.5</v>
       </c>
+      <c r="I12" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>1681</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -829,6 +901,12 @@
       <c r="H13" s="4" t="n">
         <v>100.4</v>
       </c>
+      <c r="I13" s="4" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>2153.3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -857,6 +935,12 @@
       <c r="H14" s="4" t="n">
         <v>73.59999999999999</v>
       </c>
+      <c r="I14" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>525</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -885,6 +969,12 @@
       <c r="H15" s="4" t="n">
         <v>79.09999999999999</v>
       </c>
+      <c r="I15" s="4" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>1241.5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -913,6 +1003,12 @@
       <c r="H16" s="4" t="n">
         <v>91.8</v>
       </c>
+      <c r="I16" s="4" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>1508.3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -941,6 +1037,12 @@
       <c r="H17" s="4" t="n">
         <v>97.09999999999999</v>
       </c>
+      <c r="I17" s="4" t="n">
+        <v>144.3</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>1368.3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -969,6 +1071,12 @@
       <c r="H18" s="4" t="n">
         <v>82.5</v>
       </c>
+      <c r="I18" s="4" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>1869.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -997,6 +1105,12 @@
       <c r="H19" s="4" t="n">
         <v>83</v>
       </c>
+      <c r="I19" s="4" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>1866.1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1025,6 +1139,12 @@
       <c r="H20" s="4" t="n">
         <v>95.8</v>
       </c>
+      <c r="I20" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>1456.6</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1053,6 +1173,12 @@
       <c r="H21" s="4" t="n">
         <v>96.59999999999999</v>
       </c>
+      <c r="I21" s="4" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>1208.4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1081,6 +1207,12 @@
       <c r="H22" s="4" t="n">
         <v>84.59999999999999</v>
       </c>
+      <c r="I22" s="4" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>2009.4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1109,6 +1241,12 @@
       <c r="H23" s="4" t="n">
         <v>108.1</v>
       </c>
+      <c r="I23" s="4" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>609.9</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1137,6 +1275,12 @@
       <c r="H24" s="4" t="n">
         <v>83.2</v>
       </c>
+      <c r="I24" s="4" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>2942.7</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1165,117 +1309,139 @@
       <c r="H25" s="4" t="n">
         <v>105.4</v>
       </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>[비발디]</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>37454</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>183</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>6855</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>30842</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>185</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>5696</v>
-      </c>
-      <c r="H27" s="7" t="n">
-        <v>82.3</v>
-      </c>
-    </row>
+      <c r="I25" s="4" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>473.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>합계(사업장)</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>34800</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>1339.5</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>36139.5</v>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>[한국중부]</t>
+          <t>[비발디]</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>76820</v>
+        <v>37454</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>14147</v>
+        <v>6855</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>68835</v>
+        <v>30842</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>12323</v>
+        <v>5696</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>89.59999999999999</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>[아시아퍼시픽]</t>
+          <t>[한국중부]</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>32190</v>
+        <v>76820</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>5030</v>
+        <v>14147</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>29159</v>
+        <v>68835</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>4511</v>
+        <v>12323</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>90.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>[아시아퍼시픽]</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>32190</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>156</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>5030</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>29159</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>4511</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>90.59999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>[한국남부]</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B31" s="6" t="n">
         <v>67805</v>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C31" s="6" t="n">
         <v>205</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D31" s="6" t="n">
         <v>13897</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E31" s="6" t="n">
         <v>60323</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F31" s="6" t="n">
         <v>203</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G31" s="6" t="n">
         <v>12273</v>
       </c>
-      <c r="H30" s="7" t="n">
+      <c r="H31" s="7" t="n">
         <v>89</v>
       </c>
     </row>
@@ -1290,11 +1456,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1355,6 +1523,16 @@
           <t>차이 RN</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>소사업 비율(천원/실)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>소사업 매출(백만)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1391,6 +1569,12 @@
       <c r="J3" s="3" t="n">
         <v>300</v>
       </c>
+      <c r="K3" s="4" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>124.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1427,6 +1611,12 @@
       <c r="J4" s="3" t="n">
         <v>200</v>
       </c>
+      <c r="K4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1463,6 +1653,12 @@
       <c r="J5" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="K5" s="4" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1499,6 +1695,12 @@
       <c r="J6" s="3" t="n">
         <v>-500</v>
       </c>
+      <c r="K6" s="4" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>9.800000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1535,6 +1737,12 @@
       <c r="J7" s="3" t="n">
         <v>-260</v>
       </c>
+      <c r="K7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1571,6 +1779,12 @@
       <c r="J8" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="K8" s="4" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1607,6 +1821,12 @@
       <c r="J9" s="3" t="n">
         <v>-150</v>
       </c>
+      <c r="K9" s="4" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>7.4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1643,6 +1863,12 @@
       <c r="J10" s="3" t="n">
         <v>-50</v>
       </c>
+      <c r="K10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1679,6 +1905,12 @@
       <c r="J11" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K11" s="4" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1715,6 +1947,12 @@
       <c r="J12" s="3" t="n">
         <v>-200</v>
       </c>
+      <c r="K12" s="4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1751,6 +1989,12 @@
       <c r="J13" s="3" t="n">
         <v>150</v>
       </c>
+      <c r="K13" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1787,6 +2031,12 @@
       <c r="J14" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K14" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1823,6 +2073,12 @@
       <c r="J15" s="3" t="n">
         <v>-350</v>
       </c>
+      <c r="K15" s="4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1859,6 +2115,12 @@
       <c r="J16" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K16" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1895,6 +2157,12 @@
       <c r="J17" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K17" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1931,6 +2199,12 @@
       <c r="J18" s="3" t="n">
         <v>-60</v>
       </c>
+      <c r="K18" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1967,6 +2241,12 @@
       <c r="J19" s="3" t="n">
         <v>40</v>
       </c>
+      <c r="K19" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2003,6 +2283,12 @@
       <c r="J20" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K20" s="4" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2039,6 +2325,12 @@
       <c r="J21" s="3" t="n">
         <v>770</v>
       </c>
+      <c r="K21" s="4" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>71.3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2075,6 +2367,12 @@
       <c r="J22" s="3" t="n">
         <v>410</v>
       </c>
+      <c r="K22" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>17.6</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2111,6 +2409,12 @@
       <c r="J23" s="3" t="n">
         <v>-34</v>
       </c>
+      <c r="K23" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2147,6 +2451,12 @@
       <c r="J24" s="3" t="n">
         <v>-350</v>
       </c>
+      <c r="K24" s="4" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>43.9</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2183,6 +2493,12 @@
       <c r="J25" s="3" t="n">
         <v>150</v>
       </c>
+      <c r="K25" s="4" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>12.8</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2219,6 +2535,12 @@
       <c r="J26" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2255,6 +2577,12 @@
       <c r="J27" s="3" t="n">
         <v>-200</v>
       </c>
+      <c r="K27" s="4" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>57.3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2291,6 +2619,12 @@
       <c r="J28" s="3" t="n">
         <v>-500</v>
       </c>
+      <c r="K28" s="4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>21.2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2327,6 +2661,12 @@
       <c r="J29" s="3" t="n">
         <v>13</v>
       </c>
+      <c r="K29" s="4" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2363,6 +2703,12 @@
       <c r="J30" s="3" t="n">
         <v>-950</v>
       </c>
+      <c r="K30" s="4" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>81.7</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2399,6 +2745,12 @@
       <c r="J31" s="3" t="n">
         <v>-100</v>
       </c>
+      <c r="K31" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>18.6</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2435,6 +2787,12 @@
       <c r="J32" s="3" t="n">
         <v>-71</v>
       </c>
+      <c r="K32" s="4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2471,6 +2829,12 @@
       <c r="J33" s="3" t="n">
         <v>175</v>
       </c>
+      <c r="K33" s="4" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>32.1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2507,6 +2871,12 @@
       <c r="J34" s="3" t="n">
         <v>70</v>
       </c>
+      <c r="K34" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2543,6 +2913,12 @@
       <c r="J35" s="3" t="n">
         <v>12</v>
       </c>
+      <c r="K35" s="4" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2579,6 +2955,12 @@
       <c r="J36" s="3" t="n">
         <v>-540</v>
       </c>
+      <c r="K36" s="4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2615,6 +2997,12 @@
       <c r="J37" s="3" t="n">
         <v>250</v>
       </c>
+      <c r="K37" s="4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2651,6 +3039,12 @@
       <c r="J38" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="K38" s="4" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2687,6 +3081,12 @@
       <c r="J39" s="3" t="n">
         <v>-120</v>
       </c>
+      <c r="K39" s="4" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>80.3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2723,6 +3123,12 @@
       <c r="J40" s="3" t="n">
         <v>-120</v>
       </c>
+      <c r="K40" s="4" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>18.2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2759,6 +3165,12 @@
       <c r="J41" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K41" s="4" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2795,6 +3207,12 @@
       <c r="J42" s="3" t="n">
         <v>-50</v>
       </c>
+      <c r="K42" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>107.3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2831,6 +3249,12 @@
       <c r="J43" s="3" t="n">
         <v>250</v>
       </c>
+      <c r="K43" s="4" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>23.1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2867,6 +3291,12 @@
       <c r="J44" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K44" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2903,6 +3333,12 @@
       <c r="J45" s="3" t="n">
         <v>-215</v>
       </c>
+      <c r="K45" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>59.7</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2939,6 +3375,12 @@
       <c r="J46" s="3" t="n">
         <v>150</v>
       </c>
+      <c r="K46" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2975,6 +3417,12 @@
       <c r="J47" s="3" t="n">
         <v>-37</v>
       </c>
+      <c r="K47" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3011,6 +3459,12 @@
       <c r="J48" s="3" t="n">
         <v>-350</v>
       </c>
+      <c r="K48" s="4" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>76.59999999999999</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3047,6 +3501,12 @@
       <c r="J49" s="3" t="n">
         <v>-200</v>
       </c>
+      <c r="K49" s="4" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>19.4</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3083,6 +3543,12 @@
       <c r="J50" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="K50" s="4" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3119,6 +3585,12 @@
       <c r="J51" s="3" t="n">
         <v>-350</v>
       </c>
+      <c r="K51" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>23.2</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3155,6 +3627,12 @@
       <c r="J52" s="3" t="n">
         <v>20</v>
       </c>
+      <c r="K52" s="4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>13.9</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3191,6 +3669,12 @@
       <c r="J53" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="K53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3227,6 +3711,12 @@
       <c r="J54" s="3" t="n">
         <v>20</v>
       </c>
+      <c r="K54" s="4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3263,6 +3753,12 @@
       <c r="J55" s="3" t="n">
         <v>570</v>
       </c>
+      <c r="K55" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>14.9</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3299,6 +3795,12 @@
       <c r="J56" s="3" t="n">
         <v>-6</v>
       </c>
+      <c r="K56" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3335,6 +3837,12 @@
       <c r="J57" s="3" t="n">
         <v>-120</v>
       </c>
+      <c r="K57" s="4" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3371,6 +3879,12 @@
       <c r="J58" s="3" t="n">
         <v>160</v>
       </c>
+      <c r="K58" s="4" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>17.7</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3407,6 +3921,12 @@
       <c r="J59" s="3" t="n">
         <v>20</v>
       </c>
+      <c r="K59" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3443,6 +3963,12 @@
       <c r="J60" s="3" t="n">
         <v>-250</v>
       </c>
+      <c r="K60" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3479,6 +4005,12 @@
       <c r="J61" s="3" t="n">
         <v>-600</v>
       </c>
+      <c r="K61" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3515,6 +4047,12 @@
       <c r="J62" s="3" t="n">
         <v>-1050</v>
       </c>
+      <c r="K62" s="4" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>92.3</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3551,6 +4089,12 @@
       <c r="J63" s="3" t="n">
         <v>-200</v>
       </c>
+      <c r="K63" s="4" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>20.4</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3587,6 +4131,12 @@
       <c r="J64" s="3" t="n">
         <v>200</v>
       </c>
+      <c r="K64" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3623,6 +4173,12 @@
       <c r="J65" s="3" t="n">
         <v>441</v>
       </c>
+      <c r="K65" s="4" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3659,6 +4215,12 @@
       <c r="J66" s="3" t="n">
         <v>-150</v>
       </c>
+      <c r="K66" s="4" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="L66" s="4" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3695,6 +4257,12 @@
       <c r="J67" s="3" t="n">
         <v>840</v>
       </c>
+      <c r="K67" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L67" s="4" t="n">
+        <v>7.7</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3731,6 +4299,12 @@
       <c r="J68" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="K68" s="4" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3767,6 +4341,12 @@
       <c r="J69" s="3" t="n">
         <v>225</v>
       </c>
+      <c r="K69" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>10.1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3803,6 +4383,12 @@
       <c r="J70" s="3" t="n">
         <v>35</v>
       </c>
+      <c r="K70" s="4" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3837,6 +4423,12 @@
         <v>0</v>
       </c>
       <c r="J71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3851,7 +4443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3918,6 +4510,42 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>소사업 기준</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>전년 2025-06 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>소사업 정의</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GS 객실 외 7유형(식음+부대+아쿠아+스포츠+골프+유통+기타), VAT제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>소사업 소스</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>d08238c0-_______________5______________________260602_12.xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -4542,7 +4542,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>d08238c0-_______________5______________________260602_12.xlsx</t>
+          <t>소사업_전년비율_소스_2025.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09T10:19:21.177798Z</t>
+          <t>2026-06-10T15:58:33.930112Z</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>2992</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>17728</v>
+        <v>18016</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2607</v>
+        <v>2625</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>85.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>129.3</v>
+        <v>135.9</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2736.3</v>
+        <v>2760.9</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>705</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1750</v>
+        <v>1710</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>53.9</v>
+        <v>52.7</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>385.5</v>
+        <v>371.1</v>
       </c>
     </row>
     <row r="5">
@@ -621,19 +621,19 @@
         <v>1713</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>83.7</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>518.2</v>
+        <v>517.1</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>1303</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4346</v>
+        <v>4274</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>266</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1158</v>
+        <v>1136</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>86.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1167.7</v>
+        <v>1145.7</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>860</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2406</v>
+        <v>2414</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>83.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>713.8</v>
+        <v>715.6</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>401</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2899</v>
+        <v>2895</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>84.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>338.8</v>
+        <v>342.9</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>4116</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>19463</v>
+        <v>19470</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>3974</v>
+        <v>3922</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>98</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>89.3</v>
+        <v>87.7</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4063.3</v>
+        <v>4009.7</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>2267</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>10401</v>
+        <v>10454</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1838</v>
+        <v>1842</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>83.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>56.7</v>
+        <v>60.7</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1894.7</v>
+        <v>1902.7</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>3993</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>17426</v>
+        <v>18063</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>191</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3328</v>
+        <v>3443</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>86.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>79.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3407.8</v>
+        <v>3527.9</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>1836</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>11985</v>
+        <v>12015</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1580</v>
+        <v>1567</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>92.5</v>
+        <v>92.7</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>101</v>
+        <v>100.2</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1681</v>
+        <v>1667.2</v>
       </c>
     </row>
     <row r="13">
@@ -893,19 +893,19 @@
         <v>9540</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2117</v>
+        <v>2126</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>100.4</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2153.3</v>
+        <v>2162.6</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>712</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>3465</v>
+        <v>3500</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>148</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>73.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>11</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>1425</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7315</v>
+        <v>7334</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>156</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>79.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>98.5</v>
+        <v>100.8</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1241.5</v>
+        <v>1244.8</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>1464</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9110</v>
+        <v>9427</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1378</v>
+        <v>1409</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>91.8</v>
+        <v>95</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>130.3</v>
+        <v>139.6</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1508.3</v>
+        <v>1548.6</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1222</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4886</v>
+        <v>4882</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>144.3</v>
+        <v>140.4</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1368.3</v>
+        <v>1367.4</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>2063</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>8546</v>
+        <v>8832</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1773</v>
+        <v>1817</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>82.5</v>
+        <v>85.3</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>96.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1869.1</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>2347</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>9895</v>
+        <v>10180</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1829</v>
+        <v>1894</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>83</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>37.1</v>
+        <v>38.7</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1866.1</v>
+        <v>1932.7</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>1502</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9318</v>
+        <v>9851</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>154</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1433</v>
+        <v>1516</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>95.8</v>
+        <v>101.2</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>23.6</v>
+        <v>25.9</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1456.6</v>
+        <v>1541.9</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1359</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>6761</v>
+        <v>7111</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1172</v>
+        <v>1224</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>96.59999999999999</v>
+        <v>101.6</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>36.4</v>
+        <v>39.8</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1208.4</v>
+        <v>1263.8</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2168</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>13080</v>
+        <v>12690</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>146</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1905</v>
+        <v>1853</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>84.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>104.4</v>
+        <v>85.8</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2009.4</v>
+        <v>1938.8</v>
       </c>
     </row>
     <row r="23">
@@ -1230,22 +1230,22 @@
         <v>482</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5524</v>
+        <v>5618</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>108.1</v>
+        <v>109.9</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>75.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>609.9</v>
+        <v>627.4</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>3383</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>9357</v>
+        <v>9518</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>310</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2903</v>
+        <v>2954</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>83.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>39.7</v>
+        <v>41.9</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2942.7</v>
+        <v>2995.9</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>509</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2245</v>
+        <v>2330</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>205</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>105.4</v>
+        <v>109.4</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14.8</v>
+        <v>15.9</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>473.8</v>
+        <v>494.9</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>34800</v>
+        <v>35169</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1339.5</v>
+        <v>1355.6</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>36139.5</v>
+        <v>36524.6</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>6855</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>30842</v>
+        <v>31022</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>5696</v>
+        <v>5685</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>82.3</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>14147</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>68835</v>
+        <v>69666</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>12323</v>
+        <v>12397</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>89.59999999999999</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5030</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>29159</v>
+        <v>29652</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>155</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>4511</v>
+        <v>4593</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>90.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>13897</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>60323</v>
+        <v>61497</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>203</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>12273</v>
+        <v>12496</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>89</v>
+        <v>90.7</v>
       </c>
     </row>
   </sheetData>
@@ -1555,25 +1555,25 @@
         <v>1018</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>7600</v>
+        <v>8000</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1148</v>
+        <v>1192</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>104.1</v>
+        <v>109.6</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>16.3</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>124.2</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="4">
@@ -1597,25 +1597,25 @@
         <v>182</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1300</v>
+        <v>1230</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>163</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>118.2</v>
+        <v>111.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -1639,25 +1639,25 @@
         <v>4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>5</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>40.1</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -1681,25 +1681,25 @@
         <v>237</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>600</v>
+        <v>520</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>54.5</v>
+        <v>47.3</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-500</v>
+        <v>-580</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>16.3</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7">
@@ -1726,7 +1726,7 @@
         <v>240</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>57</v>
@@ -1810,7 +1810,7 @@
         <v>450</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>135</v>
@@ -1849,19 +1849,19 @@
         <v>130</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>88.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-50</v>
+        <v>-70</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>2</v>
@@ -1936,10 +1936,10 @@
         <v>1100</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>84.59999999999999</v>
@@ -1975,19 +1975,19 @@
         <v>174</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>279</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>125</v>
+        <v>116.7</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0.2</v>
@@ -2059,25 +2059,25 @@
         <v>271</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>61.1</v>
+        <v>58.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-350</v>
+        <v>-370</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>8.6</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="16">
@@ -2104,10 +2104,10 @@
         <v>300</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>100</v>
@@ -2185,25 +2185,25 @@
         <v>57</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19">
@@ -2227,19 +2227,19 @@
         <v>35</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>1.1</v>
@@ -2311,25 +2311,25 @@
         <v>827</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>988</v>
+        <v>940</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>123.8</v>
+        <v>120.7</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>770</v>
+        <v>670</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>17.8</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>71.3</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>637</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3050</v>
+        <v>3100</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>115.5</v>
+        <v>117.4</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>5.8</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="23">
@@ -2395,25 +2395,25 @@
         <v>4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-34</v>
+        <v>-36</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>29</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24">
@@ -2437,25 +2437,25 @@
         <v>431</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1750</v>
+        <v>1900</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>83.3</v>
+        <v>90.5</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-350</v>
+        <v>-200</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>25.1</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>43.9</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="25">
@@ -2479,25 +2479,25 @@
         <v>204</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1250</v>
+        <v>1280</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>113.6</v>
+        <v>116.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="26">
@@ -2563,25 +2563,25 @@
         <v>828</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>778</v>
+        <v>839</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>94.7</v>
+        <v>102.6</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>15.9</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>57.3</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="28">
@@ -2605,25 +2605,25 @@
         <v>667</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2800</v>
+        <v>2850</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>197</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>84.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>-500</v>
+        <v>-450</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>7.6</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>21.2</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="29">
@@ -2692,10 +2692,10 @@
         <v>2600</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="I30" s="4" t="n">
         <v>73.2</v>
@@ -2731,25 +2731,25 @@
         <v>248</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1550</v>
+        <v>1480</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>93.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-100</v>
+        <v>-170</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>12</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>18.6</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="32">
@@ -2773,25 +2773,25 @@
         <v>19</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>58</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>71.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-71</v>
+        <v>-61</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>3.6</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="33">
@@ -2815,25 +2815,25 @@
         <v>396</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1670</v>
+        <v>1680</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>274</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>111.7</v>
+        <v>112.4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>241</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>253</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>107.5</v>
+        <v>112.9</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>166</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>530</v>
+        <v>610</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>49.5</v>
+        <v>57</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-540</v>
+        <v>-460</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="37">
@@ -2983,25 +2983,25 @@
         <v>60</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>650</v>
+        <v>580</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>165</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>162.5</v>
+        <v>145</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -3025,7 +3025,7 @@
         <v>3</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>132</v>
@@ -3034,16 +3034,16 @@
         <v>2</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>120</v>
+        <v>106.7</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>36.9</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="39">
@@ -3109,25 +3109,25 @@
         <v>148</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>780</v>
+        <v>880</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>86.7</v>
+        <v>97.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-120</v>
+        <v>-20</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>18.2</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="41">
@@ -3193,25 +3193,25 @@
         <v>248</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1450</v>
+        <v>1580</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>96.7</v>
+        <v>105.3</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>-50</v>
+        <v>80</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>74</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>107.3</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="43">
@@ -3235,25 +3235,25 @@
         <v>180</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1450</v>
+        <v>1430</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>120.8</v>
+        <v>119.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>15.9</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="44">
@@ -3319,25 +3319,25 @@
         <v>164</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>64.2</v>
+        <v>60</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-215</v>
+        <v>-240</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>155</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>59.7</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="46">
@@ -3403,19 +3403,19 @@
         <v>24</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>14</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>75.3</v>
+        <v>74.7</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>5</v>
@@ -3445,25 +3445,25 @@
         <v>366</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>79.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-350</v>
+        <v>-300</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>56.8</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>76.59999999999999</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="49">
@@ -3490,10 +3490,10 @@
         <v>1400</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="I49" s="4" t="n">
         <v>87.5</v>
@@ -3571,25 +3571,25 @@
         <v>574</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2450</v>
+        <v>2620</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>480</v>
+        <v>517</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>87.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-350</v>
+        <v>-180</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>9.5</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>23.2</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="52">
@@ -3616,10 +3616,10 @@
         <v>2020</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I52" s="4" t="n">
         <v>101</v>
@@ -3697,25 +3697,25 @@
         <v>140</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>920</v>
+        <v>960</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>179</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>102.2</v>
+        <v>106.7</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="55">
@@ -3739,25 +3739,25 @@
         <v>152</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1570</v>
+        <v>1770</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>570</v>
+        <v>770</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>9.5</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>14.9</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="56">
@@ -3823,25 +3823,25 @@
         <v>141</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>79.3</v>
+        <v>86.2</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-120</v>
+        <v>-80</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>40.3</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>18.5</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="58">
@@ -3865,25 +3865,25 @@
         <v>160</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>880</v>
+        <v>970</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>122.2</v>
+        <v>134.7</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>20.1</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>17.7</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="59">
@@ -3949,25 +3949,25 @@
         <v>211</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>850</v>
+        <v>700</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>77.3</v>
+        <v>63.6</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-250</v>
+        <v>-400</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>9.5</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="61">
@@ -3991,25 +3991,25 @@
         <v>724</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>3200</v>
+        <v>3050</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>191</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>612</v>
+        <v>583</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>84.2</v>
+        <v>80.3</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-600</v>
+        <v>-750</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>1.3</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="62">
@@ -4033,25 +4033,25 @@
         <v>315</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2450</v>
+        <v>2000</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>221</v>
+        <v>177</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>70</v>
+        <v>57.1</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>-1050</v>
+        <v>-1500</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>37.7</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>92.3</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="63">
@@ -4075,25 +4075,25 @@
         <v>75</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-200</v>
+        <v>-180</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>40.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>20.4</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="64">
@@ -4117,25 +4117,25 @@
         <v>100</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>15</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="65">
@@ -4159,25 +4159,25 @@
         <v>49</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1241</v>
+        <v>1212</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>62</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>155.1</v>
+        <v>151.5</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>441</v>
+        <v>412</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>37.5</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="66">
@@ -4201,25 +4201,25 @@
         <v>640</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1700</v>
+        <v>1820</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>630</v>
+        <v>668</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>91.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>-150</v>
+        <v>-30</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>18.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>32</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="67">
@@ -4246,10 +4246,10 @@
         <v>1750</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="I67" s="4" t="n">
         <v>192.3</v>
@@ -4327,25 +4327,25 @@
         <v>135</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>750</v>
+        <v>835</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>142.9</v>
+        <v>159</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>225</v>
+        <v>310</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>10.1</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>110</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="G70" s="3" t="n">
         <v>181</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>108.2</v>
+        <v>105.9</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.06.08.pdf</t>
+          <t>Revenue Meeting_2026.06.16.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-10T15:58:33.930112Z</t>
+          <t>2026-06-17T08:54:12.277000Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.06.08</t>
+          <t>2026.06.16</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-17T08:54:12.277000Z</t>
+          <t>2026-06-17T09:17:30.288557Z</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -478,7 +478,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST - 2026-06</t>
+          <t>RM FCST - 2026-07</t>
         </is>
       </c>
     </row>
@@ -541,31 +541,31 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>20810</v>
+        <v>28100</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2992</v>
+        <v>5343</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>18016</v>
+        <v>28830</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>146</v>
+        <v>191</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2625</v>
+        <v>5504</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>102.6</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>135.9</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2760.9</v>
+        <v>5591.1</v>
       </c>
     </row>
     <row r="4">
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3245</v>
+        <v>5525</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>705</v>
+        <v>1421</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1710</v>
+        <v>5295</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>212</v>
+        <v>258</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>362</v>
+        <v>1364</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>52.7</v>
+        <v>95.8</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>9.1</v>
+        <v>19.3</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>371.1</v>
+        <v>1383.3</v>
       </c>
     </row>
     <row r="5">
@@ -609,31 +609,31 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2047</v>
+        <v>3037</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>290</v>
+        <v>372</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>594</v>
+        <v>1130</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1713</v>
+        <v>3104</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>297</v>
+        <v>372</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>509</v>
+        <v>1155</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>83.7</v>
+        <v>102.2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>517.1</v>
+        <v>1164.1</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5030</v>
+        <v>7650</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>259</v>
+        <v>314</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1303</v>
+        <v>2399</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4274</v>
+        <v>7572</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>266</v>
+        <v>318</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1136</v>
+        <v>2410</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1145.7</v>
+        <v>2419.8</v>
       </c>
     </row>
     <row r="7">
@@ -677,31 +677,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2897</v>
+        <v>3492</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>297</v>
+        <v>355</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>860</v>
+        <v>1241</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2414</v>
+        <v>3493</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>294</v>
+        <v>356</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>711</v>
+        <v>1244</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>715.6</v>
+        <v>1247.8</v>
       </c>
     </row>
     <row r="8">
@@ -711,31 +711,31 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3425</v>
+        <v>3605</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>401</v>
+        <v>517</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2895</v>
+        <v>3448</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>341</v>
+        <v>520</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>84.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>342.9</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9">
@@ -745,31 +745,31 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>19860</v>
+        <v>29075</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4116</v>
+        <v>6796</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>19470</v>
+        <v>28134</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>3922</v>
+        <v>6443</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>98</v>
+        <v>96.8</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>87.7</v>
+        <v>79.7</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4009.7</v>
+        <v>6522.7</v>
       </c>
     </row>
     <row r="10">
@@ -779,31 +779,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>12445</v>
+        <v>14790</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2267</v>
+        <v>3214</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>10454</v>
+        <v>14496</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1842</v>
+        <v>3152</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>60.7</v>
+        <v>60.5</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1902.7</v>
+        <v>3212.5</v>
       </c>
     </row>
     <row r="11">
@@ -813,31 +813,31 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>20175</v>
+        <v>21300</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3993</v>
+        <v>5037</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>18063</v>
+        <v>21306</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>191</v>
+        <v>237</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3443</v>
+        <v>5049</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>89.5</v>
+        <v>100</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>118.7</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3527.9</v>
+        <v>5167.7</v>
       </c>
     </row>
     <row r="12">
@@ -847,31 +847,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>12960</v>
+        <v>18080</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1836</v>
+        <v>2770</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>12015</v>
+        <v>18490</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1567</v>
+        <v>2582</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>92.7</v>
+        <v>102.3</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>100.2</v>
+        <v>134.3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1667.2</v>
+        <v>2716.3</v>
       </c>
     </row>
     <row r="13">
@@ -881,31 +881,31 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>9505</v>
+        <v>10675</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2223</v>
+        <v>2705</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>9540</v>
+        <v>10335</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2126</v>
+        <v>2643</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>100.4</v>
+        <v>96.8</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>36.6</v>
+        <v>35.1</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2162.6</v>
+        <v>2678.1</v>
       </c>
     </row>
     <row r="14">
@@ -915,31 +915,31 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>4710</v>
+        <v>5290</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>712</v>
+        <v>928</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>3500</v>
+        <v>4330</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>518</v>
+        <v>792</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>74.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>529</v>
+        <v>803.5</v>
       </c>
     </row>
     <row r="15">
@@ -949,31 +949,31 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9250</v>
+        <v>11470</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1425</v>
+        <v>2188</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7334</v>
+        <v>10748</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1144</v>
+        <v>2053</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>79.3</v>
+        <v>93.7</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>100.8</v>
+        <v>152.7</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1244.8</v>
+        <v>2205.7</v>
       </c>
     </row>
     <row r="16">
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9920</v>
+        <v>12080</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1464</v>
+        <v>2244</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9427</v>
+        <v>11510</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1409</v>
+        <v>2158</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>139.6</v>
+        <v>167.3</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1548.6</v>
+        <v>2325.3</v>
       </c>
     </row>
     <row r="17">
@@ -1017,31 +1017,31 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5030</v>
+        <v>5400</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1222</v>
+        <v>1570</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4882</v>
+        <v>5200</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>251</v>
+        <v>291</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1227</v>
+        <v>1514</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>140.4</v>
+        <v>146.1</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1367.4</v>
+        <v>1660.1</v>
       </c>
     </row>
     <row r="18">
@@ -1051,31 +1051,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>10360</v>
+        <v>12610</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>199</v>
+        <v>247</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2063</v>
+        <v>3120</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>8832</v>
+        <v>12280</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1817</v>
+        <v>3041</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>85.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>99</v>
+        <v>106.5</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1916</v>
+        <v>3147.5</v>
       </c>
     </row>
     <row r="19">
@@ -1085,31 +1085,31 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>11920</v>
+        <v>15510</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2347</v>
+        <v>3531</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>10180</v>
+        <v>13755</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>186</v>
+        <v>239</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1894</v>
+        <v>3287</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>85.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>38.7</v>
+        <v>53.4</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1932.7</v>
+        <v>3340.4</v>
       </c>
     </row>
     <row r="20">
@@ -1119,31 +1119,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>9730</v>
+        <v>10450</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1502</v>
+        <v>1984</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9851</v>
+        <v>10000</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1516</v>
+        <v>1936</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>101.2</v>
+        <v>95.7</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>25.9</v>
+        <v>25.4</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1541.9</v>
+        <v>1961.4</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7000</v>
+        <v>6150</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1359</v>
+        <v>1432</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7111</v>
+        <v>5815</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1224</v>
+        <v>1362</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>101.6</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>39.8</v>
+        <v>24.6</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1263.8</v>
+        <v>1386.6</v>
       </c>
     </row>
     <row r="22">
@@ -1187,31 +1187,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>15460</v>
+        <v>17010</v>
       </c>
       <c r="C22" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2221</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>16020</v>
+      </c>
+      <c r="F22" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>2168</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>12690</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>146</v>
-      </c>
       <c r="G22" s="3" t="n">
-        <v>1853</v>
+        <v>2238</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>82.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>85.8</v>
+        <v>126.5</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1938.8</v>
+        <v>2364.5</v>
       </c>
     </row>
     <row r="23">
@@ -1221,31 +1221,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5110</v>
+        <v>5820</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>482</v>
+        <v>711</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5618</v>
+        <v>5570</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>550</v>
+        <v>711</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>109.9</v>
+        <v>95.7</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>77.40000000000001</v>
+        <v>106.9</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>627.4</v>
+        <v>817.9</v>
       </c>
     </row>
     <row r="24">
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>11250</v>
+        <v>12490</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>301</v>
+        <v>353</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>3383</v>
+        <v>4414</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>9518</v>
+        <v>11880</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2954</v>
+        <v>4272</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>84.59999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>41.9</v>
+        <v>26.3</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2995.9</v>
+        <v>4298.3</v>
       </c>
     </row>
     <row r="25">
@@ -1289,31 +1289,31 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2130</v>
+        <v>2305</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>239</v>
+        <v>327</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>509</v>
+        <v>754</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2330</v>
+        <v>2395</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>205</v>
+        <v>303</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>479</v>
+        <v>727</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>109.4</v>
+        <v>103.9</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15.9</v>
+        <v>14.5</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>494.9</v>
+        <v>741.5</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>35169</v>
+        <v>56157</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1355.6</v>
+        <v>1520.1</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>36524.6</v>
+        <v>57677.1</v>
       </c>
     </row>
     <row r="27"/>
@@ -1340,25 +1340,25 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>37454</v>
+        <v>51409</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>6855</v>
+        <v>12051</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>31022</v>
+        <v>51742</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>183</v>
+        <v>236</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>5685</v>
+        <v>12196</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>82.8</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="29">
@@ -1368,25 +1368,25 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>76820</v>
+        <v>97020</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>14147</v>
+        <v>20758</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>69666</v>
+        <v>95569</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>12397</v>
+        <v>20005</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>90.7</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="30">
@@ -1396,25 +1396,25 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>32190</v>
+        <v>33610</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>5030</v>
+        <v>5637</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>29652</v>
+        <v>31835</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>4593</v>
+        <v>5536</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>92.09999999999999</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="31">
@@ -1424,25 +1424,25 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>67805</v>
+        <v>79875</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>13897</v>
+        <v>19224</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>61497</v>
+        <v>74860</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>12496</v>
+        <v>18418</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>90.7</v>
+        <v>93.7</v>
       </c>
     </row>
   </sheetData>
@@ -1468,7 +1468,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST 세그먼트별 - 2026-06</t>
+          <t>RM FCST 세그먼트별 - 2026-07</t>
         </is>
       </c>
     </row>
@@ -1546,34 +1546,34 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>7300</v>
+        <v>8800</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1018</v>
+        <v>1690</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1192</v>
+        <v>1746</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>109.6</v>
+        <v>102.3</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>130.8</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1588,34 +1588,34 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1100</v>
+        <v>2700</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>182</v>
+        <v>599</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1230</v>
+        <v>2700</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>163</v>
+        <v>215</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>200</v>
+        <v>581</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>111.8</v>
+        <v>100</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5">
@@ -1630,34 +1630,34 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>130</v>
-      </c>
       <c r="J5" s="3" t="n">
-        <v>15</v>
+        <v>-150</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -1672,34 +1672,34 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1100</v>
+        <v>2050</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>237</v>
+        <v>521</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>520</v>
+        <v>2050</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>128</v>
+        <v>547</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>47.3</v>
+        <v>100</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-580</v>
+        <v>0</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.5</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="7">
@@ -1714,34 +1714,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>500</v>
+        <v>860</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>224</v>
+        <v>282</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>112</v>
+        <v>242</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>240</v>
+        <v>860</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>57</v>
+        <v>236</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-260</v>
+        <v>0</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -1765,25 +1765,25 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1798,34 +1798,34 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>282</v>
+        <v>377</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>169</v>
+        <v>302</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>450</v>
+        <v>800</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>301</v>
+        <v>381</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>135</v>
+        <v>305</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-150</v>
+        <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
@@ -1840,34 +1840,34 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>450</v>
+        <v>820</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>288</v>
+        <v>395</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>130</v>
+        <v>324</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>380</v>
+        <v>820</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>307</v>
+        <v>386</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>116</v>
+        <v>317</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>84.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-70</v>
+        <v>0</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -1924,34 +1924,34 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1300</v>
+        <v>2080</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>267</v>
+        <v>333</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>347</v>
+        <v>692</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1100</v>
+        <v>2100</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>277</v>
+        <v>335</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>305</v>
+        <v>704</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>84.59999999999999</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-200</v>
+        <v>20</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1966,34 +1966,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>600</v>
+        <v>1420</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>290</v>
+        <v>359</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>174</v>
+        <v>510</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>700</v>
+        <v>1450</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>279</v>
+        <v>350</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>195</v>
+        <v>508</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>116.7</v>
+        <v>102.1</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -2032,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>25.5</v>
+        <v>468.4</v>
       </c>
       <c r="L14" s="4" t="n">
         <v>0</v>
@@ -2050,34 +2050,34 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>301</v>
+        <v>377</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>530</v>
+        <v>800</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>328</v>
+        <v>378</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>174</v>
+        <v>302</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>58.9</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-370</v>
+        <v>0</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -2092,22 +2092,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>322</v>
+        <v>391</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>97</v>
+        <v>235</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>319</v>
+        <v>389</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>96</v>
+        <v>233</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>100</v>
@@ -2116,10 +2116,10 @@
         <v>0</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="17">
@@ -2158,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>25.5</v>
+        <v>468.4</v>
       </c>
       <c r="L17" s="4" t="n">
         <v>0</v>
@@ -2179,31 +2179,31 @@
         <v>400</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19">
@@ -2218,31 +2218,31 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>124</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>60</v>
+        <v>-30</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>0.3</v>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>29.3</v>
+        <v>10.8</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>0</v>
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3230</v>
+        <v>4350</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>827</v>
+        <v>1217</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3900</v>
+        <v>4350</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>940</v>
+        <v>1196</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>120.7</v>
+        <v>100</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>670</v>
+        <v>0</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>17.8</v>
+        <v>13.6</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>69.5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
@@ -2344,34 +2344,34 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2640</v>
+        <v>3670</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>637</v>
+        <v>956</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3100</v>
+        <v>3800</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>716</v>
+        <v>950</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>117.4</v>
+        <v>103.5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>460</v>
+        <v>130</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>17.8</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="23">
@@ -2389,7 +2389,7 @@
         <v>50</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>4</v>
@@ -2398,10 +2398,10 @@
         <v>14</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="4" t="n">
         <v>28</v>
@@ -2410,10 +2410,10 @@
         <v>-36</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>29</v>
+        <v>38.2</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2100</v>
+        <v>2420</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>431</v>
+        <v>577</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>366</v>
+        <v>564</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>90.5</v>
+        <v>99.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-200</v>
+        <v>-20</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>25.1</v>
+        <v>19.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>47.6</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="25">
@@ -2470,34 +2470,34 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1100</v>
+        <v>1350</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>204</v>
+        <v>289</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1280</v>
+        <v>1500</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>226</v>
+        <v>315</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>116.4</v>
+        <v>111.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>10.2</v>
+        <v>9.1</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="26">
@@ -2554,34 +2554,34 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>828</v>
+        <v>875</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3900</v>
+        <v>3250</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>839</v>
+        <v>816</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>102.6</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>100</v>
+        <v>-250</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>15.9</v>
+        <v>19.1</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="28">
@@ -2596,34 +2596,34 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>3300</v>
+        <v>2900</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>667</v>
+        <v>690</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2850</v>
+        <v>2660</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>197</v>
+        <v>237</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>561</v>
+        <v>630</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>86.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>-450</v>
+        <v>-240</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.6</v>
+        <v>21.3</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>21.6</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="29">
@@ -2647,25 +2647,25 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>94.2</v>
+        <v>54.5</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2680,34 +2680,34 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3550</v>
+        <v>4250</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>527</v>
+        <v>799</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2600</v>
+        <v>3350</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>403</v>
+        <v>633</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>73.2</v>
+        <v>78.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-950</v>
+        <v>-900</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>31.4</v>
+        <v>30.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>81.7</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="31">
@@ -2722,34 +2722,34 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1650</v>
+        <v>2200</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>248</v>
+        <v>401</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1480</v>
+        <v>1950</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>205</v>
+        <v>348</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>89.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-170</v>
+        <v>-250</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>12</v>
+        <v>15.6</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>17.8</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="32">
@@ -2764,34 +2764,34 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>75.59999999999999</v>
+        <v>141.2</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-61</v>
+        <v>33</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="33">
@@ -2806,34 +2806,34 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1495</v>
+        <v>1670</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>396</v>
+        <v>487</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1680</v>
+        <v>1620</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>112.4</v>
+        <v>97</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>185</v>
+        <v>-50</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>32.3</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="34">
@@ -2848,34 +2848,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>930</v>
+        <v>1125</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>241</v>
+        <v>326</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1050</v>
+        <v>1130</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>266</v>
+        <v>311</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>112.9</v>
+        <v>100.4</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2899,25 +2899,25 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1070</v>
+        <v>1165</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>610</v>
+        <v>950</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>103</v>
+        <v>181</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>57</v>
+        <v>81.5</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-460</v>
+        <v>-215</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>5.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="37">
@@ -2974,34 +2974,34 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>580</v>
+        <v>650</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>145</v>
+        <v>108.3</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="38">
@@ -3016,34 +3016,34 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>106.7</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>1</v>
+        <v>-20</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>36.9</v>
+        <v>38.8</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1950</v>
+        <v>2750</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>325</v>
+        <v>549</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1830</v>
+        <v>2750</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>307</v>
+        <v>534</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>-120</v>
+        <v>0</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>80.3</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="40">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>148</v>
+        <v>277</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>880</v>
+        <v>1350</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>143</v>
+        <v>269</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>97.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>20.6</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="41">
@@ -3151,25 +3151,25 @@
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="42">
@@ -3184,34 +3184,34 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>248</v>
+        <v>439</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1580</v>
+        <v>2150</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>268</v>
+        <v>411</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>105.3</v>
+        <v>97.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>80</v>
+        <v>-50</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>116.9</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="43">
@@ -3226,34 +3226,34 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>180</v>
+        <v>299</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1430</v>
+        <v>1650</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>230</v>
+        <v>305</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>119.2</v>
+        <v>103.1</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>15.9</v>
+        <v>18</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>22.8</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="44">
@@ -3310,34 +3310,34 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>273</v>
+        <v>321</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>60</v>
+        <v>81.8</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-240</v>
+        <v>-100</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>155</v>
+        <v>176.1</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>55.8</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="46">
@@ -3352,34 +3352,34 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>266</v>
+        <v>323</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>160</v>
+        <v>258</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>750</v>
+        <v>850</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>204</v>
+        <v>269</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>125</v>
+        <v>106.2</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>112</v>
+        <v>78.3</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>84</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -3394,34 +3394,34 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>74.7</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>-38</v>
+        <v>38</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="48">
@@ -3436,34 +3436,34 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1700</v>
+        <v>2200</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>366</v>
+        <v>565</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>334</v>
+        <v>546</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>82.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>56.8</v>
+        <v>31.9</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>79.5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49">
@@ -3478,34 +3478,34 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>203</v>
+        <v>248</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>325</v>
+        <v>372</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>330</v>
+        <v>430</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>87.5</v>
+        <v>113.3</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>-200</v>
+        <v>200</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>13.9</v>
+        <v>23.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>19.4</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="50">
@@ -3529,10 +3529,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0</v>
@@ -3541,13 +3541,13 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K50" s="4" t="n">
         <v>35.9</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3562,34 +3562,34 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2800</v>
+        <v>3450</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>574</v>
+        <v>804</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2620</v>
+        <v>3020</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>197</v>
+        <v>238</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>517</v>
+        <v>719</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>93.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-180</v>
+        <v>-430</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>24.8</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="52">
@@ -3604,34 +3604,34 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2000</v>
+        <v>2800</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>388</v>
+        <v>627</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2020</v>
+        <v>2550</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>368</v>
+        <v>571</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>101</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>20</v>
+        <v>-250</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>13.9</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="53">
@@ -3655,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0</v>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K53" s="4" t="n">
         <v>0</v>
@@ -3688,34 +3688,34 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>140</v>
+        <v>211</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>960</v>
+        <v>1345</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>172</v>
+        <v>276</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>106.7</v>
+        <v>122.3</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>60</v>
+        <v>245</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>8.9</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="55">
@@ -3730,34 +3730,34 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1000</v>
+        <v>2200</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>152</v>
+        <v>433</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1770</v>
+        <v>2350</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>289</v>
+        <v>451</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>177</v>
+        <v>106.8</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>770</v>
+        <v>150</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>9.5</v>
+        <v>5.6</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>16.8</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="56">
@@ -3772,34 +3772,34 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>2.4</v>
+        <v>23.8</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3817,31 +3817,31 @@
         <v>580</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>86.2</v>
+        <v>103.4</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-80</v>
+        <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>40.3</v>
+        <v>25.9</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>20.1</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="58">
@@ -3856,34 +3856,34 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>720</v>
+        <v>690</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>970</v>
+        <v>780</v>
       </c>
       <c r="G58" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="H58" s="3" t="n">
         <v>176</v>
       </c>
-      <c r="H58" s="3" t="n">
-        <v>171</v>
-      </c>
       <c r="I58" s="4" t="n">
-        <v>134.7</v>
+        <v>113</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>250</v>
+        <v>90</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>20.1</v>
+        <v>11.6</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>19.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -3907,25 +3907,25 @@
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3940,34 +3940,34 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1100</v>
+        <v>1050</v>
       </c>
       <c r="D60" s="3" t="n">
+        <v>183</v>
+      </c>
+      <c r="E60" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="E60" s="3" t="n">
-        <v>211</v>
-      </c>
       <c r="F60" s="3" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>137</v>
+        <v>189</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>63.6</v>
+        <v>85.7</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-400</v>
+        <v>-150</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>6.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -3982,34 +3982,34 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>3800</v>
+        <v>2700</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>724</v>
+        <v>495</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>3050</v>
+        <v>2600</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>583</v>
+        <v>507</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>80.3</v>
+        <v>96.3</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-750</v>
+        <v>-100</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="62">
@@ -4024,34 +4024,34 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>177</v>
+        <v>294</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>57.1</v>
+        <v>83.3</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>-1500</v>
+        <v>-600</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>37.7</v>
+        <v>37.3</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>75.3</v>
+        <v>111.9</v>
       </c>
     </row>
     <row r="63">
@@ -4066,34 +4066,34 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>700</v>
+        <v>850</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>520</v>
+        <v>650</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>74.3</v>
+        <v>76.5</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-180</v>
+        <v>-200</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>40.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>21.2</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="64">
@@ -4108,34 +4108,34 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="F64" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="D64" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>1300</v>
-      </c>
       <c r="G64" s="3" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>130</v>
+        <v>83.3</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>15</v>
+        <v>31.3</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>19.5</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="65">
@@ -4150,34 +4150,34 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1212</v>
+        <v>750</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>151.5</v>
+        <v>125</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>412</v>
+        <v>150</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>36.6</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="66">
@@ -4192,34 +4192,34 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1850</v>
+        <v>1930</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>640</v>
+        <v>750</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1820</v>
+        <v>2200</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>668</v>
+        <v>856</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>98.40000000000001</v>
+        <v>114</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>-30</v>
+        <v>270</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>34.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -4234,34 +4234,34 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>910</v>
+        <v>1040</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>342</v>
+        <v>396</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>312</v>
+        <v>412</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1750</v>
+        <v>1600</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>609</v>
+        <v>581</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>192.3</v>
+        <v>153.8</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>840</v>
+        <v>560</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>7.7</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="68">
@@ -4318,34 +4318,34 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>525</v>
+        <v>700</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>257</v>
+        <v>344</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>835</v>
+        <v>580</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>205</v>
+        <v>293</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>159</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>310</v>
+        <v>-120</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>11.3</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="70">
@@ -4360,34 +4360,34 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>425</v>
+        <v>530</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>259</v>
+        <v>343</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>450</v>
+        <v>650</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>181</v>
+        <v>300</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>105.9</v>
+        <v>122.6</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="71">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전년 2025-06 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-07 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>5343</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>28830</v>
+        <v>29333</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5504</v>
+        <v>5662</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>102.6</v>
+        <v>104.4</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>87.09999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>5591.1</v>
+        <v>5748.5</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>1421</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5295</v>
+        <v>5053</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1364</v>
+        <v>1319</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>95.8</v>
+        <v>91.5</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>19.3</v>
+        <v>15.9</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1383.3</v>
+        <v>1334.9</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>1130</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3104</v>
+        <v>3112</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>102.2</v>
+        <v>102.5</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1164.1</v>
+        <v>1159.9</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>2399</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7572</v>
+        <v>7470</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>99</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2419.8</v>
+        <v>2409.7</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>1241</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3493</v>
+        <v>3428</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1244</v>
+        <v>1264</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1247.8</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>517</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3448</v>
+        <v>3500</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>95.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>521</v>
+        <v>526.1</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>6796</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>28134</v>
+        <v>29076</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6443</v>
+        <v>6798</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>79.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6522.7</v>
+        <v>6884.6</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>3214</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14496</v>
+        <v>14630</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3152</v>
+        <v>3217</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>98</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>60.5</v>
+        <v>60.9</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3212.5</v>
+        <v>3277.9</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>5037</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>21306</v>
+        <v>21311</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>237</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5049</v>
+        <v>5048</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>118.7</v>
+        <v>123.5</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5167.7</v>
+        <v>5171.5</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>2770</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>18490</v>
+        <v>18975</v>
       </c>
       <c r="F12" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>2685</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="I12" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>2582</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>102.3</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>134.3</v>
-      </c>
       <c r="J12" s="4" t="n">
-        <v>2716.3</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2705</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>10335</v>
+        <v>10675</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2643</v>
+        <v>2752</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>35.1</v>
+        <v>34.4</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2678.1</v>
+        <v>2786.4</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>928</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4330</v>
+        <v>4613</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>792</v>
+        <v>849</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>81.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>11.5</v>
+        <v>13.1</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>803.5</v>
+        <v>862.1</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>2188</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>10748</v>
+        <v>11056</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2053</v>
+        <v>2156</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>93.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>152.7</v>
+        <v>156.7</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2205.7</v>
+        <v>2312.7</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>2244</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>11510</v>
+        <v>11785</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2158</v>
+        <v>2248</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>95.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>167.3</v>
+        <v>170.4</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2325.3</v>
+        <v>2418.4</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1570</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5200</v>
+        <v>5149</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1514</v>
+        <v>1505</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>96.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>146.1</v>
+        <v>151.2</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1660.1</v>
+        <v>1656.2</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>3120</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12280</v>
+        <v>12515</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3041</v>
+        <v>3121</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>106.5</v>
+        <v>106.9</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3147.5</v>
+        <v>3227.9</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>3531</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>13755</v>
+        <v>14385</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3287</v>
+        <v>3533</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>88.7</v>
+        <v>92.7</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>53.4</v>
+        <v>53.7</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3340.4</v>
+        <v>3586.7</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>1984</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>10000</v>
+        <v>10160</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1936</v>
+        <v>1994</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>95.7</v>
+        <v>97.2</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>25.4</v>
+        <v>24.7</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1961.4</v>
+        <v>2018.7</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1432</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5815</v>
+        <v>6302</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>234</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1362</v>
+        <v>1475</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>94.59999999999999</v>
+        <v>102.5</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1386.6</v>
+        <v>1499.3</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2221</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>16020</v>
+        <v>16200</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2238</v>
+        <v>2257</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>94.2</v>
+        <v>95.2</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>126.5</v>
+        <v>130.4</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2364.5</v>
+        <v>2387.4</v>
       </c>
     </row>
     <row r="23">
@@ -1230,22 +1230,22 @@
         <v>711</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5570</v>
+        <v>5576</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>711</v>
+        <v>740</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>106.9</v>
+        <v>106.7</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>817.9</v>
+        <v>846.7</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>4414</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>11880</v>
+        <v>11890</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>4272</v>
+        <v>4357</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>26.3</v>
+        <v>26</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4298.3</v>
+        <v>4383</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>754</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2395</v>
+        <v>2475</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>727</v>
+        <v>787</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>103.9</v>
+        <v>107.4</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14.5</v>
+        <v>15.7</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>741.5</v>
+        <v>802.7</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>56157</v>
+        <v>57843</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1520.1</v>
+        <v>1551.3</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>57677.1</v>
+        <v>59394.3</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>12051</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>51742</v>
+        <v>51896</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>12196</v>
+        <v>12320</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>100.6</v>
+        <v>100.9</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>20758</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>95569</v>
+        <v>97523</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>20005</v>
+        <v>20692</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>98.5</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5637</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>31835</v>
+        <v>32662</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5536</v>
+        <v>5727</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>94.7</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>19224</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>74860</v>
+        <v>76588</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>18418</v>
+        <v>19105</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>93.7</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1597,25 +1597,25 @@
         <v>599</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>581</v>
+        <v>545</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>100</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1642,10 +1642,10 @@
         <v>150</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>50</v>
@@ -1681,25 +1681,25 @@
         <v>521</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2050</v>
+        <v>1650</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>547</v>
+        <v>454</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>100</v>
+        <v>80.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>16.6</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="7">
@@ -1723,25 +1723,25 @@
         <v>242</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>860</v>
+        <v>810</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>100</v>
+        <v>94.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -1810,10 +1810,10 @@
         <v>800</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>100</v>
@@ -1849,25 +1849,25 @@
         <v>324</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>820</v>
+        <v>770</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>386</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -1936,10 +1936,10 @@
         <v>2100</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>101</v>
@@ -1975,25 +1975,25 @@
         <v>510</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1450</v>
+        <v>1420</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>102.1</v>
+        <v>100</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -2059,25 +2059,25 @@
         <v>302</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>302</v>
+        <v>351</v>
       </c>
       <c r="I15" s="4" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="J15" s="3" t="n">
         <v>100</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -2101,25 +2101,25 @@
         <v>235</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2188,10 +2188,10 @@
         <v>400</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>100</v>
@@ -2227,25 +2227,25 @@
         <v>63</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20">
@@ -2311,25 +2311,25 @@
         <v>1217</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1196</v>
+        <v>1310</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>100</v>
+        <v>111.5</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>13.6</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>59</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>956</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3800</v>
+        <v>3785</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>950</v>
+        <v>1003</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>103.5</v>
+        <v>103.1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>5.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -2395,25 +2395,25 @@
         <v>4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-36</v>
+        <v>-30</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>38.2</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24">
@@ -2440,10 +2440,10 @@
         <v>2400</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>99.2</v>
@@ -2479,25 +2479,25 @@
         <v>289</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>111.1</v>
+        <v>114.8</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>13.7</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="26">
@@ -2563,25 +2563,25 @@
         <v>875</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3250</v>
+        <v>3400</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>816</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>92.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-250</v>
+        <v>-100</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>19.1</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>62.2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28">
@@ -2605,25 +2605,25 @@
         <v>690</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2660</v>
+        <v>2750</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>-240</v>
+        <v>-150</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>21.3</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>56.5</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="29">
@@ -2689,25 +2689,25 @@
         <v>799</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3350</v>
+        <v>3500</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>633</v>
+        <v>659</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>78.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-900</v>
+        <v>-750</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>30.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>102.7</v>
+        <v>107.3</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>401</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>88.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-250</v>
+        <v>-200</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>30.5</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="32">
@@ -2773,25 +2773,25 @@
         <v>7</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>141.2</v>
+        <v>180</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="33">
@@ -2815,25 +2815,25 @@
         <v>487</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1620</v>
+        <v>1600</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>297</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>-50</v>
+        <v>-70</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>326</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1130</v>
+        <v>1025</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>100.4</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>5</v>
+        <v>-100</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>210</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>950</v>
+        <v>1065</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>81.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-215</v>
+        <v>-100</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="37">
@@ -2986,10 +2986,10 @@
         <v>650</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="I37" s="4" t="n">
         <v>108.3</v>
@@ -3025,25 +3025,25 @@
         <v>4</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>38.8</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="39">
@@ -3067,25 +3067,25 @@
         <v>549</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2750</v>
+        <v>2800</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>100</v>
+        <v>101.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>120.6</v>
+        <v>122.8</v>
       </c>
     </row>
     <row r="40">
@@ -3109,25 +3109,25 @@
         <v>277</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>31.5</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="41">
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>68</v>
@@ -3163,13 +3163,13 @@
         <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="42">
@@ -3193,25 +3193,25 @@
         <v>439</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2150</v>
+        <v>2250</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>97.7</v>
+        <v>102.3</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>64</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>137.5</v>
+        <v>143.9</v>
       </c>
     </row>
     <row r="43">
@@ -3235,25 +3235,25 @@
         <v>299</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1650</v>
+        <v>1470</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>103.1</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>50</v>
+        <v>-130</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>18</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>29.7</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="44">
@@ -3319,25 +3319,25 @@
         <v>177</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>81.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>176.1</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>79.2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46">
@@ -3361,25 +3361,25 @@
         <v>258</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>106.2</v>
+        <v>100</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>78.3</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="47">
@@ -3403,25 +3403,25 @@
         <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48">
@@ -3445,25 +3445,25 @@
         <v>565</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2100</v>
+        <v>2005</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>95.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-100</v>
+        <v>-195</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>67</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>372</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1700</v>
+        <v>1850</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>113.3</v>
+        <v>123.3</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>23.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>39.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>804</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>3020</v>
+        <v>3150</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>719</v>
+        <v>769</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>87.5</v>
+        <v>91.3</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-430</v>
+        <v>-300</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>34.6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52">
@@ -3613,25 +3613,25 @@
         <v>627</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2550</v>
+        <v>2400</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>91.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>-250</v>
+        <v>-400</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>7.4</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>18.8</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="53">
@@ -3697,25 +3697,25 @@
         <v>211</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1345</v>
+        <v>1300</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>122.3</v>
+        <v>118.2</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>245</v>
+        <v>200</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="55">
@@ -3739,25 +3739,25 @@
         <v>433</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>2350</v>
+        <v>2300</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>106.8</v>
+        <v>104.5</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="56">
@@ -3823,25 +3823,25 @@
         <v>151</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>103.4</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>20</v>
+        <v>-20</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>25.9</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="58">
@@ -3865,25 +3865,25 @@
         <v>169</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>780</v>
+        <v>850</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>113</v>
+        <v>123.2</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>11.6</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -3952,10 +3952,10 @@
         <v>900</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>85.7</v>
@@ -3991,25 +3991,25 @@
         <v>495</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="62">
@@ -4033,25 +4033,25 @@
         <v>331</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>83.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>37.3</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>111.9</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="63">
@@ -4075,25 +4075,25 @@
         <v>104</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>650</v>
+        <v>520</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>76.5</v>
+        <v>61.2</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-200</v>
+        <v>-330</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>52.9</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="64">
@@ -4117,25 +4117,25 @@
         <v>151</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>31.3</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>31.3</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="65">
@@ -4159,25 +4159,25 @@
         <v>47</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>750</v>
+        <v>989</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>125</v>
+        <v>164.8</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>150</v>
+        <v>389</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>22.7</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="66">
@@ -4201,25 +4201,25 @@
         <v>750</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>856</v>
+        <v>804</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>114</v>
+        <v>103.6</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>270</v>
+        <v>70</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="67">
@@ -4246,10 +4246,10 @@
         <v>1600</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>581</v>
+        <v>635</v>
       </c>
       <c r="I67" s="4" t="n">
         <v>153.8</v>
@@ -4327,25 +4327,25 @@
         <v>240</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>580</v>
+        <v>640</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>82.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>-120</v>
+        <v>-60</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>182</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>650</v>
+        <v>690</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>122.6</v>
+        <v>130.2</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.06.16.pdf</t>
+          <t>Revenue Meeting_2026.06.23.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-17T09:17:30.288557Z</t>
+          <t>2026-06-24T08:01:04.207226Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.06.16</t>
+          <t>2026.06.23</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -550,7 +550,7 @@
         <v>5343</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>29333</v>
+        <v>29379</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>193</v>
@@ -559,13 +559,13 @@
         <v>5662</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>104.4</v>
+        <v>104.6</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>86.5</v>
+        <v>90.5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>5748.5</v>
+        <v>5752.5</v>
       </c>
     </row>
     <row r="4">
@@ -584,16 +584,16 @@
         <v>1421</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5053</v>
+        <v>5064</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>1319</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>91.5</v>
+        <v>91.7</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>15.9</v>
@@ -618,22 +618,22 @@
         <v>1130</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3112</v>
+        <v>3091</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>102.5</v>
+        <v>101.8</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>8.9</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1159.9</v>
+        <v>1155.9</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>2399</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7470</v>
+        <v>7475</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>321</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>97.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2409.7</v>
+        <v>2410.8</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>1241</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3428</v>
+        <v>3453</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>98.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>517</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3500</v>
+        <v>3429</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>1.1</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>526.1</v>
+        <v>518.1</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>6796</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>29076</v>
+        <v>29231</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6798</v>
+        <v>6824</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>100</v>
+        <v>100.5</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6884.6</v>
+        <v>6911.9</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>3214</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14630</v>
+        <v>14561</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3217</v>
+        <v>3222</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>60.9</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3277.9</v>
+        <v>3282.9</v>
       </c>
     </row>
     <row r="11">
@@ -822,7 +822,7 @@
         <v>5037</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>21311</v>
+        <v>21332</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>237</v>
@@ -831,13 +831,13 @@
         <v>5048</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>100.1</v>
+        <v>100.2</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>123.5</v>
+        <v>125.4</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5171.5</v>
+        <v>5173.4</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>2770</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>18975</v>
+        <v>19170</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>142</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2685</v>
+        <v>2724</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>140</v>
+        <v>138.3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2825</v>
+        <v>2862.3</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2705</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>10675</v>
+        <v>10785</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>258</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2752</v>
+        <v>2781</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>34.4</v>
+        <v>36.8</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2786.4</v>
+        <v>2817.8</v>
       </c>
     </row>
     <row r="14">
@@ -927,19 +927,19 @@
         <v>4613</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>87.2</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>862.1</v>
+        <v>867.9</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>2188</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>11056</v>
+        <v>11131</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2156</v>
+        <v>2201</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>96.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>156.7</v>
+        <v>161.1</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2312.7</v>
+        <v>2362.1</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>2244</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>11785</v>
+        <v>11885</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2248</v>
+        <v>2289</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>170.4</v>
+        <v>177.9</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2418.4</v>
+        <v>2466.9</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1570</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5149</v>
+        <v>5160</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1505</v>
+        <v>1511</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>95.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>151.2</v>
+        <v>160.1</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1656.2</v>
+        <v>1671.1</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>3120</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12515</v>
+        <v>12410</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3121</v>
+        <v>3132</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>99.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>106.9</v>
+        <v>104</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3227.9</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>3531</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>14385</v>
+        <v>14275</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>3533</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>92.7</v>
+        <v>92</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3586.7</v>
+        <v>3586.8</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>1984</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>10160</v>
+        <v>10162</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1994</v>
+        <v>2002</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>97.2</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2018.7</v>
+        <v>2026.5</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1432</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>6302</v>
+        <v>6208</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1475</v>
+        <v>1461</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>102.5</v>
+        <v>100.9</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1499.3</v>
+        <v>1485.1</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2221</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>16200</v>
+        <v>17450</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2257</v>
+        <v>2366</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>95.2</v>
+        <v>102.6</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>130.4</v>
+        <v>152.2</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2387.4</v>
+        <v>2518.2</v>
       </c>
     </row>
     <row r="23">
@@ -1230,22 +1230,22 @@
         <v>711</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5576</v>
+        <v>5644</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>740</v>
+        <v>767</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>95.8</v>
+        <v>97</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>106.7</v>
+        <v>112.2</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>846.7</v>
+        <v>879.2</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>4414</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>11890</v>
+        <v>11940</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>4357</v>
+        <v>4396</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>95.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>26</v>
+        <v>25.4</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4383</v>
+        <v>4421.4</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>754</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2475</v>
+        <v>2521</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>787</v>
+        <v>811</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>107.4</v>
+        <v>109.4</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15.7</v>
+        <v>17.1</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>802.7</v>
+        <v>828.1</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>57843</v>
+        <v>58235</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1551.3</v>
+        <v>1604.8</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>59394.3</v>
+        <v>59839.8</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,13 +1349,13 @@
         <v>12051</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>51896</v>
+        <v>51891</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>237</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>12320</v>
+        <v>12312</v>
       </c>
       <c r="H28" s="7" t="n">
         <v>100.9</v>
@@ -1377,16 +1377,16 @@
         <v>20758</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>97523</v>
+        <v>97946</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>20692</v>
+        <v>20831</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>100.5</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5637</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>32662</v>
+        <v>33820</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5727</v>
+        <v>5828</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>97.2</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>19224</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>76588</v>
+        <v>76712</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>19105</v>
+        <v>19263</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>95.90000000000001</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1555,25 +1555,25 @@
         <v>1690</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1746</v>
+        <v>1853</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>102.3</v>
+        <v>108</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>72.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1600,10 +1600,10 @@
         <v>2500</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>92.59999999999999</v>
@@ -1933,25 +1933,25 @@
         <v>692</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>336</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>706</v>
+        <v>756</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>101</v>
+        <v>108.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
@@ -1975,25 +1975,25 @@
         <v>510</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1420</v>
+        <v>1200</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>496</v>
+        <v>421</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>100</v>
+        <v>84.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>-220</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -2059,25 +2059,25 @@
         <v>302</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>900</v>
+        <v>930</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>112.5</v>
+        <v>116.3</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="16">
@@ -2101,25 +2101,25 @@
         <v>235</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-100</v>
+        <v>-150</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -2227,25 +2227,25 @@
         <v>63</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>58</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="20">
@@ -2311,25 +2311,25 @@
         <v>1217</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4850</v>
+        <v>4900</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>270</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1310</v>
+        <v>1323</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>111.5</v>
+        <v>112.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>13.6</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>65.8</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>956</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3785</v>
+        <v>3800</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>265</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>103.1</v>
+        <v>103.5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>5.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="23">
@@ -2395,25 +2395,25 @@
         <v>4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-30</v>
+        <v>-16</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>38.2</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="24">
@@ -2440,10 +2440,10 @@
         <v>2400</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>99.2</v>
@@ -2563,25 +2563,25 @@
         <v>875</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>816</v>
+        <v>848</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>19.1</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>65</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2608,10 +2608,10 @@
         <v>2750</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>94.8</v>
@@ -2689,25 +2689,25 @@
         <v>799</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3500</v>
+        <v>3450</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>82.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-750</v>
+        <v>-800</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>30.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>107.3</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="31">
@@ -2734,10 +2734,10 @@
         <v>2000</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>90.90000000000001</v>
@@ -2773,25 +2773,25 @@
         <v>7</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="33">
@@ -2815,25 +2815,25 @@
         <v>487</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1600</v>
+        <v>1750</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>297</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>475</v>
+        <v>520</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>95.8</v>
+        <v>104.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>-70</v>
+        <v>80</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>30.8</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>326</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1025</v>
+        <v>900</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>91.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>-100</v>
+        <v>-225</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>210</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>197</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>91.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-100</v>
+        <v>-115</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
@@ -2983,25 +2983,25 @@
         <v>112</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>650</v>
+        <v>620</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>108.3</v>
+        <v>103.3</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="38">
@@ -3067,25 +3067,25 @@
         <v>549</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>571</v>
+        <v>600</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>101.8</v>
+        <v>105.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>122.8</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="40">
@@ -3112,10 +3112,10 @@
         <v>1400</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>100</v>
@@ -3193,25 +3193,25 @@
         <v>439</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2250</v>
+        <v>2400</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>190</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>102.3</v>
+        <v>109.1</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>64</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>143.9</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="43">
@@ -3235,25 +3235,25 @@
         <v>299</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1470</v>
+        <v>1350</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>191</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>91.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>-130</v>
+        <v>-250</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>18</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>26.5</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="44">
@@ -3319,25 +3319,25 @@
         <v>177</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>330</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>176.1</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>88</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="46">
@@ -3403,25 +3403,25 @@
         <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="48">
@@ -3445,25 +3445,25 @@
         <v>565</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2005</v>
+        <v>1950</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>91.09999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-195</v>
+        <v>-250</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>63.9</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>372</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1850</v>
+        <v>1800</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>123.3</v>
+        <v>120</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>23.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>43</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>804</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>3150</v>
+        <v>3120</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>769</v>
+        <v>785</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>91.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-300</v>
+        <v>-330</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>36</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="52">
@@ -3613,25 +3613,25 @@
         <v>627</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2400</v>
+        <v>2450</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>588</v>
+        <v>617</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>85.7</v>
+        <v>87.5</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>-400</v>
+        <v>-350</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>7.4</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="53">
@@ -3697,25 +3697,25 @@
         <v>211</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>118.2</v>
+        <v>113.6</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="55">
@@ -3742,10 +3742,10 @@
         <v>2300</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="I55" s="4" t="n">
         <v>104.5</v>
@@ -3781,25 +3781,25 @@
         <v>0</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>23.8</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="57">
@@ -3823,25 +3823,25 @@
         <v>151</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>250</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>96.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>25.9</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="58">
@@ -3868,10 +3868,10 @@
         <v>850</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>123.2</v>
@@ -3949,25 +3949,25 @@
         <v>192</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>85.7</v>
+        <v>81</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-150</v>
+        <v>-200</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="61">
@@ -3994,10 +3994,10 @@
         <v>2700</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="I61" s="4" t="n">
         <v>100</v>
@@ -4033,25 +4033,25 @@
         <v>331</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>3100</v>
+        <v>3700</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>88</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>273</v>
+        <v>326</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>102.8</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>-500</v>
+        <v>100</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>37.3</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>115.6</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63">
@@ -4075,25 +4075,25 @@
         <v>104</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>520</v>
+        <v>570</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>61.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-330</v>
+        <v>-280</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>42.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="64">
@@ -4117,25 +4117,25 @@
         <v>151</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>31.3</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>34.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -4159,7 +4159,7 @@
         <v>47</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>74</v>
@@ -4168,16 +4168,16 @@
         <v>73</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>164.8</v>
+        <v>164.3</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="66">
@@ -4201,25 +4201,25 @@
         <v>750</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>402</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>804</v>
+        <v>844</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>103.6</v>
+        <v>108.8</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="67">
@@ -4243,25 +4243,25 @@
         <v>412</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1600</v>
+        <v>1550</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>153.8</v>
+        <v>149</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>560</v>
+        <v>510</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>14</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="68">
@@ -4327,25 +4327,25 @@
         <v>240</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>640</v>
+        <v>770</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>185</v>
+        <v>231</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>91.40000000000001</v>
+        <v>110</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>-60</v>
+        <v>70</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>182</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>690</v>
+        <v>660</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>130.2</v>
+        <v>124.5</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.06.23.pdf</t>
+          <t>Revenue Meeting_2026.06.30.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-24T08:01:04.207226Z</t>
+          <t>2026-07-01T08:17:56.353316Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.06.23</t>
+          <t>2026.06.30</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST - 2026-07</t>
+          <t>RM FCST - 2026-06</t>
         </is>
       </c>
     </row>
@@ -541,31 +541,31 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>28100</v>
+        <v>20810</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>190</v>
+        <v>144</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5343</v>
+        <v>2992</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>29379</v>
+        <v>18240</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5662</v>
+        <v>2652</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>104.6</v>
+        <v>87.7</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>90.5</v>
+        <v>140.1</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>5752.5</v>
+        <v>2792.1</v>
       </c>
     </row>
     <row r="4">
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5525</v>
+        <v>3245</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1421</v>
+        <v>705</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5064</v>
+        <v>1714</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>260</v>
+        <v>211</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1319</v>
+        <v>361</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>91.7</v>
+        <v>52.8</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>15.9</v>
+        <v>8.9</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1334.9</v>
+        <v>369.9</v>
       </c>
     </row>
     <row r="5">
@@ -609,31 +609,31 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3037</v>
+        <v>2047</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>372</v>
+        <v>290</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1130</v>
+        <v>594</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3091</v>
+        <v>1663</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>371</v>
+        <v>298</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1147</v>
+        <v>495</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>101.8</v>
+        <v>81.2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1155.9</v>
+        <v>502.9</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7650</v>
+        <v>5030</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>314</v>
+        <v>259</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2399</v>
+        <v>1303</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7475</v>
+        <v>4276</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>321</v>
+        <v>261</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2401</v>
+        <v>1116</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>97.7</v>
+        <v>85</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2410.8</v>
+        <v>1125.8</v>
       </c>
     </row>
     <row r="7">
@@ -677,31 +677,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3492</v>
+        <v>2897</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>355</v>
+        <v>297</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1241</v>
+        <v>860</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3453</v>
+        <v>2316</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>367</v>
+        <v>293</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1266</v>
+        <v>679</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1270</v>
+        <v>683.2</v>
       </c>
     </row>
     <row r="8">
@@ -711,31 +711,31 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3605</v>
+        <v>3425</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>517</v>
+        <v>401</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3429</v>
+        <v>2835</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>517</v>
+        <v>335</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>95.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>518.1</v>
+        <v>336.9</v>
       </c>
     </row>
     <row r="9">
@@ -745,31 +745,31 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>29075</v>
+        <v>19860</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6796</v>
+        <v>4116</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>29231</v>
+        <v>19809</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6824</v>
+        <v>3951</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>100.5</v>
+        <v>99.7</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6911.9</v>
+        <v>4040.8</v>
       </c>
     </row>
     <row r="10">
@@ -779,31 +779,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>14790</v>
+        <v>12445</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3214</v>
+        <v>2267</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14561</v>
+        <v>10537</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3222</v>
+        <v>1846</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>98.5</v>
+        <v>84.7</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>60.9</v>
+        <v>63</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3282.9</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="11">
@@ -813,31 +813,31 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>21300</v>
+        <v>20175</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>236</v>
+        <v>198</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5037</v>
+        <v>3993</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>21332</v>
+        <v>18224</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5048</v>
+        <v>3475</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>100.2</v>
+        <v>90.3</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>125.4</v>
+        <v>89.3</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5173.4</v>
+        <v>3564.3</v>
       </c>
     </row>
     <row r="12">
@@ -847,31 +847,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>18080</v>
+        <v>12960</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2770</v>
+        <v>1836</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>19170</v>
+        <v>11958</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2724</v>
+        <v>1565</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>106</v>
+        <v>92.3</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>138.3</v>
+        <v>106.7</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2862.3</v>
+        <v>1671.7</v>
       </c>
     </row>
     <row r="13">
@@ -881,31 +881,31 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>10675</v>
+        <v>9505</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2705</v>
+        <v>2223</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>10785</v>
+        <v>9580</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2781</v>
+        <v>2131</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>101</v>
+        <v>100.8</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>36.8</v>
+        <v>37.5</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2817.8</v>
+        <v>2168.5</v>
       </c>
     </row>
     <row r="14">
@@ -915,31 +915,31 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5290</v>
+        <v>4710</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>928</v>
+        <v>712</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4613</v>
+        <v>3670</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>855</v>
+        <v>542</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>87.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12.9</v>
+        <v>12</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>867.9</v>
+        <v>554</v>
       </c>
     </row>
     <row r="15">
@@ -949,31 +949,31 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>11470</v>
+        <v>9250</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2188</v>
+        <v>1425</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>11131</v>
+        <v>7335</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2201</v>
+        <v>1151</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>97</v>
+        <v>79.3</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>161.1</v>
+        <v>105</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2362.1</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="16">
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>12080</v>
+        <v>9920</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2244</v>
+        <v>1464</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>11885</v>
+        <v>9607</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>193</v>
+        <v>149</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2289</v>
+        <v>1432</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>98.40000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>177.9</v>
+        <v>155.3</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2466.9</v>
+        <v>1587.3</v>
       </c>
     </row>
     <row r="17">
@@ -1017,31 +1017,31 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5400</v>
+        <v>5030</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1570</v>
+        <v>1222</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5160</v>
+        <v>4809</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>293</v>
+        <v>252</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1511</v>
+        <v>1210</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>95.59999999999999</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>160.1</v>
+        <v>147.7</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1671.1</v>
+        <v>1357.7</v>
       </c>
     </row>
     <row r="18">
@@ -1051,31 +1051,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>12610</v>
+        <v>10360</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>247</v>
+        <v>199</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>3120</v>
+        <v>2063</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12410</v>
+        <v>8932</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>252</v>
+        <v>205</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3132</v>
+        <v>1827</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>98.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>104</v>
+        <v>101.8</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3236</v>
+        <v>1928.8</v>
       </c>
     </row>
     <row r="19">
@@ -1085,31 +1085,31 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>15510</v>
+        <v>11920</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3531</v>
+        <v>2347</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>14275</v>
+        <v>10235</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>248</v>
+        <v>186</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3533</v>
+        <v>1904</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>92</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>53.8</v>
+        <v>40</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3586.8</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="20">
@@ -1119,31 +1119,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>10450</v>
+        <v>9730</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1984</v>
+        <v>1502</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>10162</v>
+        <v>9885</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2002</v>
+        <v>1519</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>97.2</v>
+        <v>101.6</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>24.5</v>
+        <v>26.5</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2026.5</v>
+        <v>1545.5</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>6150</v>
+        <v>7000</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1432</v>
+        <v>1359</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>6208</v>
+        <v>7051</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1461</v>
+        <v>1202</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>100.9</v>
+        <v>100.7</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24.1</v>
+        <v>40.2</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1485.1</v>
+        <v>1242.2</v>
       </c>
     </row>
     <row r="22">
@@ -1187,31 +1187,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>17010</v>
+        <v>15460</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2221</v>
+        <v>2168</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17450</v>
+        <v>12005</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2366</v>
+        <v>1773</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>102.6</v>
+        <v>77.7</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>152.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2518.2</v>
+        <v>1847.1</v>
       </c>
     </row>
     <row r="23">
@@ -1221,31 +1221,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5820</v>
+        <v>5110</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>711</v>
+        <v>482</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5644</v>
+        <v>5622</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>767</v>
+        <v>557</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>112.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>879.2</v>
+        <v>635.1</v>
       </c>
     </row>
     <row r="24">
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>12490</v>
+        <v>11250</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>353</v>
+        <v>301</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4414</v>
+        <v>3383</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>11940</v>
+        <v>9438</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>368</v>
+        <v>311</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>4396</v>
+        <v>2936</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>95.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>25.4</v>
+        <v>44</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4421.4</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="25">
@@ -1289,31 +1289,31 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2305</v>
+        <v>2130</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>327</v>
+        <v>239</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>754</v>
+        <v>509</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2521</v>
+        <v>2370</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>322</v>
+        <v>206</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>811</v>
+        <v>489</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>109.4</v>
+        <v>111.3</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>17.1</v>
+        <v>16.4</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>828.1</v>
+        <v>505.4</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>58235</v>
+        <v>35148</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1604.8</v>
+        <v>1400.2</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>59839.8</v>
+        <v>36548.2</v>
       </c>
     </row>
     <row r="27"/>
@@ -1340,25 +1340,25 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>51409</v>
+        <v>37454</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>12051</v>
+        <v>6855</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>51891</v>
+        <v>31044</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>237</v>
+        <v>182</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>12312</v>
+        <v>5638</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>100.9</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1368,25 +1368,25 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>97020</v>
+        <v>76820</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>214</v>
+        <v>184</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>20758</v>
+        <v>14147</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>97946</v>
+        <v>70233</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>20831</v>
+        <v>12478</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>101</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1396,25 +1396,25 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>33610</v>
+        <v>32190</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>5637</v>
+        <v>5030</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>33820</v>
+        <v>28941</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5828</v>
+        <v>4494</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>100.6</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1424,25 +1424,25 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>79875</v>
+        <v>67805</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>19224</v>
+        <v>13897</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>76712</v>
+        <v>61893</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>251</v>
+        <v>203</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>19263</v>
+        <v>12539</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>96</v>
+        <v>91.3</v>
       </c>
     </row>
   </sheetData>
@@ -1468,7 +1468,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST 세그먼트별 - 2026-07</t>
+          <t>RM FCST 세그먼트별 - 2026-06</t>
         </is>
       </c>
     </row>
@@ -1546,34 +1546,34 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>8800</v>
+        <v>7300</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1690</v>
+        <v>1018</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>9500</v>
+        <v>8250</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1853</v>
+        <v>1229</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>700</v>
+        <v>950</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>8.1</v>
+        <v>16.3</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>76.90000000000001</v>
+        <v>134.9</v>
       </c>
     </row>
     <row r="4">
@@ -1588,34 +1588,34 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2700</v>
+        <v>1100</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>222</v>
+        <v>166</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>599</v>
+        <v>182</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2500</v>
+        <v>1250</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>220</v>
+        <v>164</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>550</v>
+        <v>204</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>92.59999999999999</v>
+        <v>113.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-200</v>
+        <v>150</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -1630,34 +1630,34 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-150</v>
+        <v>18</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>37.5</v>
+        <v>40.1</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -1672,34 +1672,34 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2050</v>
+        <v>1100</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>254</v>
+        <v>215</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>521</v>
+        <v>237</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1650</v>
+        <v>505</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>275</v>
+        <v>248</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>454</v>
+        <v>125</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>80.5</v>
+        <v>45.9</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-400</v>
+        <v>-595</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.1</v>
+        <v>16.3</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>13.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1714,34 +1714,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>860</v>
+        <v>500</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>282</v>
+        <v>224</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>242</v>
+        <v>112</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>810</v>
+        <v>220</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>220</v>
+        <v>52</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>94.2</v>
+        <v>44</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-50</v>
+        <v>-280</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -1765,25 +1765,25 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>37.5</v>
+        <v>40.1</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -1798,34 +1798,34 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>377</v>
+        <v>282</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>302</v>
+        <v>169</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>800</v>
+        <v>440</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>377</v>
+        <v>305</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>302</v>
+        <v>134</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>100</v>
+        <v>73.3</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>-160</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>8.1</v>
+        <v>16.3</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="10">
@@ -1840,34 +1840,34 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>820</v>
+        <v>450</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>395</v>
+        <v>288</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>324</v>
+        <v>130</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>770</v>
+        <v>360</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>386</v>
+        <v>309</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>297</v>
+        <v>111</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>93.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-50</v>
+        <v>-90</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11">
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>37.5</v>
+        <v>40.1</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -1924,34 +1924,34 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2080</v>
+        <v>1300</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>333</v>
+        <v>267</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>692</v>
+        <v>347</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2250</v>
+        <v>1120</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>336</v>
+        <v>274</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>756</v>
+        <v>307</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>108.2</v>
+        <v>86.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>170</v>
+        <v>-180</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1966,34 +1966,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1420</v>
+        <v>600</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>510</v>
+        <v>174</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1200</v>
+        <v>670</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>351</v>
+        <v>277</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>421</v>
+        <v>186</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>84.5</v>
+        <v>111.7</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-220</v>
+        <v>70</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14">
@@ -2032,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>468.4</v>
+        <v>25.5</v>
       </c>
       <c r="L14" s="4" t="n">
         <v>0</v>
@@ -2050,34 +2050,34 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>377</v>
+        <v>301</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>930</v>
+        <v>480</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>392</v>
+        <v>331</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>116.3</v>
+        <v>53.3</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>130</v>
+        <v>-420</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="16">
@@ -2092,34 +2092,34 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>391</v>
+        <v>322</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>235</v>
+        <v>97</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>450</v>
+        <v>280</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>382</v>
+        <v>322</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>75</v>
+        <v>93.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-150</v>
+        <v>-20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="17">
@@ -2158,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>468.4</v>
+        <v>25.5</v>
       </c>
       <c r="L17" s="4" t="n">
         <v>0</v>
@@ -2179,31 +2179,31 @@
         <v>400</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="19">
@@ -2218,31 +2218,31 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>132</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-10</v>
+        <v>80</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>0.3</v>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>10.8</v>
+        <v>29.3</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>0</v>
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4350</v>
+        <v>3230</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1217</v>
+        <v>827</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4900</v>
+        <v>4000</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1323</v>
+        <v>950</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>112.6</v>
+        <v>123.8</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>550</v>
+        <v>770</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>13.6</v>
+        <v>17.8</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>66.5</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="22">
@@ -2344,34 +2344,34 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3670</v>
+        <v>2640</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>956</v>
+        <v>637</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3800</v>
+        <v>3150</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1007</v>
+        <v>717</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>103.5</v>
+        <v>119.3</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>130</v>
+        <v>510</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="23">
@@ -2389,31 +2389,31 @@
         <v>50</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>157</v>
+        <v>69</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-16</v>
+        <v>-36</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>38.2</v>
+        <v>29</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24">
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2420</v>
+        <v>2100</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>577</v>
+        <v>431</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2400</v>
+        <v>1970</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>235</v>
+        <v>191</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>564</v>
+        <v>376</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>99.2</v>
+        <v>93.8</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-20</v>
+        <v>-130</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>19.5</v>
+        <v>25.1</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>46.8</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="25">
@@ -2470,34 +2470,34 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1350</v>
+        <v>1100</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>289</v>
+        <v>204</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1550</v>
+        <v>1330</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>215</v>
+        <v>176</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>333</v>
+        <v>235</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>114.8</v>
+        <v>120.9</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>9.1</v>
+        <v>10.2</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>14.2</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="26">
@@ -2554,31 +2554,31 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>875</v>
+        <v>828</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3500</v>
+        <v>4200</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>848</v>
+        <v>899</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>100</v>
+        <v>110.5</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>19.1</v>
+        <v>15.9</v>
       </c>
       <c r="L27" s="4" t="n">
         <v>66.90000000000001</v>
@@ -2596,34 +2596,34 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2900</v>
+        <v>3300</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>690</v>
+        <v>667</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2750</v>
+        <v>2800</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>646</v>
+        <v>550</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>94.8</v>
+        <v>84.8</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>-150</v>
+        <v>-500</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>21.3</v>
+        <v>7.6</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>58.5</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="29">
@@ -2647,25 +2647,25 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>54.5</v>
+        <v>94.2</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="30">
@@ -2680,34 +2680,34 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4250</v>
+        <v>3550</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>799</v>
+        <v>527</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3450</v>
+        <v>2800</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>653</v>
+        <v>430</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>81.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-800</v>
+        <v>-750</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>30.7</v>
+        <v>31.4</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>105.8</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31">
@@ -2722,34 +2722,34 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2200</v>
+        <v>1650</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>401</v>
+        <v>248</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>379</v>
+        <v>208</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-200</v>
+        <v>-150</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>15.6</v>
+        <v>12</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>31.3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
@@ -2764,34 +2764,34 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>170</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>56</v>
+        <v>-76</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="33">
@@ -2806,34 +2806,34 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1670</v>
+        <v>1495</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>487</v>
+        <v>396</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1750</v>
+        <v>1730</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>520</v>
+        <v>474</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>104.8</v>
+        <v>115.7</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>33.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="34">
@@ -2848,34 +2848,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1125</v>
+        <v>930</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>326</v>
+        <v>241</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>900</v>
+        <v>1030</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>261</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>80</v>
+        <v>110.8</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>-225</v>
+        <v>100</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="35">
@@ -2899,25 +2899,25 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="36">
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1165</v>
+        <v>1070</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1050</v>
+        <v>705</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>207</v>
+        <v>117</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>90.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-115</v>
+        <v>-365</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>8.9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="37">
@@ -2974,34 +2974,34 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F37" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="D37" s="3" t="n">
-        <v>186</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>620</v>
-      </c>
       <c r="G37" s="3" t="n">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>103.3</v>
+        <v>150</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="K37" s="4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L37" s="4" t="n">
         <v>5.2</v>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v>3.2</v>
       </c>
     </row>
     <row r="38">
@@ -3016,34 +3016,34 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>90</v>
+        <v>106.7</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>38.8</v>
+        <v>36.9</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="39">
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2750</v>
+        <v>1950</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>549</v>
+        <v>325</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2900</v>
+        <v>1900</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>600</v>
+        <v>320</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>105.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>150</v>
+        <v>-50</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>127.2</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1400</v>
+        <v>900</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>198</v>
+        <v>164</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>277</v>
+        <v>148</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1400</v>
+        <v>925</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>287</v>
+        <v>150</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>100</v>
+        <v>102.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>32.7</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="41">
@@ -3151,25 +3151,25 @@
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3184,34 +3184,34 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>439</v>
+        <v>248</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>456</v>
+        <v>299</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>109.1</v>
+        <v>120</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>153.5</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="43">
@@ -3226,34 +3226,34 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>299</v>
+        <v>180</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1350</v>
+        <v>1390</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>258</v>
+        <v>223</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>84.40000000000001</v>
+        <v>115.8</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>-250</v>
+        <v>190</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>18</v>
+        <v>15.9</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>24.3</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="44">
@@ -3310,34 +3310,34 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>321</v>
+        <v>273</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>182</v>
+        <v>114</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>176.1</v>
+        <v>155</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>96.8</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46">
@@ -3352,34 +3352,34 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>323</v>
+        <v>266</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>258</v>
+        <v>160</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>800</v>
+        <v>760</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>256</v>
+        <v>205</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>100</v>
+        <v>126.7</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>78.3</v>
+        <v>112</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>62.7</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -3394,34 +3394,34 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>64</v>
+        <v>-42</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48">
@@ -3436,34 +3436,34 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2200</v>
+        <v>1700</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>257</v>
+        <v>215</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>565</v>
+        <v>366</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1950</v>
+        <v>1450</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>280</v>
+        <v>239</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>546</v>
+        <v>346</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>88.59999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>-250</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>31.9</v>
+        <v>56.8</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>62.2</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="49">
@@ -3478,34 +3478,34 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>248</v>
+        <v>203</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>372</v>
+        <v>325</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1800</v>
+        <v>1400</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>272</v>
+        <v>234</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>490</v>
+        <v>327</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>120</v>
+        <v>87.5</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>23.2</v>
+        <v>13.9</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>41.8</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="50">
@@ -3529,10 +3529,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0</v>
@@ -3541,13 +3541,13 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K50" s="4" t="n">
         <v>35.9</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="51">
@@ -3562,34 +3562,34 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3450</v>
+        <v>2800</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>804</v>
+        <v>574</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>3120</v>
+        <v>2780</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>252</v>
+        <v>196</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>785</v>
+        <v>544</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>90.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-330</v>
+        <v>-20</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>11.4</v>
+        <v>9.5</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>35.7</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="52">
@@ -3604,34 +3604,34 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2800</v>
+        <v>2000</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>627</v>
+        <v>388</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2450</v>
+        <v>1990</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>252</v>
+        <v>181</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>617</v>
+        <v>361</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>87.5</v>
+        <v>99.5</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>-350</v>
+        <v>-10</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>18.1</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="53">
@@ -3655,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0</v>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K53" s="4" t="n">
         <v>0</v>
@@ -3688,34 +3688,34 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>211</v>
+        <v>140</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1250</v>
+        <v>960</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>265</v>
+        <v>172</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>113.6</v>
+        <v>106.7</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>11.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="55">
@@ -3730,34 +3730,34 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2200</v>
+        <v>1000</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>433</v>
+        <v>152</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>2300</v>
+        <v>1830</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>442</v>
+        <v>299</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>104.5</v>
+        <v>183</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>100</v>
+        <v>830</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>5.6</v>
+        <v>9.5</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>12.9</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="56">
@@ -3772,34 +3772,34 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>205</v>
+        <v>94</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>13</v>
+        <v>-6</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>23.8</v>
+        <v>2.4</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="57">
@@ -3817,31 +3817,31 @@
         <v>580</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>250</v>
+        <v>191</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>138</v>
+        <v>96</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>94.8</v>
+        <v>86.2</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-30</v>
+        <v>-80</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>25.9</v>
+        <v>40.3</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>14.2</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="58">
@@ -3856,34 +3856,34 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>690</v>
+        <v>720</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>850</v>
+        <v>990</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>123.2</v>
+        <v>137.5</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>160</v>
+        <v>270</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>11.6</v>
+        <v>20.1</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="59">
@@ -3907,25 +3907,25 @@
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="60">
@@ -3940,34 +3940,34 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>850</v>
+        <v>700</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>187</v>
+        <v>137</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>81</v>
+        <v>63.6</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>10.7</v>
+        <v>9.5</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>9.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="61">
@@ -3982,34 +3982,34 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2700</v>
+        <v>3800</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>495</v>
+        <v>724</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>100</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0</v>
+        <v>-1050</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="62">
@@ -4024,34 +4024,34 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>3700</v>
+        <v>1700</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>326</v>
+        <v>151</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>102.8</v>
+        <v>48.6</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>100</v>
+        <v>-1800</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>138</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63">
@@ -4066,34 +4066,34 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>850</v>
+        <v>700</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-280</v>
+        <v>-150</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>81.40000000000001</v>
+        <v>40.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>46.4</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="64">
@@ -4108,34 +4108,34 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1150</v>
+        <v>1360</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>95.8</v>
+        <v>136</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>-50</v>
+        <v>360</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>31.3</v>
+        <v>15</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>36</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="65">
@@ -4150,34 +4150,34 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>986</v>
+        <v>1165</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>164.3</v>
+        <v>145.6</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>29.8</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="66">
@@ -4192,34 +4192,34 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1930</v>
+        <v>1850</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>750</v>
+        <v>640</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2100</v>
+        <v>1934</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>402</v>
+        <v>365</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>844</v>
+        <v>705</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>108.8</v>
+        <v>104.5</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1.8</v>
+        <v>18.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>3.8</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="67">
@@ -4234,34 +4234,34 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1040</v>
+        <v>910</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>396</v>
+        <v>342</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>412</v>
+        <v>312</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1550</v>
+        <v>1745</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>411</v>
+        <v>351</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>636</v>
+        <v>612</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>149</v>
+        <v>191.8</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>510</v>
+        <v>835</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>14</v>
+        <v>4.4</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>21.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="68">
@@ -4318,34 +4318,34 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>700</v>
+        <v>525</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>344</v>
+        <v>257</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>240</v>
+        <v>135</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>770</v>
+        <v>885</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>300</v>
+        <v>205</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>231</v>
+        <v>182</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>110</v>
+        <v>168.6</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>70</v>
+        <v>360</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>10.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
@@ -4360,34 +4360,34 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>530</v>
+        <v>425</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>343</v>
+        <v>259</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>182</v>
+        <v>110</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>660</v>
+        <v>435</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>320</v>
+        <v>181</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>124.5</v>
+        <v>102.4</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="71">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전년 2025-07 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-06 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -478,7 +478,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST - 2026-06</t>
+          <t>RM FCST - 2026-07</t>
         </is>
       </c>
     </row>
@@ -541,31 +541,31 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>20810</v>
+        <v>28100</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2992</v>
+        <v>5343</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>18240</v>
+        <v>29379</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2652</v>
+        <v>5662</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>87.7</v>
+        <v>104.6</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>140.1</v>
+        <v>90.5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2792.1</v>
+        <v>5752.5</v>
       </c>
     </row>
     <row r="4">
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3245</v>
+        <v>5525</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>705</v>
+        <v>1421</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1714</v>
+        <v>5064</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>211</v>
+        <v>260</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>361</v>
+        <v>1319</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>52.8</v>
+        <v>91.7</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>8.9</v>
+        <v>15.9</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>369.9</v>
+        <v>1334.9</v>
       </c>
     </row>
     <row r="5">
@@ -609,31 +609,31 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2047</v>
+        <v>3037</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>290</v>
+        <v>372</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>594</v>
+        <v>1130</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1663</v>
+        <v>3091</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>298</v>
+        <v>371</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>495</v>
+        <v>1147</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>81.2</v>
+        <v>101.8</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>502.9</v>
+        <v>1155.9</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5030</v>
+        <v>7650</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>259</v>
+        <v>314</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1303</v>
+        <v>2399</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4276</v>
+        <v>7475</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>261</v>
+        <v>321</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1116</v>
+        <v>2401</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>85</v>
+        <v>97.7</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1125.8</v>
+        <v>2410.8</v>
       </c>
     </row>
     <row r="7">
@@ -677,31 +677,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2897</v>
+        <v>3492</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>297</v>
+        <v>355</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>860</v>
+        <v>1241</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2316</v>
+        <v>3453</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>293</v>
+        <v>367</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>679</v>
+        <v>1266</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>79.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>683.2</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="8">
@@ -711,31 +711,31 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3425</v>
+        <v>3605</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>401</v>
+        <v>517</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2835</v>
+        <v>3429</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>335</v>
+        <v>517</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>82.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>336.9</v>
+        <v>518.1</v>
       </c>
     </row>
     <row r="9">
@@ -745,31 +745,31 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>19860</v>
+        <v>29075</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4116</v>
+        <v>6796</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>19809</v>
+        <v>29231</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>199</v>
+        <v>233</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>3951</v>
+        <v>6824</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>99.7</v>
+        <v>100.5</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>89.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4040.8</v>
+        <v>6911.9</v>
       </c>
     </row>
     <row r="10">
@@ -779,31 +779,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>12445</v>
+        <v>14790</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2267</v>
+        <v>3214</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>10537</v>
+        <v>14561</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>175</v>
+        <v>221</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1846</v>
+        <v>3222</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>84.7</v>
+        <v>98.5</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>63</v>
+        <v>60.9</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1909</v>
+        <v>3282.9</v>
       </c>
     </row>
     <row r="11">
@@ -813,31 +813,31 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>20175</v>
+        <v>21300</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3993</v>
+        <v>5037</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>18224</v>
+        <v>21332</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>191</v>
+        <v>237</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3475</v>
+        <v>5048</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>90.3</v>
+        <v>100.2</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>89.3</v>
+        <v>125.4</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3564.3</v>
+        <v>5173.4</v>
       </c>
     </row>
     <row r="12">
@@ -847,31 +847,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>12960</v>
+        <v>18080</v>
       </c>
       <c r="C12" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2770</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>19170</v>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>1836</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>11958</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>131</v>
-      </c>
       <c r="G12" s="3" t="n">
-        <v>1565</v>
+        <v>2724</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>92.3</v>
+        <v>106</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>106.7</v>
+        <v>138.3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1671.7</v>
+        <v>2862.3</v>
       </c>
     </row>
     <row r="13">
@@ -881,31 +881,31 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>9505</v>
+        <v>10675</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2223</v>
+        <v>2705</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>9580</v>
+        <v>10785</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2131</v>
+        <v>2781</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>100.8</v>
+        <v>101</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>37.5</v>
+        <v>36.8</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2168.5</v>
+        <v>2817.8</v>
       </c>
     </row>
     <row r="14">
@@ -915,31 +915,31 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>4710</v>
+        <v>5290</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>712</v>
+        <v>928</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>3670</v>
+        <v>4613</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>542</v>
+        <v>855</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>77.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>554</v>
+        <v>867.9</v>
       </c>
     </row>
     <row r="15">
@@ -949,31 +949,31 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9250</v>
+        <v>11470</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1425</v>
+        <v>2188</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7335</v>
+        <v>11131</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1151</v>
+        <v>2201</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>79.3</v>
+        <v>97</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>105</v>
+        <v>161.1</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1256</v>
+        <v>2362.1</v>
       </c>
     </row>
     <row r="16">
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9920</v>
+        <v>12080</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1464</v>
+        <v>2244</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9607</v>
+        <v>11885</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1432</v>
+        <v>2289</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>96.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>155.3</v>
+        <v>177.9</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1587.3</v>
+        <v>2466.9</v>
       </c>
     </row>
     <row r="17">
@@ -1017,31 +1017,31 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5030</v>
+        <v>5400</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1222</v>
+        <v>1570</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4809</v>
+        <v>5160</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1210</v>
+        <v>1511</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>95.59999999999999</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>147.7</v>
+        <v>160.1</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1357.7</v>
+        <v>1671.1</v>
       </c>
     </row>
     <row r="18">
@@ -1051,31 +1051,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>10360</v>
+        <v>12610</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>199</v>
+        <v>247</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2063</v>
+        <v>3120</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>8932</v>
+        <v>12410</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1827</v>
+        <v>3132</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>86.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>101.8</v>
+        <v>104</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1928.8</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="19">
@@ -1085,31 +1085,31 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>11920</v>
+        <v>15510</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2347</v>
+        <v>3531</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>10235</v>
+        <v>14275</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>186</v>
+        <v>248</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1904</v>
+        <v>3533</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>85.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>40</v>
+        <v>53.8</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1944</v>
+        <v>3586.8</v>
       </c>
     </row>
     <row r="20">
@@ -1119,31 +1119,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>9730</v>
+        <v>10450</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1502</v>
+        <v>1984</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9885</v>
+        <v>10162</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1519</v>
+        <v>2002</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>101.6</v>
+        <v>97.2</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>26.5</v>
+        <v>24.5</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1545.5</v>
+        <v>2026.5</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7000</v>
+        <v>6150</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1359</v>
+        <v>1432</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7051</v>
+        <v>6208</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>171</v>
+        <v>235</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1202</v>
+        <v>1461</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>100.7</v>
+        <v>100.9</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>40.2</v>
+        <v>24.1</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1242.2</v>
+        <v>1485.1</v>
       </c>
     </row>
     <row r="22">
@@ -1187,31 +1187,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>15460</v>
+        <v>17010</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2168</v>
+        <v>2221</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>12005</v>
+        <v>17450</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1773</v>
+        <v>2366</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>77.7</v>
+        <v>102.6</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>74.09999999999999</v>
+        <v>152.2</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1847.1</v>
+        <v>2518.2</v>
       </c>
     </row>
     <row r="23">
@@ -1221,31 +1221,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5110</v>
+        <v>5820</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>482</v>
+        <v>711</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5622</v>
+        <v>5644</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>557</v>
+        <v>767</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>78.09999999999999</v>
+        <v>112.2</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>635.1</v>
+        <v>879.2</v>
       </c>
     </row>
     <row r="24">
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>11250</v>
+        <v>12490</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>301</v>
+        <v>353</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>3383</v>
+        <v>4414</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>9438</v>
+        <v>11940</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>311</v>
+        <v>368</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2936</v>
+        <v>4396</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>83.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>44</v>
+        <v>25.4</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2980</v>
+        <v>4421.4</v>
       </c>
     </row>
     <row r="25">
@@ -1289,31 +1289,31 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2130</v>
+        <v>2305</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>239</v>
+        <v>327</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>509</v>
+        <v>754</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2370</v>
+        <v>2521</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>206</v>
+        <v>322</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>489</v>
+        <v>811</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>111.3</v>
+        <v>109.4</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>16.4</v>
+        <v>17.1</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>505.4</v>
+        <v>828.1</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>35148</v>
+        <v>58235</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1400.2</v>
+        <v>1604.8</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>36548.2</v>
+        <v>59839.8</v>
       </c>
     </row>
     <row r="27"/>
@@ -1340,25 +1340,25 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>37454</v>
+        <v>51409</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>6855</v>
+        <v>12051</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>31044</v>
+        <v>51891</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>182</v>
+        <v>237</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>5638</v>
+        <v>12312</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>82.90000000000001</v>
+        <v>100.9</v>
       </c>
     </row>
     <row r="29">
@@ -1368,25 +1368,25 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>76820</v>
+        <v>97020</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>14147</v>
+        <v>20758</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>70233</v>
+        <v>97946</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>12478</v>
+        <v>20831</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>91.40000000000001</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30">
@@ -1396,25 +1396,25 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>32190</v>
+        <v>33610</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>5030</v>
+        <v>5637</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>28941</v>
+        <v>33820</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>4494</v>
+        <v>5828</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>89.90000000000001</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="31">
@@ -1424,25 +1424,25 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>67805</v>
+        <v>79875</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>13897</v>
+        <v>19224</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>61893</v>
+        <v>76712</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>12539</v>
+        <v>19263</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>91.3</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1468,7 +1468,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST 세그먼트별 - 2026-06</t>
+          <t>RM FCST 세그먼트별 - 2026-07</t>
         </is>
       </c>
     </row>
@@ -1546,34 +1546,34 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>7300</v>
+        <v>8800</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1018</v>
+        <v>1690</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>8250</v>
+        <v>9500</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1229</v>
+        <v>1853</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>950</v>
+        <v>700</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>134.9</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1588,34 +1588,34 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1100</v>
+        <v>2700</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>182</v>
+        <v>599</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1250</v>
+        <v>2500</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>164</v>
+        <v>220</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>204</v>
+        <v>550</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>113.6</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>150</v>
+        <v>-200</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1630,34 +1630,34 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>136</v>
-      </c>
       <c r="J5" s="3" t="n">
-        <v>18</v>
+        <v>-150</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -1672,34 +1672,34 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1100</v>
+        <v>2050</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>237</v>
+        <v>521</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>505</v>
+        <v>1650</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>125</v>
+        <v>454</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>45.9</v>
+        <v>80.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-595</v>
+        <v>-400</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="7">
@@ -1714,34 +1714,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>500</v>
+        <v>860</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>224</v>
+        <v>282</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>112</v>
+        <v>242</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>810</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>238</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>52</v>
-      </c>
       <c r="I7" s="4" t="n">
-        <v>44</v>
+        <v>94.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-280</v>
+        <v>-50</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -1765,25 +1765,25 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1798,34 +1798,34 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>282</v>
+        <v>377</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>169</v>
+        <v>302</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>440</v>
+        <v>800</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>305</v>
+        <v>377</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>134</v>
+        <v>302</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>73.3</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-160</v>
+        <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
@@ -1840,34 +1840,34 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>450</v>
+        <v>820</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>288</v>
+        <v>395</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>130</v>
+        <v>324</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>360</v>
+        <v>770</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>309</v>
+        <v>386</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>111</v>
+        <v>297</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>80</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-90</v>
+        <v>-50</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -1924,34 +1924,34 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1300</v>
+        <v>2080</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>267</v>
+        <v>333</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>347</v>
+        <v>692</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1120</v>
+        <v>2250</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>274</v>
+        <v>336</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>307</v>
+        <v>756</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>86.2</v>
+        <v>108.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-180</v>
+        <v>170</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
@@ -1966,34 +1966,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>600</v>
+        <v>1420</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>290</v>
+        <v>359</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>174</v>
+        <v>510</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>670</v>
+        <v>1200</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>277</v>
+        <v>351</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>186</v>
+        <v>421</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>111.7</v>
+        <v>84.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>70</v>
+        <v>-220</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -2032,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>25.5</v>
+        <v>468.4</v>
       </c>
       <c r="L14" s="4" t="n">
         <v>0</v>
@@ -2050,34 +2050,34 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>301</v>
+        <v>377</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>480</v>
+        <v>930</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>331</v>
+        <v>392</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>53.3</v>
+        <v>116.3</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-420</v>
+        <v>130</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="16">
@@ -2092,34 +2092,34 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>322</v>
+        <v>391</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>97</v>
+        <v>235</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>280</v>
+        <v>450</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>322</v>
+        <v>382</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>93.3</v>
+        <v>75</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-20</v>
+        <v>-150</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -2158,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>25.5</v>
+        <v>468.4</v>
       </c>
       <c r="L17" s="4" t="n">
         <v>0</v>
@@ -2179,31 +2179,31 @@
         <v>400</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19">
@@ -2218,31 +2218,31 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>132</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>80</v>
+        <v>-10</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>0.3</v>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>29.3</v>
+        <v>10.8</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>0</v>
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3230</v>
+        <v>4350</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>827</v>
+        <v>1217</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4000</v>
+        <v>4900</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>950</v>
+        <v>1323</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>123.8</v>
+        <v>112.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>770</v>
+        <v>550</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>17.8</v>
+        <v>13.6</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>71.3</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="22">
@@ -2344,34 +2344,34 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2640</v>
+        <v>3670</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>637</v>
+        <v>956</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3150</v>
+        <v>3800</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>717</v>
+        <v>1007</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>119.3</v>
+        <v>103.5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>510</v>
+        <v>130</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="23">
@@ -2389,31 +2389,31 @@
         <v>50</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-36</v>
+        <v>-16</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>29</v>
+        <v>38.2</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="24">
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2100</v>
+        <v>2420</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>431</v>
+        <v>577</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1970</v>
+        <v>2400</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>376</v>
+        <v>564</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>93.8</v>
+        <v>99.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-130</v>
+        <v>-20</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>25.1</v>
+        <v>19.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>49.4</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="25">
@@ -2470,34 +2470,34 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1100</v>
+        <v>1350</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>204</v>
+        <v>289</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1330</v>
+        <v>1550</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>235</v>
+        <v>333</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>120.9</v>
+        <v>114.8</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>10.2</v>
+        <v>9.1</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="26">
@@ -2554,31 +2554,31 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>828</v>
+        <v>875</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4200</v>
+        <v>3500</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>899</v>
+        <v>848</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>110.5</v>
+        <v>100</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>15.9</v>
+        <v>19.1</v>
       </c>
       <c r="L27" s="4" t="n">
         <v>66.90000000000001</v>
@@ -2596,34 +2596,34 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>3300</v>
+        <v>2900</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>667</v>
+        <v>690</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2800</v>
+        <v>2750</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>550</v>
+        <v>646</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>84.8</v>
+        <v>94.8</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>-500</v>
+        <v>-150</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.6</v>
+        <v>21.3</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>21.2</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="29">
@@ -2647,25 +2647,25 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>94.2</v>
+        <v>54.5</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2680,34 +2680,34 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3550</v>
+        <v>4250</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>527</v>
+        <v>799</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2800</v>
+        <v>3450</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>430</v>
+        <v>653</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>78.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-750</v>
+        <v>-800</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>31.4</v>
+        <v>30.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>88</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="31">
@@ -2722,34 +2722,34 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1650</v>
+        <v>2200</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>248</v>
+        <v>401</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>208</v>
+        <v>379</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-150</v>
+        <v>-200</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>12</v>
+        <v>15.6</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>18</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="32">
@@ -2764,34 +2764,34 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>170</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-76</v>
+        <v>56</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="33">
@@ -2806,34 +2806,34 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1495</v>
+        <v>1670</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>396</v>
+        <v>487</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1730</v>
+        <v>1750</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>474</v>
+        <v>520</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>115.7</v>
+        <v>104.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>235</v>
+        <v>80</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="34">
@@ -2848,34 +2848,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>930</v>
+        <v>1125</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>241</v>
+        <v>326</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1030</v>
+        <v>900</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>261</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>110.8</v>
+        <v>80</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>100</v>
+        <v>-225</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="35">
@@ -2899,25 +2899,25 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1070</v>
+        <v>1165</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>705</v>
+        <v>1050</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>117</v>
+        <v>207</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-365</v>
+        <v>-115</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>6.2</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
@@ -2974,34 +2974,34 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>150</v>
+        <v>103.3</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="38">
@@ -3016,34 +3016,34 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>132</v>
+        <v>214</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>106.7</v>
+        <v>90</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>36.9</v>
+        <v>38.8</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="39">
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1950</v>
+        <v>2750</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>325</v>
+        <v>549</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1900</v>
+        <v>2900</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>320</v>
+        <v>600</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>105.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>-50</v>
+        <v>150</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="40">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>148</v>
+        <v>277</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>925</v>
+        <v>1400</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>163</v>
+        <v>205</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>150</v>
+        <v>287</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>102.8</v>
+        <v>100</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>21.6</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="41">
@@ -3151,25 +3151,25 @@
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="42">
@@ -3184,34 +3184,34 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>248</v>
+        <v>439</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>299</v>
+        <v>456</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>120</v>
+        <v>109.1</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>133.1</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="43">
@@ -3226,34 +3226,34 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>180</v>
+        <v>299</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1390</v>
+        <v>1350</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>115.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>190</v>
+        <v>-250</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>15.9</v>
+        <v>18</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="44">
@@ -3310,34 +3310,34 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>273</v>
+        <v>321</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>284</v>
+        <v>330</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>155</v>
+        <v>176.1</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>62</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="46">
@@ -3352,34 +3352,34 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>266</v>
+        <v>323</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>160</v>
+        <v>258</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>205</v>
+        <v>256</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>126.7</v>
+        <v>100</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>112</v>
+        <v>78.3</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>85.09999999999999</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="47">
@@ -3394,34 +3394,34 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>-42</v>
+        <v>64</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="48">
@@ -3436,34 +3436,34 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1700</v>
+        <v>2200</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>366</v>
+        <v>565</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1450</v>
+        <v>1950</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>239</v>
+        <v>280</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>346</v>
+        <v>546</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>85.3</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>-250</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>56.8</v>
+        <v>31.9</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>82.3</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="49">
@@ -3478,34 +3478,34 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>203</v>
+        <v>248</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>325</v>
+        <v>372</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>327</v>
+        <v>490</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>87.5</v>
+        <v>120</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>13.9</v>
+        <v>23.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>19.4</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="50">
@@ -3529,10 +3529,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0</v>
@@ -3541,13 +3541,13 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K50" s="4" t="n">
         <v>35.9</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3562,34 +3562,34 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2800</v>
+        <v>3450</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>574</v>
+        <v>804</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2780</v>
+        <v>3120</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>196</v>
+        <v>252</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>544</v>
+        <v>785</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>99.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-20</v>
+        <v>-330</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>26.3</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="52">
@@ -3604,34 +3604,34 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2000</v>
+        <v>2800</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>388</v>
+        <v>627</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1990</v>
+        <v>2450</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>181</v>
+        <v>252</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>361</v>
+        <v>617</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>99.5</v>
+        <v>87.5</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>-10</v>
+        <v>-350</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>13.7</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="53">
@@ -3655,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0</v>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K53" s="4" t="n">
         <v>0</v>
@@ -3688,34 +3688,34 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>140</v>
+        <v>211</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>960</v>
+        <v>1250</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>172</v>
+        <v>265</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>106.7</v>
+        <v>113.6</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>8.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="55">
@@ -3730,34 +3730,34 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1000</v>
+        <v>2200</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>152</v>
+        <v>433</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1830</v>
+        <v>2300</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>299</v>
+        <v>442</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>183</v>
+        <v>104.5</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>830</v>
+        <v>100</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>9.5</v>
+        <v>5.6</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>17.4</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="56">
@@ -3772,34 +3772,34 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>94</v>
+        <v>205</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-6</v>
+        <v>13</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>2.4</v>
+        <v>23.8</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="57">
@@ -3817,31 +3817,31 @@
         <v>580</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>86.2</v>
+        <v>94.8</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-80</v>
+        <v>-30</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>40.3</v>
+        <v>25.9</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>20.1</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="58">
@@ -3856,34 +3856,34 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>720</v>
+        <v>690</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="E58" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="J58" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="F58" s="3" t="n">
-        <v>990</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="H58" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="I58" s="4" t="n">
-        <v>137.5</v>
-      </c>
-      <c r="J58" s="3" t="n">
-        <v>270</v>
-      </c>
       <c r="K58" s="4" t="n">
-        <v>20.1</v>
+        <v>11.6</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>19.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -3907,25 +3907,25 @@
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3940,34 +3940,34 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1100</v>
+        <v>1050</v>
       </c>
       <c r="D60" s="3" t="n">
+        <v>183</v>
+      </c>
+      <c r="E60" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="E60" s="3" t="n">
-        <v>211</v>
-      </c>
       <c r="F60" s="3" t="n">
-        <v>700</v>
+        <v>850</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>63.6</v>
+        <v>81</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>6.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="61">
@@ -3982,34 +3982,34 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>3800</v>
+        <v>2700</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>724</v>
+        <v>495</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-1050</v>
+        <v>0</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="62">
@@ -4024,34 +4024,34 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>1700</v>
+        <v>3700</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>151</v>
+        <v>326</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>48.6</v>
+        <v>102.8</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>-1800</v>
+        <v>100</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>37.7</v>
+        <v>37.3</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>64</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63">
@@ -4066,34 +4066,34 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>700</v>
+        <v>850</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>78.59999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-150</v>
+        <v>-280</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>40.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>22.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="64">
@@ -4108,34 +4108,34 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>100</v>
+        <v>151</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1360</v>
+        <v>1150</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>136</v>
+        <v>95.8</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>360</v>
+        <v>-50</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>15</v>
+        <v>31.3</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>20.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -4150,34 +4150,34 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1165</v>
+        <v>986</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>145.6</v>
+        <v>164.3</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>35.2</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="66">
@@ -4192,34 +4192,34 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1850</v>
+        <v>1930</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>640</v>
+        <v>750</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1934</v>
+        <v>2100</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>705</v>
+        <v>844</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>104.5</v>
+        <v>108.8</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>36.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="67">
@@ -4234,34 +4234,34 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>910</v>
+        <v>1040</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>342</v>
+        <v>396</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>312</v>
+        <v>412</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1745</v>
+        <v>1550</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>351</v>
+        <v>411</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>612</v>
+        <v>636</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>191.8</v>
+        <v>149</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>835</v>
+        <v>510</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>7.7</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="68">
@@ -4318,34 +4318,34 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>525</v>
+        <v>700</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>257</v>
+        <v>344</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>885</v>
+        <v>770</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>205</v>
+        <v>300</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>182</v>
+        <v>231</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>168.6</v>
+        <v>110</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>360</v>
+        <v>70</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="70">
@@ -4360,34 +4360,34 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>425</v>
+        <v>530</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>259</v>
+        <v>343</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>435</v>
+        <v>660</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>181</v>
+        <v>320</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>102.4</v>
+        <v>124.5</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="71">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전년 2025-06 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-07 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST - 2026-06</t>
+          <t>RM FCST - 2026-07</t>
         </is>
       </c>
     </row>
@@ -541,31 +541,31 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>20810</v>
+        <v>28100</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2992</v>
+        <v>5343</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>18240</v>
+        <v>29379</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2652</v>
+        <v>5662</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>87.7</v>
+        <v>104.6</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>140.1</v>
+        <v>90.5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2792.1</v>
+        <v>5752.5</v>
       </c>
     </row>
     <row r="4">
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3245</v>
+        <v>5525</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>705</v>
+        <v>1421</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1714</v>
+        <v>5064</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>211</v>
+        <v>260</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>361</v>
+        <v>1319</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>52.8</v>
+        <v>91.7</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>8.9</v>
+        <v>15.9</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>369.9</v>
+        <v>1334.9</v>
       </c>
     </row>
     <row r="5">
@@ -609,31 +609,31 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2047</v>
+        <v>3037</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>290</v>
+        <v>372</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>594</v>
+        <v>1130</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1663</v>
+        <v>3091</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>298</v>
+        <v>371</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>495</v>
+        <v>1147</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>81.2</v>
+        <v>101.8</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>502.9</v>
+        <v>1155.9</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5030</v>
+        <v>7650</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>259</v>
+        <v>314</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1303</v>
+        <v>2399</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4276</v>
+        <v>7475</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>261</v>
+        <v>321</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1116</v>
+        <v>2401</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>85</v>
+        <v>97.7</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1125.8</v>
+        <v>2410.8</v>
       </c>
     </row>
     <row r="7">
@@ -677,31 +677,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2897</v>
+        <v>3492</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>297</v>
+        <v>355</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>860</v>
+        <v>1241</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2316</v>
+        <v>3453</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>293</v>
+        <v>367</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>679</v>
+        <v>1266</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>79.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>683.2</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="8">
@@ -711,31 +711,31 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3425</v>
+        <v>3605</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>401</v>
+        <v>517</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2835</v>
+        <v>3429</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>335</v>
+        <v>517</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>82.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>336.9</v>
+        <v>518.1</v>
       </c>
     </row>
     <row r="9">
@@ -745,31 +745,31 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>19860</v>
+        <v>29075</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4116</v>
+        <v>6796</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>19809</v>
+        <v>29231</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>199</v>
+        <v>233</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>3951</v>
+        <v>6824</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>99.7</v>
+        <v>100.5</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>89.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4040.8</v>
+        <v>6911.9</v>
       </c>
     </row>
     <row r="10">
@@ -779,31 +779,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>12445</v>
+        <v>14790</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2267</v>
+        <v>3214</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>10537</v>
+        <v>14561</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>175</v>
+        <v>221</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1846</v>
+        <v>3222</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>84.7</v>
+        <v>98.5</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>63</v>
+        <v>60.9</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1909</v>
+        <v>3282.9</v>
       </c>
     </row>
     <row r="11">
@@ -813,31 +813,31 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>20175</v>
+        <v>21300</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3993</v>
+        <v>5037</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>18224</v>
+        <v>21332</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>191</v>
+        <v>237</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3475</v>
+        <v>5048</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>90.3</v>
+        <v>100.2</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>89.3</v>
+        <v>125.4</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3564.3</v>
+        <v>5173.4</v>
       </c>
     </row>
     <row r="12">
@@ -847,31 +847,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>12960</v>
+        <v>18080</v>
       </c>
       <c r="C12" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2770</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>19170</v>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>1836</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>11958</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>131</v>
-      </c>
       <c r="G12" s="3" t="n">
-        <v>1565</v>
+        <v>2724</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>92.3</v>
+        <v>106</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>106.7</v>
+        <v>138.3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1671.7</v>
+        <v>2862.3</v>
       </c>
     </row>
     <row r="13">
@@ -881,31 +881,31 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>9505</v>
+        <v>10675</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2223</v>
+        <v>2705</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>9580</v>
+        <v>10785</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2131</v>
+        <v>2781</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>100.8</v>
+        <v>101</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>37.5</v>
+        <v>36.8</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2168.5</v>
+        <v>2817.8</v>
       </c>
     </row>
     <row r="14">
@@ -915,31 +915,31 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>4710</v>
+        <v>5290</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>712</v>
+        <v>928</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>3670</v>
+        <v>4613</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>542</v>
+        <v>855</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>77.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>554</v>
+        <v>867.9</v>
       </c>
     </row>
     <row r="15">
@@ -949,31 +949,31 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9250</v>
+        <v>11470</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1425</v>
+        <v>2188</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7335</v>
+        <v>11131</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1151</v>
+        <v>2201</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>79.3</v>
+        <v>97</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>105</v>
+        <v>161.1</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1256</v>
+        <v>2362.1</v>
       </c>
     </row>
     <row r="16">
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9920</v>
+        <v>12080</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1464</v>
+        <v>2244</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9607</v>
+        <v>11885</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1432</v>
+        <v>2289</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>96.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>155.3</v>
+        <v>177.9</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1587.3</v>
+        <v>2466.9</v>
       </c>
     </row>
     <row r="17">
@@ -1017,31 +1017,31 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5030</v>
+        <v>5400</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1222</v>
+        <v>1570</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4809</v>
+        <v>5160</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1210</v>
+        <v>1511</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>95.59999999999999</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>147.7</v>
+        <v>160.1</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1357.7</v>
+        <v>1671.1</v>
       </c>
     </row>
     <row r="18">
@@ -1051,31 +1051,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>10360</v>
+        <v>12610</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>199</v>
+        <v>247</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2063</v>
+        <v>3120</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>8932</v>
+        <v>12410</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1827</v>
+        <v>3132</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>86.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>101.8</v>
+        <v>104</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1928.8</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="19">
@@ -1085,31 +1085,31 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>11920</v>
+        <v>15510</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2347</v>
+        <v>3531</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>10235</v>
+        <v>14275</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>186</v>
+        <v>248</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1904</v>
+        <v>3533</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>85.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>40</v>
+        <v>53.8</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1944</v>
+        <v>3586.8</v>
       </c>
     </row>
     <row r="20">
@@ -1119,31 +1119,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>9730</v>
+        <v>10450</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1502</v>
+        <v>1984</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9885</v>
+        <v>10162</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1519</v>
+        <v>2002</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>101.6</v>
+        <v>97.2</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>26.5</v>
+        <v>24.5</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1545.5</v>
+        <v>2026.5</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7000</v>
+        <v>6150</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1359</v>
+        <v>1432</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7051</v>
+        <v>6208</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>171</v>
+        <v>235</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1202</v>
+        <v>1461</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>100.7</v>
+        <v>100.9</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>40.2</v>
+        <v>24.1</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1242.2</v>
+        <v>1485.1</v>
       </c>
     </row>
     <row r="22">
@@ -1187,31 +1187,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>15460</v>
+        <v>17010</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2168</v>
+        <v>2221</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>12005</v>
+        <v>17450</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1773</v>
+        <v>2366</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>77.7</v>
+        <v>102.6</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>74.09999999999999</v>
+        <v>152.2</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1847.1</v>
+        <v>2518.2</v>
       </c>
     </row>
     <row r="23">
@@ -1221,31 +1221,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5110</v>
+        <v>5820</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>482</v>
+        <v>711</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5622</v>
+        <v>5644</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>557</v>
+        <v>767</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>78.09999999999999</v>
+        <v>112.2</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>635.1</v>
+        <v>879.2</v>
       </c>
     </row>
     <row r="24">
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>11250</v>
+        <v>12490</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>301</v>
+        <v>353</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>3383</v>
+        <v>4414</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>9438</v>
+        <v>11940</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>311</v>
+        <v>368</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2936</v>
+        <v>4396</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>83.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>44</v>
+        <v>25.4</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2980</v>
+        <v>4421.4</v>
       </c>
     </row>
     <row r="25">
@@ -1289,31 +1289,31 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2130</v>
+        <v>2305</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>239</v>
+        <v>327</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>509</v>
+        <v>754</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2370</v>
+        <v>2521</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>206</v>
+        <v>322</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>489</v>
+        <v>811</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>111.3</v>
+        <v>109.4</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>16.4</v>
+        <v>17.1</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>505.4</v>
+        <v>828.1</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>35148</v>
+        <v>58235</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1400.2</v>
+        <v>1604.8</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>36548.2</v>
+        <v>59839.8</v>
       </c>
     </row>
     <row r="27"/>
@@ -1340,25 +1340,25 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>37454</v>
+        <v>51409</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>6855</v>
+        <v>12051</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>31044</v>
+        <v>51891</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>182</v>
+        <v>237</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>5638</v>
+        <v>12312</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>82.90000000000001</v>
+        <v>100.9</v>
       </c>
     </row>
     <row r="29">
@@ -1368,25 +1368,25 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>76820</v>
+        <v>97020</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>14147</v>
+        <v>20758</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>70233</v>
+        <v>97946</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>12478</v>
+        <v>20831</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>91.40000000000001</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30">
@@ -1396,25 +1396,25 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>32190</v>
+        <v>33610</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>5030</v>
+        <v>5637</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>28941</v>
+        <v>33820</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>4494</v>
+        <v>5828</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>89.90000000000001</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="31">
@@ -1424,25 +1424,25 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>67805</v>
+        <v>79875</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>13897</v>
+        <v>19224</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>61893</v>
+        <v>76712</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>12539</v>
+        <v>19263</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>91.3</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1468,7 +1468,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST 세그먼트별 - 2026-06</t>
+          <t>RM FCST 세그먼트별 - 2026-07</t>
         </is>
       </c>
     </row>
@@ -1546,34 +1546,34 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>7300</v>
+        <v>8800</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1018</v>
+        <v>1690</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>8250</v>
+        <v>9500</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1229</v>
+        <v>1853</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>950</v>
+        <v>700</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>134.9</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1588,34 +1588,34 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1100</v>
+        <v>2700</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>182</v>
+        <v>599</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1250</v>
+        <v>2500</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>164</v>
+        <v>220</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>204</v>
+        <v>550</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>113.6</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>150</v>
+        <v>-200</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1630,34 +1630,34 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>136</v>
-      </c>
       <c r="J5" s="3" t="n">
-        <v>18</v>
+        <v>-150</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -1672,34 +1672,34 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1100</v>
+        <v>2050</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>237</v>
+        <v>521</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>505</v>
+        <v>1650</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>125</v>
+        <v>454</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>45.9</v>
+        <v>80.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-595</v>
+        <v>-400</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="7">
@@ -1714,34 +1714,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>500</v>
+        <v>860</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>224</v>
+        <v>282</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>112</v>
+        <v>242</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>810</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>238</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>52</v>
-      </c>
       <c r="I7" s="4" t="n">
-        <v>44</v>
+        <v>94.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-280</v>
+        <v>-50</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -1765,25 +1765,25 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1798,34 +1798,34 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>282</v>
+        <v>377</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>169</v>
+        <v>302</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>440</v>
+        <v>800</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>305</v>
+        <v>377</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>134</v>
+        <v>302</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>73.3</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-160</v>
+        <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
@@ -1840,34 +1840,34 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>450</v>
+        <v>820</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>288</v>
+        <v>395</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>130</v>
+        <v>324</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>360</v>
+        <v>770</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>309</v>
+        <v>386</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>111</v>
+        <v>297</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>80</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-90</v>
+        <v>-50</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -1924,34 +1924,34 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1300</v>
+        <v>2080</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>267</v>
+        <v>333</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>347</v>
+        <v>692</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1120</v>
+        <v>2250</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>274</v>
+        <v>336</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>307</v>
+        <v>756</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>86.2</v>
+        <v>108.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-180</v>
+        <v>170</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
@@ -1966,34 +1966,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>600</v>
+        <v>1420</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>290</v>
+        <v>359</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>174</v>
+        <v>510</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>670</v>
+        <v>1200</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>277</v>
+        <v>351</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>186</v>
+        <v>421</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>111.7</v>
+        <v>84.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>70</v>
+        <v>-220</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -2032,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>25.5</v>
+        <v>468.4</v>
       </c>
       <c r="L14" s="4" t="n">
         <v>0</v>
@@ -2050,34 +2050,34 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>301</v>
+        <v>377</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>480</v>
+        <v>930</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>331</v>
+        <v>392</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>53.3</v>
+        <v>116.3</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-420</v>
+        <v>130</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="16">
@@ -2092,34 +2092,34 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>322</v>
+        <v>391</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>97</v>
+        <v>235</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>280</v>
+        <v>450</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>322</v>
+        <v>382</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>93.3</v>
+        <v>75</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-20</v>
+        <v>-150</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -2158,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>25.5</v>
+        <v>468.4</v>
       </c>
       <c r="L17" s="4" t="n">
         <v>0</v>
@@ -2179,31 +2179,31 @@
         <v>400</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19">
@@ -2218,31 +2218,31 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>132</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>80</v>
+        <v>-10</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>0.3</v>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>29.3</v>
+        <v>10.8</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>0</v>
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3230</v>
+        <v>4350</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>827</v>
+        <v>1217</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4000</v>
+        <v>4900</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>950</v>
+        <v>1323</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>123.8</v>
+        <v>112.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>770</v>
+        <v>550</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>17.8</v>
+        <v>13.6</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>71.3</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="22">
@@ -2344,34 +2344,34 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2640</v>
+        <v>3670</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>637</v>
+        <v>956</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3150</v>
+        <v>3800</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>717</v>
+        <v>1007</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>119.3</v>
+        <v>103.5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>510</v>
+        <v>130</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="23">
@@ -2389,31 +2389,31 @@
         <v>50</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-36</v>
+        <v>-16</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>29</v>
+        <v>38.2</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="24">
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2100</v>
+        <v>2420</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>431</v>
+        <v>577</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1970</v>
+        <v>2400</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>376</v>
+        <v>564</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>93.8</v>
+        <v>99.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-130</v>
+        <v>-20</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>25.1</v>
+        <v>19.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>49.4</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="25">
@@ -2470,34 +2470,34 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1100</v>
+        <v>1350</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>204</v>
+        <v>289</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1330</v>
+        <v>1550</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>235</v>
+        <v>333</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>120.9</v>
+        <v>114.8</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>10.2</v>
+        <v>9.1</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="26">
@@ -2554,31 +2554,31 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>828</v>
+        <v>875</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4200</v>
+        <v>3500</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>899</v>
+        <v>848</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>110.5</v>
+        <v>100</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>15.9</v>
+        <v>19.1</v>
       </c>
       <c r="L27" s="4" t="n">
         <v>66.90000000000001</v>
@@ -2596,34 +2596,34 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>3300</v>
+        <v>2900</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>667</v>
+        <v>690</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2800</v>
+        <v>2750</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>550</v>
+        <v>646</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>84.8</v>
+        <v>94.8</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>-500</v>
+        <v>-150</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.6</v>
+        <v>21.3</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>21.2</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="29">
@@ -2647,25 +2647,25 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>94.2</v>
+        <v>54.5</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2680,34 +2680,34 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3550</v>
+        <v>4250</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>527</v>
+        <v>799</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2800</v>
+        <v>3450</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>430</v>
+        <v>653</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>78.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-750</v>
+        <v>-800</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>31.4</v>
+        <v>30.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>88</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="31">
@@ -2722,34 +2722,34 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1650</v>
+        <v>2200</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>248</v>
+        <v>401</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>208</v>
+        <v>379</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-150</v>
+        <v>-200</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>12</v>
+        <v>15.6</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>18</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="32">
@@ -2764,34 +2764,34 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>170</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-76</v>
+        <v>56</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="33">
@@ -2806,34 +2806,34 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1495</v>
+        <v>1670</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>396</v>
+        <v>487</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1730</v>
+        <v>1750</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>474</v>
+        <v>520</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>115.7</v>
+        <v>104.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>235</v>
+        <v>80</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="34">
@@ -2848,34 +2848,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>930</v>
+        <v>1125</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>241</v>
+        <v>326</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1030</v>
+        <v>900</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>261</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>110.8</v>
+        <v>80</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>100</v>
+        <v>-225</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="35">
@@ -2899,25 +2899,25 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1070</v>
+        <v>1165</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>705</v>
+        <v>1050</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>117</v>
+        <v>207</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-365</v>
+        <v>-115</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>6.2</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
@@ -2974,34 +2974,34 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>150</v>
+        <v>103.3</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="38">
@@ -3016,34 +3016,34 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>132</v>
+        <v>214</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>106.7</v>
+        <v>90</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>36.9</v>
+        <v>38.8</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="39">
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1950</v>
+        <v>2750</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>325</v>
+        <v>549</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1900</v>
+        <v>2900</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>320</v>
+        <v>600</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>105.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>-50</v>
+        <v>150</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="40">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>148</v>
+        <v>277</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>925</v>
+        <v>1400</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>163</v>
+        <v>205</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>150</v>
+        <v>287</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>102.8</v>
+        <v>100</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>21.6</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="41">
@@ -3151,25 +3151,25 @@
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="42">
@@ -3184,34 +3184,34 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>248</v>
+        <v>439</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>299</v>
+        <v>456</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>120</v>
+        <v>109.1</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>133.1</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="43">
@@ -3226,34 +3226,34 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>180</v>
+        <v>299</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1390</v>
+        <v>1350</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>115.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>190</v>
+        <v>-250</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>15.9</v>
+        <v>18</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="44">
@@ -3310,34 +3310,34 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>273</v>
+        <v>321</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>284</v>
+        <v>330</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>155</v>
+        <v>176.1</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>62</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="46">
@@ -3352,34 +3352,34 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>266</v>
+        <v>323</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>160</v>
+        <v>258</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>205</v>
+        <v>256</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>126.7</v>
+        <v>100</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>112</v>
+        <v>78.3</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>85.09999999999999</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="47">
@@ -3394,34 +3394,34 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>-42</v>
+        <v>64</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="48">
@@ -3436,34 +3436,34 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1700</v>
+        <v>2200</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>366</v>
+        <v>565</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1450</v>
+        <v>1950</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>239</v>
+        <v>280</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>346</v>
+        <v>546</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>85.3</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>-250</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>56.8</v>
+        <v>31.9</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>82.3</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="49">
@@ -3478,34 +3478,34 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>203</v>
+        <v>248</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>325</v>
+        <v>372</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>327</v>
+        <v>490</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>87.5</v>
+        <v>120</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>13.9</v>
+        <v>23.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>19.4</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="50">
@@ -3529,10 +3529,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0</v>
@@ -3541,13 +3541,13 @@
         <v>0</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K50" s="4" t="n">
         <v>35.9</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3562,34 +3562,34 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2800</v>
+        <v>3450</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>574</v>
+        <v>804</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2780</v>
+        <v>3120</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>196</v>
+        <v>252</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>544</v>
+        <v>785</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>99.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-20</v>
+        <v>-330</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>26.3</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="52">
@@ -3604,34 +3604,34 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2000</v>
+        <v>2800</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>388</v>
+        <v>627</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1990</v>
+        <v>2450</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>181</v>
+        <v>252</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>361</v>
+        <v>617</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>99.5</v>
+        <v>87.5</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>-10</v>
+        <v>-350</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>13.7</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="53">
@@ -3655,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0</v>
@@ -3667,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K53" s="4" t="n">
         <v>0</v>
@@ -3688,34 +3688,34 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>140</v>
+        <v>211</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>960</v>
+        <v>1250</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>172</v>
+        <v>265</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>106.7</v>
+        <v>113.6</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>8.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="55">
@@ -3730,34 +3730,34 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1000</v>
+        <v>2200</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>152</v>
+        <v>433</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1830</v>
+        <v>2300</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>299</v>
+        <v>442</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>183</v>
+        <v>104.5</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>830</v>
+        <v>100</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>9.5</v>
+        <v>5.6</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>17.4</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="56">
@@ -3772,34 +3772,34 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>94</v>
+        <v>205</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-6</v>
+        <v>13</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>2.4</v>
+        <v>23.8</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="57">
@@ -3817,31 +3817,31 @@
         <v>580</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>86.2</v>
+        <v>94.8</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-80</v>
+        <v>-30</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>40.3</v>
+        <v>25.9</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>20.1</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="58">
@@ -3856,34 +3856,34 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>720</v>
+        <v>690</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="E58" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="J58" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="F58" s="3" t="n">
-        <v>990</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="H58" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="I58" s="4" t="n">
-        <v>137.5</v>
-      </c>
-      <c r="J58" s="3" t="n">
-        <v>270</v>
-      </c>
       <c r="K58" s="4" t="n">
-        <v>20.1</v>
+        <v>11.6</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>19.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -3907,25 +3907,25 @@
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3940,34 +3940,34 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1100</v>
+        <v>1050</v>
       </c>
       <c r="D60" s="3" t="n">
+        <v>183</v>
+      </c>
+      <c r="E60" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="E60" s="3" t="n">
-        <v>211</v>
-      </c>
       <c r="F60" s="3" t="n">
-        <v>700</v>
+        <v>850</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>63.6</v>
+        <v>81</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>6.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="61">
@@ -3982,34 +3982,34 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>3800</v>
+        <v>2700</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>724</v>
+        <v>495</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-1050</v>
+        <v>0</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="62">
@@ -4024,34 +4024,34 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>1700</v>
+        <v>3700</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>151</v>
+        <v>326</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>48.6</v>
+        <v>102.8</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>-1800</v>
+        <v>100</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>37.7</v>
+        <v>37.3</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>64</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63">
@@ -4066,34 +4066,34 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>700</v>
+        <v>850</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>78.59999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-150</v>
+        <v>-280</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>40.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>22.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="64">
@@ -4108,34 +4108,34 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>100</v>
+        <v>151</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1360</v>
+        <v>1150</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>136</v>
+        <v>95.8</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>360</v>
+        <v>-50</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>15</v>
+        <v>31.3</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>20.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -4150,34 +4150,34 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1165</v>
+        <v>986</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>145.6</v>
+        <v>164.3</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>35.2</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="66">
@@ -4192,34 +4192,34 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1850</v>
+        <v>1930</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>640</v>
+        <v>750</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1934</v>
+        <v>2100</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>705</v>
+        <v>844</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>104.5</v>
+        <v>108.8</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>36.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="67">
@@ -4234,34 +4234,34 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>910</v>
+        <v>1040</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>342</v>
+        <v>396</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>312</v>
+        <v>412</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1745</v>
+        <v>1550</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>351</v>
+        <v>411</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>612</v>
+        <v>636</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>191.8</v>
+        <v>149</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>835</v>
+        <v>510</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>7.7</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="68">
@@ -4318,34 +4318,34 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>525</v>
+        <v>700</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>257</v>
+        <v>344</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>885</v>
+        <v>770</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>205</v>
+        <v>300</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>182</v>
+        <v>231</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>168.6</v>
+        <v>110</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>360</v>
+        <v>70</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="70">
@@ -4360,34 +4360,34 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>425</v>
+        <v>530</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>259</v>
+        <v>343</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>435</v>
+        <v>660</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>181</v>
+        <v>320</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>102.4</v>
+        <v>124.5</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="71">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전년 2025-06 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-07 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>5343</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>29379</v>
+        <v>29082</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5662</v>
+        <v>5743</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>104.6</v>
+        <v>103.5</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>90.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>5752.5</v>
+        <v>5832.1</v>
       </c>
     </row>
     <row r="4">
@@ -584,13 +584,13 @@
         <v>1421</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5064</v>
+        <v>5065</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1319</v>
+        <v>1398</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>91.7</v>
@@ -599,7 +599,7 @@
         <v>15.9</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1334.9</v>
+        <v>1413.9</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>1130</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3091</v>
+        <v>2795</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1147</v>
+        <v>1041</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>101.8</v>
+        <v>92</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1155.9</v>
+        <v>1049.2</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>2399</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7475</v>
+        <v>7266</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2401</v>
+        <v>2412</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>97.7</v>
+        <v>95</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2410.8</v>
+        <v>2421.6</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>1241</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3453</v>
+        <v>3363</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1266</v>
+        <v>1248</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1270</v>
+        <v>1251.6</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>517</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3429</v>
+        <v>3441</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>95.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>1.1</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>518.1</v>
+        <v>526.1</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>6796</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>29231</v>
+        <v>29487</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6824</v>
+        <v>7000</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>100.5</v>
+        <v>101.4</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6911.9</v>
+        <v>7093.9</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>3214</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14561</v>
+        <v>14565</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3222</v>
+        <v>3269</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>98.5</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>60.9</v>
+        <v>63.4</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3282.9</v>
+        <v>3332.4</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>5037</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>21332</v>
+        <v>21333</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5048</v>
+        <v>5077</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>100.2</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>125.4</v>
+        <v>125.5</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5173.4</v>
+        <v>5202.5</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>2770</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>19170</v>
+        <v>18380</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2724</v>
+        <v>2638</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>106</v>
+        <v>101.7</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>138.3</v>
+        <v>128.6</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2862.3</v>
+        <v>2766.6</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2705</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>10785</v>
+        <v>11365</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2781</v>
+        <v>3011</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>101</v>
+        <v>106.5</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>36.8</v>
+        <v>44.6</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2817.8</v>
+        <v>3055.6</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>928</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4613</v>
+        <v>4678</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>855</v>
+        <v>880</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>87.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12.9</v>
+        <v>13.3</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>867.9</v>
+        <v>893.3</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>2188</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>11131</v>
+        <v>11141</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2201</v>
+        <v>2290</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>161.1</v>
+        <v>163.3</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2362.1</v>
+        <v>2453.3</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>2244</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>11885</v>
+        <v>11975</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2289</v>
+        <v>2350</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>98.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>177.9</v>
+        <v>188.9</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2466.9</v>
+        <v>2538.9</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1570</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5160</v>
+        <v>4926</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1511</v>
+        <v>1455</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>95.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>160.1</v>
+        <v>151.2</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1671.1</v>
+        <v>1606.2</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>3120</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12410</v>
+        <v>12194</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3132</v>
+        <v>3156</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>98.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3236</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>3531</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>14275</v>
+        <v>14015</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3533</v>
+        <v>3566</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>92</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>53.8</v>
+        <v>54.5</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3586.8</v>
+        <v>3620.5</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>1984</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>10162</v>
+        <v>9846</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2002</v>
+        <v>1992</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>97.2</v>
+        <v>94.2</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>24.5</v>
+        <v>23.4</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2026.5</v>
+        <v>2015.4</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1432</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>6208</v>
+        <v>5918</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1461</v>
+        <v>1358</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>100.9</v>
+        <v>96.2</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24.1</v>
+        <v>22.2</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1485.1</v>
+        <v>1380.2</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2221</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17450</v>
+        <v>17590</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2366</v>
+        <v>2355</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>102.6</v>
+        <v>103.4</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>152.2</v>
+        <v>152.1</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2518.2</v>
+        <v>2507.1</v>
       </c>
     </row>
     <row r="23">
@@ -1233,19 +1233,19 @@
         <v>5644</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>767</v>
+        <v>784</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>97</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>112.2</v>
+        <v>111.8</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>879.2</v>
+        <v>895.8</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>4414</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>11940</v>
+        <v>11830</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>4396</v>
+        <v>4329</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>95.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4421.4</v>
+        <v>4354.9</v>
       </c>
     </row>
     <row r="25">
@@ -1301,19 +1301,19 @@
         <v>2521</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>811</v>
+        <v>830</v>
       </c>
       <c r="H25" s="4" t="n">
         <v>109.4</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>828.1</v>
+        <v>847.6</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>58235</v>
+        <v>58707</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1604.8</v>
+        <v>1612.7</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>59839.8</v>
+        <v>60319.7</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>12051</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>51891</v>
+        <v>51012</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>12312</v>
+        <v>12366</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>100.9</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>20758</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>97946</v>
+        <v>97427</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>20831</v>
+        <v>21101</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>101</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5637</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>33820</v>
+        <v>33354</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5828</v>
+        <v>5706</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>100.6</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>19224</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>76712</v>
+        <v>76627</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>19263</v>
+        <v>19530</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1555,25 +1555,25 @@
         <v>1690</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1853</v>
+        <v>1904</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>108</v>
+        <v>109.1</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>76.90000000000001</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="4">
@@ -1597,25 +1597,25 @@
         <v>599</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>92.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5">
@@ -1639,25 +1639,25 @@
         <v>44</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>145</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-150</v>
+        <v>-200</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>37.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
@@ -1684,10 +1684,10 @@
         <v>1650</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>454</v>
+        <v>516</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>80.5</v>
@@ -1726,10 +1726,10 @@
         <v>810</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>94.2</v>
@@ -1810,10 +1810,10 @@
         <v>800</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>100</v>
@@ -1849,25 +1849,25 @@
         <v>324</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>770</v>
+        <v>550</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>297</v>
+        <v>216</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>93.90000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-50</v>
+        <v>-270</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11">
@@ -1936,10 +1936,10 @@
         <v>2250</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>756</v>
+        <v>788</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>108.2</v>
@@ -1975,25 +1975,25 @@
         <v>510</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>84.5</v>
+        <v>77.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-220</v>
+        <v>-320</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -2059,25 +2059,25 @@
         <v>302</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>930</v>
+        <v>850</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>116.3</v>
+        <v>106.2</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -2101,25 +2101,25 @@
         <v>235</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>382</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-150</v>
+        <v>-180</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="17">
@@ -2188,10 +2188,10 @@
         <v>400</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>100</v>
@@ -2230,10 +2230,10 @@
         <v>340</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>97.09999999999999</v>
@@ -2311,25 +2311,25 @@
         <v>1217</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4900</v>
+        <v>5500</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>270</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1323</v>
+        <v>1487</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>112.6</v>
+        <v>126.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>550</v>
+        <v>1150</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>13.6</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>66.5</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>956</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3800</v>
+        <v>3400</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1007</v>
+        <v>915</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>103.5</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>130</v>
+        <v>-270</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>5.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>20.1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -2395,19 +2395,19 @@
         <v>4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>5</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>38.2</v>
@@ -2437,25 +2437,25 @@
         <v>577</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2400</v>
+        <v>2550</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>564</v>
+        <v>580</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>99.2</v>
+        <v>105.4</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-20</v>
+        <v>130</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>19.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>46.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="25">
@@ -2479,25 +2479,25 @@
         <v>289</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>114.8</v>
+        <v>111.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="26">
@@ -2563,25 +2563,25 @@
         <v>875</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3500</v>
+        <v>3950</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>848</v>
+        <v>968</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>100</v>
+        <v>112.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>19.1</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="28">
@@ -2605,25 +2605,25 @@
         <v>690</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2750</v>
+        <v>2350</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>646</v>
+        <v>548</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>94.8</v>
+        <v>81</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>-150</v>
+        <v>-550</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>21.3</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>58.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
@@ -2689,25 +2689,25 @@
         <v>799</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3450</v>
+        <v>3300</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>653</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>81.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-800</v>
+        <v>-950</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>30.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>105.8</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>401</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2000</v>
+        <v>1670</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>379</v>
+        <v>341</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-200</v>
+        <v>-530</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>31.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="32">
@@ -2773,25 +2773,25 @@
         <v>7</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="33">
@@ -2815,25 +2815,25 @@
         <v>487</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1750</v>
+        <v>2110</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>520</v>
+        <v>647</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>104.8</v>
+        <v>126.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>80</v>
+        <v>440</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>33.7</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>326</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>900</v>
+        <v>1130</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>261</v>
+        <v>338</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>80</v>
+        <v>100.4</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>-225</v>
+        <v>5</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>210</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>197</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>90.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-115</v>
+        <v>-65</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="37">
@@ -2983,25 +2983,25 @@
         <v>112</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>103.3</v>
+        <v>105</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="38">
@@ -3067,25 +3067,25 @@
         <v>549</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2900</v>
+        <v>2950</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>600</v>
+        <v>634</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>105.5</v>
+        <v>107.3</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>127.2</v>
+        <v>129.4</v>
       </c>
     </row>
     <row r="40">
@@ -3112,10 +3112,10 @@
         <v>1400</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>100</v>
@@ -3193,25 +3193,25 @@
         <v>439</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2400</v>
+        <v>2550</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>456</v>
+        <v>505</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>109.1</v>
+        <v>115.9</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>64</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>153.5</v>
+        <v>163.1</v>
       </c>
     </row>
     <row r="43">
@@ -3235,25 +3235,25 @@
         <v>299</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1350</v>
+        <v>1430</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>84.40000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>-250</v>
+        <v>-170</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>18</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>24.3</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="44">
@@ -3319,25 +3319,25 @@
         <v>177</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>176.1</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>96.8</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46">
@@ -3364,10 +3364,10 @@
         <v>800</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>100</v>
@@ -3403,10 +3403,10 @@
         <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>8</v>
@@ -3415,13 +3415,13 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48">
@@ -3445,25 +3445,25 @@
         <v>565</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1950</v>
+        <v>2200</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>546</v>
+        <v>623</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>88.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-250</v>
+        <v>0</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>62.2</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>372</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>490</v>
+        <v>417</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>23.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>41.8</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>804</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>3120</v>
+        <v>3250</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>785</v>
+        <v>849</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-330</v>
+        <v>-200</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>35.7</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="52">
@@ -3613,25 +3613,25 @@
         <v>627</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2450</v>
+        <v>2350</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>87.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>-350</v>
+        <v>-450</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>7.4</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="53">
@@ -3697,25 +3697,25 @@
         <v>211</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1250</v>
+        <v>1150</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>113.6</v>
+        <v>104.5</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="55">
@@ -3739,25 +3739,25 @@
         <v>433</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>104.5</v>
+        <v>102.3</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="56">
@@ -3823,25 +3823,25 @@
         <v>151</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>250</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>94.8</v>
+        <v>86.2</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-30</v>
+        <v>-80</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>25.9</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>14.2</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="58">
@@ -3865,25 +3865,25 @@
         <v>169</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>123.2</v>
+        <v>115.9</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>11.6</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -3991,25 +3991,25 @@
         <v>495</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2700</v>
+        <v>2640</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -4036,10 +4036,10 @@
         <v>3700</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>102.8</v>
@@ -4075,25 +4075,25 @@
         <v>104</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>570</v>
+        <v>500</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-280</v>
+        <v>-350</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>46.4</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="64">
@@ -4117,25 +4117,25 @@
         <v>151</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>95.8</v>
+        <v>91.7</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>31.3</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>36</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="65">
@@ -4159,25 +4159,25 @@
         <v>47</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>986</v>
+        <v>1214</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>164.3</v>
+        <v>202.3</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>386</v>
+        <v>614</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>29.8</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="66">
@@ -4201,25 +4201,25 @@
         <v>750</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2100</v>
+        <v>2340</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>844</v>
+        <v>948</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>108.8</v>
+        <v>121.2</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>170</v>
+        <v>410</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="67">
@@ -4246,10 +4246,10 @@
         <v>1550</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="I67" s="4" t="n">
         <v>149</v>
@@ -4327,25 +4327,25 @@
         <v>240</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>770</v>
+        <v>810</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="I69" s="4" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="J69" s="3" t="n">
         <v>110</v>
-      </c>
-      <c r="J69" s="3" t="n">
-        <v>70</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>182</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="G70" s="3" t="n">
         <v>320</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>124.5</v>
+        <v>122.6</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.06.30.pdf</t>
+          <t>Revenue Meeting_2026.07.07.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01T08:17:56.353316Z</t>
+          <t>2026-07-08T08:43:55.128456Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.06.30</t>
+          <t>2026.07.07</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>5343</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>29082</v>
+        <v>29200</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5743</v>
+        <v>5864</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>103.5</v>
+        <v>103.9</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>89.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>5832.1</v>
+        <v>5956.9</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>1421</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5065</v>
+        <v>4695</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1398</v>
+        <v>1359</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>91.7</v>
+        <v>85</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1413.9</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>1130</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2795</v>
+        <v>2729</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1041</v>
+        <v>1019</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>92</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1049.2</v>
+        <v>1026.9</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>2399</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7266</v>
+        <v>7033</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2412</v>
+        <v>2354</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>95</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2421.6</v>
+        <v>2363.3</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>1241</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3363</v>
+        <v>3369</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1248</v>
+        <v>1276</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>96.3</v>
+        <v>96.5</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1251.6</v>
+        <v>1279.9</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>517</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3441</v>
+        <v>3323</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>152</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>95.5</v>
+        <v>92.2</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>526.1</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>6796</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>29487</v>
+        <v>29211</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>237</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>7000</v>
+        <v>6919</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>101.4</v>
+        <v>100.5</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>93.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7093.9</v>
+        <v>7011.2</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>3214</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14565</v>
+        <v>14327</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>224</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3269</v>
+        <v>3216</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>98.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>63.4</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3332.4</v>
+        <v>3279.4</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>5037</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>21333</v>
+        <v>21351</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5077</v>
+        <v>5093</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>100.2</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>125.5</v>
+        <v>126.6</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5202.5</v>
+        <v>5219.6</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>2770</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>18380</v>
+        <v>17690</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2638</v>
+        <v>2550</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>101.7</v>
+        <v>97.8</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>128.6</v>
+        <v>119.1</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2766.6</v>
+        <v>2669.1</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2705</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>11365</v>
+        <v>11540</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3011</v>
+        <v>3085</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>106.5</v>
+        <v>108.1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>44.6</v>
+        <v>48.3</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3055.6</v>
+        <v>3133.3</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>928</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4678</v>
+        <v>4680</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>13.3</v>
+        <v>14</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>893.3</v>
+        <v>908</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>2188</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>11141</v>
+        <v>10895</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2290</v>
+        <v>2253</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>163.3</v>
+        <v>161.1</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2453.3</v>
+        <v>2414.1</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>2244</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>11975</v>
+        <v>11906</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>188.9</v>
+        <v>194.8</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2538.9</v>
+        <v>2546.8</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1570</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4926</v>
+        <v>4802</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>295</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1455</v>
+        <v>1418</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>91.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>151.2</v>
+        <v>138.9</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1606.2</v>
+        <v>1556.9</v>
       </c>
     </row>
     <row r="18">
@@ -1066,16 +1066,16 @@
         <v>259</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3156</v>
+        <v>3161</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>96.7</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>105</v>
+        <v>108.9</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3261</v>
+        <v>3269.9</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>3531</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>14015</v>
+        <v>13370</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3566</v>
+        <v>3416</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>90.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>54.5</v>
+        <v>50.7</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3620.5</v>
+        <v>3466.7</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>1984</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9846</v>
+        <v>9606</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1992</v>
+        <v>1962</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>94.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>23.4</v>
+        <v>22.5</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2015.4</v>
+        <v>1984.5</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1432</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5918</v>
+        <v>5671</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1358</v>
+        <v>1320</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>96.2</v>
+        <v>92.2</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1380.2</v>
+        <v>1342.7</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2221</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17590</v>
+        <v>17800</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2355</v>
+        <v>2368</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>103.4</v>
+        <v>104.6</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>152.1</v>
+        <v>152.6</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2507.1</v>
+        <v>2520.6</v>
       </c>
     </row>
     <row r="23">
@@ -1233,19 +1233,19 @@
         <v>5644</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>784</v>
+        <v>805</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>97</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>111.8</v>
+        <v>111.1</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>895.8</v>
+        <v>916.1</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>4414</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>11830</v>
+        <v>11535</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>4329</v>
+        <v>4243</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>94.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>25.9</v>
+        <v>27.5</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4354.9</v>
+        <v>4270.5</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>754</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>109.4</v>
+        <v>109.5</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>847.6</v>
+        <v>854.5</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>58707</v>
+        <v>58269</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1612.7</v>
+        <v>1601.9</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>60319.7</v>
+        <v>59870.9</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>12051</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>51012</v>
+        <v>50349</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>12366</v>
+        <v>12376</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>99.2</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>20758</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>97427</v>
+        <v>95999</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>217</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>21101</v>
+        <v>20867</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>100.4</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5637</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>33354</v>
+        <v>33077</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>171</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5706</v>
+        <v>5651</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>99.2</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>19224</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>76627</v>
+        <v>75671</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>19530</v>
+        <v>19376</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>95.90000000000001</v>
+        <v>94.7</v>
       </c>
     </row>
   </sheetData>
@@ -1555,25 +1555,25 @@
         <v>1690</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>9600</v>
+        <v>10200</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1904</v>
+        <v>2091</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>109.1</v>
+        <v>115.9</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>800</v>
+        <v>1400</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>77.7</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1597,25 +1597,25 @@
         <v>599</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>88.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5">
@@ -1639,25 +1639,25 @@
         <v>44</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>33.3</v>
+        <v>26.7</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-200</v>
+        <v>-220</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>37.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1681,25 +1681,25 @@
         <v>521</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1650</v>
+        <v>1530</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>80.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-400</v>
+        <v>-520</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>13.4</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="7">
@@ -1723,25 +1723,25 @@
         <v>242</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>810</v>
+        <v>720</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>290</v>
+        <v>329</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>94.2</v>
+        <v>83.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-50</v>
+        <v>-140</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -1765,25 +1765,25 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>37.5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9">
@@ -1807,25 +1807,25 @@
         <v>302</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="10">
@@ -1849,25 +1849,25 @@
         <v>324</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>61</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-270</v>
+        <v>-320</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11">
@@ -1933,25 +1933,25 @@
         <v>692</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>788</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>108.2</v>
+        <v>105.8</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="13">
@@ -1975,25 +1975,25 @@
         <v>510</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>77.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-320</v>
+        <v>-420</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="14">
@@ -2059,25 +2059,25 @@
         <v>302</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>339</v>
+        <v>374</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>106.2</v>
+        <v>112.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -2101,25 +2101,25 @@
         <v>235</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-180</v>
+        <v>-150</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -2185,19 +2185,19 @@
         <v>71</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>1.8</v>
@@ -2227,19 +2227,19 @@
         <v>63</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>177</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-10</v>
+        <v>-40</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>1</v>
@@ -2311,25 +2311,25 @@
         <v>1217</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5500</v>
+        <v>5450</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1487</v>
+        <v>1477</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>126.4</v>
+        <v>125.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>13.6</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>956</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3400</v>
+        <v>3250</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>915</v>
+        <v>887</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>92.59999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-270</v>
+        <v>-420</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>5.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>18</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="23">
@@ -2395,25 +2395,25 @@
         <v>4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>154</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>38.2</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="24">
@@ -2443,7 +2443,7 @@
         <v>228</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>105.4</v>
@@ -2482,10 +2482,10 @@
         <v>1500</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="I25" s="4" t="n">
         <v>111.1</v>
@@ -2566,10 +2566,10 @@
         <v>3950</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="I27" s="4" t="n">
         <v>112.9</v>
@@ -2605,25 +2605,25 @@
         <v>690</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2350</v>
+        <v>2400</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>548</v>
+        <v>574</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>81</v>
+        <v>82.8</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>-550</v>
+        <v>-500</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>21.3</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
@@ -2689,25 +2689,25 @@
         <v>799</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3300</v>
+        <v>3050</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>653</v>
+        <v>637</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>77.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-950</v>
+        <v>-1200</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>30.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>101.2</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>401</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1670</v>
+        <v>1550</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>75.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-530</v>
+        <v>-650</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>26.1</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="32">
@@ -2773,25 +2773,25 @@
         <v>7</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>175</v>
+        <v>172.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="33">
@@ -2815,25 +2815,25 @@
         <v>487</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2110</v>
+        <v>2300</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>647</v>
+        <v>727</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>126.3</v>
+        <v>137.7</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>440</v>
+        <v>630</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>40.6</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>326</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1130</v>
+        <v>1150</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>100.4</v>
+        <v>102.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>210</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1100</v>
+        <v>1180</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>94.40000000000001</v>
+        <v>101.3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-65</v>
+        <v>15</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -2986,10 +2986,10 @@
         <v>630</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I37" s="4" t="n">
         <v>105</v>
@@ -3025,7 +3025,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>214</v>
@@ -3034,10 +3034,10 @@
         <v>4</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>38.8</v>
@@ -3067,25 +3067,25 @@
         <v>549</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2950</v>
+        <v>2900</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>107.3</v>
+        <v>105.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>129.4</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="40">
@@ -3193,25 +3193,25 @@
         <v>439</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2550</v>
+        <v>2650</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>115.9</v>
+        <v>120.5</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>64</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>163.1</v>
+        <v>169.5</v>
       </c>
     </row>
     <row r="43">
@@ -3235,25 +3235,25 @@
         <v>299</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1430</v>
+        <v>1400</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>89.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>-170</v>
+        <v>-200</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>18</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="44">
@@ -3319,25 +3319,25 @@
         <v>177</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>500</v>
+        <v>430</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>328</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-50</v>
+        <v>-120</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>176.1</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>88</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="46">
@@ -3364,10 +3364,10 @@
         <v>800</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>100</v>
@@ -3406,7 +3406,7 @@
         <v>60</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>8</v>
@@ -3445,25 +3445,25 @@
         <v>565</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>623</v>
+        <v>651</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>100</v>
+        <v>102.3</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>70.2</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>372</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>417</v>
+        <v>453</v>
       </c>
       <c r="I49" s="4" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="J49" s="3" t="n">
         <v>100</v>
-      </c>
-      <c r="J49" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>23.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>34.9</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>804</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>3250</v>
+        <v>3120</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>849</v>
+        <v>830</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>94.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-200</v>
+        <v>-330</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>37.2</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="52">
@@ -3613,25 +3613,25 @@
         <v>627</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2350</v>
+        <v>2030</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>609</v>
+        <v>530</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>83.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>-450</v>
+        <v>-770</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>7.4</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>17.3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
@@ -3700,10 +3700,10 @@
         <v>1150</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="I54" s="4" t="n">
         <v>104.5</v>
@@ -3739,25 +3739,25 @@
         <v>433</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>102.3</v>
+        <v>95.5</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="56">
@@ -3823,25 +3823,25 @@
         <v>151</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>86.2</v>
+        <v>89.7</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>25.9</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="58">
@@ -3868,10 +3868,10 @@
         <v>800</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>115.9</v>
@@ -3949,25 +3949,25 @@
         <v>192</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>220</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>81</v>
+        <v>85.7</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-200</v>
+        <v>-150</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -3991,25 +3991,25 @@
         <v>495</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2640</v>
+        <v>2600</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>97.8</v>
+        <v>96.3</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-60</v>
+        <v>-100</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="62">
@@ -4039,7 +4039,7 @@
         <v>89</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>102.8</v>
@@ -4078,10 +4078,10 @@
         <v>500</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I63" s="4" t="n">
         <v>58.8</v>
@@ -4120,10 +4120,10 @@
         <v>1100</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="I64" s="4" t="n">
         <v>91.7</v>
@@ -4159,25 +4159,25 @@
         <v>47</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1214</v>
+        <v>1191</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>202.3</v>
+        <v>198.5</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>614</v>
+        <v>591</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>36.7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66">
@@ -4201,25 +4201,25 @@
         <v>750</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2340</v>
+        <v>2470</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>948</v>
+        <v>1008</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>121.2</v>
+        <v>128</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>410</v>
+        <v>540</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="67">
@@ -4243,25 +4243,25 @@
         <v>412</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1550</v>
+        <v>1650</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>632</v>
+        <v>670</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>149</v>
+        <v>158.7</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>510</v>
+        <v>610</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>14</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>21.6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68">
@@ -4327,25 +4327,25 @@
         <v>240</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>115.7</v>
+        <v>117.9</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>182</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>650</v>
+        <v>620</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>122.6</v>
+        <v>117</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.07.07.pdf</t>
+          <t>Revenue Meeting_2026.07.14.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-08T08:43:55.128456Z</t>
+          <t>2026-07-15T10:20:11.719541Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.07.07</t>
+          <t>2026.07.14</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>5343</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>29200</v>
+        <v>28784</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5864</v>
+        <v>5843</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>103.9</v>
+        <v>102.4</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>92.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>5956.9</v>
+        <v>5934.8</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>1421</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4695</v>
+        <v>4423</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>289</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1359</v>
+        <v>1277</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>85</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1374</v>
+        <v>1290.5</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>1130</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2729</v>
+        <v>2630</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1019</v>
+        <v>1005</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>89.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1026.9</v>
+        <v>1012.4</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>2399</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7033</v>
+        <v>6773</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2354</v>
+        <v>2245</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>91.90000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2363.3</v>
+        <v>2253.4</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>1241</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3369</v>
+        <v>3146</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>379</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1276</v>
+        <v>1193</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>96.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1279.9</v>
+        <v>1196.5</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>517</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3323</v>
+        <v>3203</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>505</v>
+        <v>484</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>92.2</v>
+        <v>88.8</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>506</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>6796</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>29211</v>
+        <v>29107</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6919</v>
+        <v>6976</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>100.5</v>
+        <v>100.1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>92.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7011.2</v>
+        <v>7069.4</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>3214</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14327</v>
+        <v>14150</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>3216</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>96.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>63.4</v>
+        <v>62.1</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3279.4</v>
+        <v>3278.1</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>5037</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>21351</v>
+        <v>21303</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>239</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5093</v>
+        <v>5086</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>126.6</v>
+        <v>127.5</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5219.6</v>
+        <v>5213.5</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>2770</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>17690</v>
+        <v>17140</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2550</v>
+        <v>2432</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>97.8</v>
+        <v>94.8</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>119.1</v>
+        <v>109.1</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2669.1</v>
+        <v>2541.1</v>
       </c>
     </row>
     <row r="13">
@@ -893,19 +893,19 @@
         <v>11540</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3085</v>
+        <v>3107</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>108.1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>48.3</v>
+        <v>49.4</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3133.3</v>
+        <v>3156.4</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>928</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4680</v>
+        <v>4450</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>894</v>
+        <v>846</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>88.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>908</v>
+        <v>859.1</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>2188</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>10895</v>
+        <v>10818</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2253</v>
+        <v>2260</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>95</v>
+        <v>94.3</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>161.1</v>
+        <v>166.6</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2414.1</v>
+        <v>2426.6</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>2244</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>11906</v>
+        <v>11761</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2352</v>
+        <v>2339</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>194.8</v>
+        <v>196</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2546.8</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1570</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4802</v>
+        <v>4650</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>295</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1418</v>
+        <v>1371</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>88.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>138.9</v>
+        <v>126.2</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1556.9</v>
+        <v>1497.2</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>3120</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12194</v>
+        <v>12054</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3161</v>
+        <v>3147</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>108.9</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3269.9</v>
+        <v>3255.9</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>3531</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>13370</v>
+        <v>12610</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3416</v>
+        <v>3247</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>86.2</v>
+        <v>81.3</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>50.7</v>
+        <v>46.3</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3466.7</v>
+        <v>3293.3</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>1984</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9606</v>
+        <v>9553</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>91.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>22.5</v>
+        <v>21.4</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1984.5</v>
+        <v>1985.4</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1432</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5671</v>
+        <v>5464</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1320</v>
+        <v>1255</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>92.2</v>
+        <v>88.8</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>22.7</v>
+        <v>19.5</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1342.7</v>
+        <v>1274.5</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2221</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17800</v>
+        <v>17900</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>133</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2368</v>
+        <v>2385</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>104.6</v>
+        <v>105.2</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>152.6</v>
+        <v>152.4</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2520.6</v>
+        <v>2537.4</v>
       </c>
     </row>
     <row r="23">
@@ -1230,22 +1230,22 @@
         <v>711</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5644</v>
+        <v>5494</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>97</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>111.1</v>
+        <v>107.4</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>916.1</v>
+        <v>899.4</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>4414</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>11535</v>
+        <v>11186</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>4243</v>
+        <v>4083</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>92.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>27.5</v>
+        <v>28.6</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4270.5</v>
+        <v>4111.6</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>754</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2525</v>
+        <v>2475</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>332</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>837</v>
+        <v>821</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>109.5</v>
+        <v>107.4</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>17.5</v>
+        <v>16.8</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>854.5</v>
+        <v>837.8</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>58269</v>
+        <v>57374</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1601.9</v>
+        <v>1570.3</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>59870.9</v>
+        <v>58944.3</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>12051</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>50349</v>
+        <v>48959</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>246</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>12376</v>
+        <v>12046</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>97.90000000000001</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>20758</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>95999</v>
+        <v>94993</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>20867</v>
+        <v>20791</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>98.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5637</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>33077</v>
+        <v>32917</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5651</v>
+        <v>5604</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>98.40000000000001</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>19224</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>75671</v>
+        <v>73745</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>19376</v>
+        <v>18932</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>94.7</v>
+        <v>92.3</v>
       </c>
     </row>
   </sheetData>
@@ -1558,10 +1558,10 @@
         <v>10200</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2091</v>
+        <v>2142</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>115.9</v>
@@ -1597,25 +1597,25 @@
         <v>599</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2300</v>
+        <v>2020</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>564</v>
+        <v>515</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>85.2</v>
+        <v>74.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-400</v>
+        <v>-680</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5">
@@ -1639,25 +1639,25 @@
         <v>44</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>26.7</v>
+        <v>24.3</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-220</v>
+        <v>-227</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>37.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -1681,25 +1681,25 @@
         <v>521</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1530</v>
+        <v>1400</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>508</v>
+        <v>473</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-520</v>
+        <v>-650</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>12.4</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="7">
@@ -1723,25 +1723,25 @@
         <v>242</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>720</v>
+        <v>590</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>83.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-140</v>
+        <v>-270</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="8">
@@ -1807,25 +1807,25 @@
         <v>302</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>780</v>
+        <v>715</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>97.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-20</v>
+        <v>-85</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="10">
@@ -1852,10 +1852,10 @@
         <v>500</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>61</v>
@@ -1933,25 +1933,25 @@
         <v>692</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>788</v>
+        <v>714</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>105.8</v>
+        <v>96.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>120</v>
+        <v>-80</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="13">
@@ -1975,25 +1975,25 @@
         <v>510</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>70.40000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-420</v>
+        <v>-520</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="14">
@@ -2059,25 +2059,25 @@
         <v>302</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>900</v>
+        <v>820</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>112.5</v>
+        <v>102.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -2101,25 +2101,25 @@
         <v>235</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>75</v>
+        <v>63.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-150</v>
+        <v>-220</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17">
@@ -2185,19 +2185,19 @@
         <v>71</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>1.8</v>
@@ -2227,19 +2227,19 @@
         <v>63</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>177</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>88.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>1</v>
@@ -2311,25 +2311,25 @@
         <v>1217</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5450</v>
+        <v>5500</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1477</v>
+        <v>1537</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>125.3</v>
+        <v>126.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>13.6</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>73.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>956</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3250</v>
+        <v>3350</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>887</v>
+        <v>976</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>88.59999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-420</v>
+        <v>-320</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>5.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>17.2</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="23">
@@ -2437,25 +2437,25 @@
         <v>577</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2550</v>
+        <v>2475</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>105.4</v>
+        <v>102.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>19.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>49.7</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="25">
@@ -2479,25 +2479,25 @@
         <v>289</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1500</v>
+        <v>1514</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>111.1</v>
+        <v>112.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="26">
@@ -2563,25 +2563,25 @@
         <v>875</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3950</v>
+        <v>4000</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>972</v>
+        <v>1010</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>112.9</v>
+        <v>114.3</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>19.1</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>75.5</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="28">
@@ -2608,10 +2608,10 @@
         <v>2400</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>82.8</v>
@@ -2689,25 +2689,25 @@
         <v>799</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3050</v>
+        <v>2800</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>637</v>
+        <v>603</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>71.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1200</v>
+        <v>-1450</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>30.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>93.5</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>401</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1550</v>
+        <v>1400</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>338</v>
+        <v>312</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>70.5</v>
+        <v>63.6</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-650</v>
+        <v>-800</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>24.2</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="32">
@@ -2815,25 +2815,25 @@
         <v>487</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2300</v>
+        <v>2350</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>727</v>
+        <v>764</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>137.7</v>
+        <v>140.7</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>44.2</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>326</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>102.2</v>
+        <v>106.7</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>210</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1180</v>
+        <v>1090</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>101.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>15</v>
+        <v>-75</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2983,25 +2983,25 @@
         <v>112</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>630</v>
+        <v>580</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>105</v>
+        <v>96.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>30</v>
+        <v>-20</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -3025,25 +3025,25 @@
         <v>4</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>4</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>38.8</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="39">
@@ -3067,25 +3067,25 @@
         <v>549</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2900</v>
+        <v>3060</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>632</v>
+        <v>687</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>105.5</v>
+        <v>111.3</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>150</v>
+        <v>310</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>127.2</v>
+        <v>134.2</v>
       </c>
     </row>
     <row r="40">
@@ -3109,25 +3109,25 @@
         <v>277</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1400</v>
+        <v>1334</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>-66</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>32.7</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="41">
@@ -3193,25 +3193,25 @@
         <v>439</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2650</v>
+        <v>2670</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>542</v>
+        <v>564</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>120.5</v>
+        <v>121.4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>64</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>169.5</v>
+        <v>170.8</v>
       </c>
     </row>
     <row r="43">
@@ -3238,10 +3238,10 @@
         <v>1400</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="I43" s="4" t="n">
         <v>87.5</v>
@@ -3319,25 +3319,25 @@
         <v>177</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>78.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-120</v>
+        <v>-170</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>176.1</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>75.7</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -3361,25 +3361,25 @@
         <v>258</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>78.3</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>62.7</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="47">
@@ -3448,10 +3448,10 @@
         <v>2250</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>651</v>
+        <v>675</v>
       </c>
       <c r="I48" s="4" t="n">
         <v>102.3</v>
@@ -3490,10 +3490,10 @@
         <v>1600</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="I49" s="4" t="n">
         <v>106.7</v>
@@ -3571,25 +3571,25 @@
         <v>804</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>3120</v>
+        <v>2800</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>830</v>
+        <v>763</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>90.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-330</v>
+        <v>-650</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>35.7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52">
@@ -3613,25 +3613,25 @@
         <v>627</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2030</v>
+        <v>1930</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>530</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>72.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>-770</v>
+        <v>-870</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>7.4</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>15</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="53">
@@ -3697,25 +3697,25 @@
         <v>211</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1150</v>
+        <v>1000</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>104.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="55">
@@ -3739,25 +3739,25 @@
         <v>433</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>2100</v>
+        <v>2150</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>424</v>
+        <v>455</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>95.5</v>
+        <v>97.7</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56">
@@ -3823,25 +3823,25 @@
         <v>151</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>89.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-60</v>
+        <v>-130</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>25.9</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>13.5</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="58">
@@ -3865,25 +3865,25 @@
         <v>169</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>800</v>
+        <v>680</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>115.9</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>110</v>
+        <v>-10</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>11.6</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="59">
@@ -3949,25 +3949,25 @@
         <v>192</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>900</v>
+        <v>970</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>85.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-150</v>
+        <v>-80</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="61">
@@ -3991,25 +3991,25 @@
         <v>495</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>96.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="62">
@@ -4033,25 +4033,25 @@
         <v>331</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>3700</v>
+        <v>3680</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>89</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>102.8</v>
+        <v>102.2</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>37.3</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>138</v>
+        <v>137.3</v>
       </c>
     </row>
     <row r="63">
@@ -4078,10 +4078,10 @@
         <v>500</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I63" s="4" t="n">
         <v>58.8</v>
@@ -4117,25 +4117,25 @@
         <v>151</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>91.7</v>
+        <v>83.3</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>31.3</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>34.4</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="65">
@@ -4159,25 +4159,25 @@
         <v>47</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1191</v>
+        <v>1171</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>82</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>198.5</v>
+        <v>195.2</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>591</v>
+        <v>571</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>36</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="66">
@@ -4201,25 +4201,25 @@
         <v>750</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2470</v>
+        <v>2300</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>408</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>1008</v>
+        <v>939</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>128</v>
+        <v>119.2</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>540</v>
+        <v>370</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="67">
@@ -4243,25 +4243,25 @@
         <v>412</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1650</v>
+        <v>1750</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>670</v>
+        <v>715</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>158.7</v>
+        <v>168.3</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>610</v>
+        <v>710</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>14</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>23</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="68">
@@ -4327,25 +4327,25 @@
         <v>240</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>825</v>
+        <v>790</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>316</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>117.9</v>
+        <v>112.9</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>182</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>620</v>
+        <v>595</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>117</v>
+        <v>112.3</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.07.14.pdf</t>
+          <t>Revenue Meeting_2026.07.21.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-15T10:20:11.719541Z</t>
+          <t>2026-07-22T09:47:18.996835Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.07.14</t>
+          <t>2026.07.21</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>5343</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>28784</v>
+        <v>28654</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>203</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5843</v>
+        <v>5810</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>102.4</v>
+        <v>102</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>91.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>5934.8</v>
+        <v>5901.1</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>1421</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4423</v>
+        <v>4500</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1277</v>
+        <v>1292</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>80.09999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1290.5</v>
+        <v>1305.8</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>1130</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2630</v>
+        <v>2590</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1005</v>
+        <v>980</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1012.4</v>
+        <v>987.1</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>2399</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>6773</v>
+        <v>6635</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2245</v>
+        <v>2163</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>88.5</v>
+        <v>86.7</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2253.4</v>
+        <v>2170.9</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>1241</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3146</v>
+        <v>3123</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1193</v>
+        <v>1172</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>90.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1196.5</v>
+        <v>1175.4</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>517</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3203</v>
+        <v>3034</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>484</v>
+        <v>455</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>88.8</v>
+        <v>84.2</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>485</v>
+        <v>455.8</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>6796</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>29107</v>
+        <v>28671</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6976</v>
+        <v>6897</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>100.1</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7069.4</v>
+        <v>6986.2</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>3214</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14150</v>
+        <v>14057</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3216</v>
+        <v>3184</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>95.7</v>
+        <v>95</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>62.1</v>
+        <v>60.7</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3278.1</v>
+        <v>3244.7</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>5037</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>21303</v>
+        <v>21219</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>239</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5086</v>
+        <v>5076</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>127.5</v>
+        <v>124.5</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5213.5</v>
+        <v>5200.5</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>2770</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>17140</v>
+        <v>16845</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2432</v>
+        <v>2403</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>94.8</v>
+        <v>93.2</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>109.1</v>
+        <v>106.7</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2541.1</v>
+        <v>2509.7</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2705</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>11540</v>
+        <v>11528</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3107</v>
+        <v>3115</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>49.4</v>
+        <v>50.2</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3156.4</v>
+        <v>3165.2</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>928</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4450</v>
+        <v>4290</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>846</v>
+        <v>823</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>84.09999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>859.1</v>
+        <v>835.4</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>2188</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>10818</v>
+        <v>10813</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>209</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2260</v>
+        <v>2256</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>94.3</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>166.6</v>
+        <v>164.4</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2426.6</v>
+        <v>2420.4</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>2244</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>11761</v>
+        <v>11700</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>199</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2339</v>
+        <v>2332</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>196</v>
+        <v>193.2</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2535</v>
+        <v>2525.2</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1570</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4650</v>
+        <v>4547</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1371</v>
+        <v>1350</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>126.2</v>
+        <v>117.4</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1497.2</v>
+        <v>1467.4</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>3120</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12054</v>
+        <v>12019</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3147</v>
+        <v>3145</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>95.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>108.9</v>
+        <v>107.2</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3255.9</v>
+        <v>3252.2</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>3531</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>12610</v>
+        <v>12480</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3247</v>
+        <v>3226</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>81.3</v>
+        <v>80.5</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>46.3</v>
+        <v>45.3</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3293.3</v>
+        <v>3271.3</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>1984</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9553</v>
+        <v>9632</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1964</v>
+        <v>2011</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>91.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1985.4</v>
+        <v>2032.7</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1432</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5464</v>
+        <v>5483</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1255</v>
+        <v>1267</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>88.8</v>
+        <v>89.2</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1274.5</v>
+        <v>1286.7</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2221</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17900</v>
+        <v>17722</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2385</v>
+        <v>2342</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>105.2</v>
+        <v>104.2</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>152.4</v>
+        <v>151.9</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2537.4</v>
+        <v>2493.9</v>
       </c>
     </row>
     <row r="23">
@@ -1230,22 +1230,22 @@
         <v>711</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5494</v>
+        <v>5505</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>107.4</v>
+        <v>103.9</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>899.4</v>
+        <v>902.9</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>4414</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>11186</v>
+        <v>11168</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>4083</v>
+        <v>4059</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>89.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4111.6</v>
+        <v>4086.6</v>
       </c>
     </row>
     <row r="25">
@@ -1301,19 +1301,19 @@
         <v>2475</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H25" s="4" t="n">
         <v>107.4</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>837.8</v>
+        <v>836.5</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>57374</v>
+        <v>56977</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1570.3</v>
+        <v>1536.6</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>58944.3</v>
+        <v>58513.6</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>12051</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>48959</v>
+        <v>48536</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>12046</v>
+        <v>11873</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>95.2</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>20758</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>94993</v>
+        <v>94080</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>219</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>20791</v>
+        <v>20635</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>97.90000000000001</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5637</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>32917</v>
+        <v>32837</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5604</v>
+        <v>5620</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>19224</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>73745</v>
+        <v>73237</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>257</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>18932</v>
+        <v>18850</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>92.3</v>
+        <v>91.7</v>
       </c>
     </row>
   </sheetData>
@@ -1555,25 +1555,25 @@
         <v>1690</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>10200</v>
+        <v>10110</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>210</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2142</v>
+        <v>2119</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>115.9</v>
+        <v>114.9</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1400</v>
+        <v>1310</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>82.59999999999999</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="4">
@@ -1597,25 +1597,25 @@
         <v>599</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2020</v>
+        <v>2000</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>255</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>74.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-680</v>
+        <v>-700</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5">
@@ -1639,25 +1639,25 @@
         <v>44</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>24.3</v>
+        <v>25</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-227</v>
+        <v>-225</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>37.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="6">
@@ -1681,25 +1681,25 @@
         <v>521</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>68.3</v>
+        <v>70.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-650</v>
+        <v>-600</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="7">
@@ -1723,25 +1723,25 @@
         <v>242</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>68.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-270</v>
+        <v>-300</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
@@ -1807,25 +1807,25 @@
         <v>302</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>715</v>
+        <v>690</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>89.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-85</v>
+        <v>-110</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="10">
@@ -1849,25 +1849,25 @@
         <v>324</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>500</v>
+        <v>465</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>61</v>
+        <v>56.7</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-320</v>
+        <v>-355</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
@@ -1933,25 +1933,25 @@
         <v>692</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>714</v>
+        <v>674</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>96.2</v>
+        <v>91.3</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-80</v>
+        <v>-180</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="13">
@@ -1975,25 +1975,25 @@
         <v>510</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>900</v>
+        <v>820</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>347</v>
+        <v>313</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>63.4</v>
+        <v>57.7</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-520</v>
+        <v>-600</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="14">
@@ -2059,19 +2059,19 @@
         <v>302</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>820</v>
+        <v>795</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>102.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>3.3</v>
@@ -2101,19 +2101,19 @@
         <v>235</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>63.3</v>
+        <v>62.5</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-220</v>
+        <v>-225</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>1.9</v>
@@ -2185,25 +2185,25 @@
         <v>71</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>92.5</v>
+        <v>82.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-30</v>
+        <v>-70</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
@@ -2227,25 +2227,25 @@
         <v>63</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>300</v>
+        <v>230</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>177</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>85.7</v>
+        <v>65.7</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-50</v>
+        <v>-120</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20">
@@ -2311,25 +2311,25 @@
         <v>1217</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5500</v>
+        <v>5255</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1537</v>
+        <v>1475</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>126.4</v>
+        <v>120.8</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1150</v>
+        <v>905</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>13.6</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>956</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3350</v>
+        <v>3175</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>976</v>
+        <v>940</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>91.3</v>
+        <v>86.5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-320</v>
+        <v>-495</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>5.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>17.7</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="23">
@@ -2437,25 +2437,25 @@
         <v>577</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2475</v>
+        <v>2436</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>583</v>
+        <v>568</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>102.3</v>
+        <v>100.7</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>19.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>48.2</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="25">
@@ -2479,25 +2479,25 @@
         <v>289</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1514</v>
+        <v>1448</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>112.1</v>
+        <v>107.3</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="26">
@@ -2563,25 +2563,25 @@
         <v>875</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4000</v>
+        <v>3886</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1010</v>
+        <v>980</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>114.3</v>
+        <v>111</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>500</v>
+        <v>386</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>19.1</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>76.5</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="28">
@@ -2605,25 +2605,25 @@
         <v>690</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2400</v>
+        <v>2360</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>243</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>82.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>-500</v>
+        <v>-540</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>21.3</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>51</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="29">
@@ -2689,25 +2689,25 @@
         <v>799</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2800</v>
+        <v>2788</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>603</v>
+        <v>618</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1450</v>
+        <v>-1462</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>30.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>85.8</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>401</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1400</v>
+        <v>1275</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>63.6</v>
+        <v>58</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-800</v>
+        <v>-925</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>21.9</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="32">
@@ -2776,10 +2776,10 @@
         <v>138</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I32" s="4" t="n">
         <v>172.5</v>
@@ -2815,25 +2815,25 @@
         <v>487</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2350</v>
+        <v>2395</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>764</v>
+        <v>789</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>140.7</v>
+        <v>143.4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>680</v>
+        <v>725</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>326</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1200</v>
+        <v>1170</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>106.7</v>
+        <v>104</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>210</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1090</v>
+        <v>1050</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>93.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-75</v>
+        <v>-115</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
@@ -2983,25 +2983,25 @@
         <v>112</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>580</v>
+        <v>526</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>96.7</v>
+        <v>87.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>-20</v>
+        <v>-74</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="38">
@@ -3067,25 +3067,25 @@
         <v>549</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3060</v>
+        <v>3045</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>687</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>111.3</v>
+        <v>110.7</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>134.2</v>
+        <v>133.6</v>
       </c>
     </row>
     <row r="40">
@@ -3109,25 +3109,25 @@
         <v>277</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1334</v>
+        <v>1266</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>95.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-66</v>
+        <v>-134</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>31.2</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="41">
@@ -3193,25 +3193,25 @@
         <v>439</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2670</v>
+        <v>2647</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>121.4</v>
+        <v>120.3</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>470</v>
+        <v>447</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>64</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>170.8</v>
+        <v>169.3</v>
       </c>
     </row>
     <row r="43">
@@ -3235,25 +3235,25 @@
         <v>299</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1400</v>
+        <v>1323</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>87.5</v>
+        <v>82.7</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>-200</v>
+        <v>-277</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>18</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>25.2</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="44">
@@ -3319,25 +3319,25 @@
         <v>177</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>69.09999999999999</v>
+        <v>60</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-170</v>
+        <v>-220</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>176.1</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="46">
@@ -3364,10 +3364,10 @@
         <v>750</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>93.8</v>
@@ -3445,25 +3445,25 @@
         <v>565</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2250</v>
+        <v>2232</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>102.3</v>
+        <v>101.5</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>71.8</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>372</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1600</v>
+        <v>1550</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>106.7</v>
+        <v>103.3</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>23.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>37.2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>804</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2800</v>
+        <v>2760</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>273</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>81.2</v>
+        <v>80</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-650</v>
+        <v>-690</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>32</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="52">
@@ -3613,25 +3613,25 @@
         <v>627</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1930</v>
+        <v>1864</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>68.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>-870</v>
+        <v>-936</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>7.4</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="53">
@@ -3697,25 +3697,25 @@
         <v>211</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>-100</v>
+        <v>-93</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -3739,25 +3739,25 @@
         <v>433</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>2150</v>
+        <v>2180</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>97.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="56">
@@ -3826,10 +3826,10 @@
         <v>450</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I57" s="4" t="n">
         <v>77.59999999999999</v>
@@ -3865,25 +3865,25 @@
         <v>169</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>101.4</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>11.6</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="59">
@@ -3949,25 +3949,25 @@
         <v>192</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>970</v>
+        <v>845</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>92.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-80</v>
+        <v>-205</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="61">
@@ -3991,25 +3991,25 @@
         <v>495</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2500</v>
+        <v>2380</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>533</v>
+        <v>510</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>92.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-200</v>
+        <v>-320</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="62">
@@ -4033,7 +4033,7 @@
         <v>331</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>3680</v>
+        <v>3709</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>89</v>
@@ -4042,16 +4042,16 @@
         <v>329</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>102.2</v>
+        <v>103</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>37.3</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>137.3</v>
+        <v>138.3</v>
       </c>
     </row>
     <row r="63">
@@ -4075,25 +4075,25 @@
         <v>104</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>58.8</v>
+        <v>55.9</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-350</v>
+        <v>-375</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>40.7</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="64">
@@ -4117,25 +4117,25 @@
         <v>151</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>83.3</v>
+        <v>79.2</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>-200</v>
+        <v>-250</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>31.3</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>31.3</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="65">
@@ -4159,25 +4159,25 @@
         <v>47</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>82</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>195.2</v>
+        <v>195.5</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="66">
@@ -4201,19 +4201,19 @@
         <v>750</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2300</v>
+        <v>2314</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>119.2</v>
+        <v>119.9</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.8</v>
@@ -4243,25 +4243,25 @@
         <v>412</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1750</v>
+        <v>1674</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>715</v>
+        <v>675</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>168.3</v>
+        <v>161</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>710</v>
+        <v>634</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>14</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="68">
@@ -4327,25 +4327,25 @@
         <v>240</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>790</v>
+        <v>775</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>112.9</v>
+        <v>110.7</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>182</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>112.3</v>
+        <v>110.8</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.07.21.pdf</t>
+          <t>Revenue Meeting_2026.07.28.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-22T09:47:18.996835Z</t>
+          <t>2026-07-29T17:21:21.216784Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.07.21</t>
+          <t>2026.07.28</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST - 2026-07</t>
+          <t>RM FCST - 2026-08</t>
         </is>
       </c>
     </row>
@@ -541,31 +541,31 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>28100</v>
+        <v>35550</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5343</v>
+        <v>6866</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>28654</v>
+        <v>33771</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5810</v>
+        <v>7266</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>91.09999999999999</v>
+        <v>119.2</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>5901.1</v>
+        <v>7385.2</v>
       </c>
     </row>
     <row r="4">
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5525</v>
+        <v>6265</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1421</v>
+        <v>1757</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4500</v>
+        <v>5892</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>287</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1292</v>
+        <v>1689</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>81.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>13.8</v>
+        <v>23</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1305.8</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="5">
@@ -609,31 +609,31 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3037</v>
+        <v>3837</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1130</v>
+        <v>1440</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2590</v>
+        <v>3306</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>980</v>
+        <v>1303</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>85.3</v>
+        <v>86.2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7.1</v>
+        <v>11.7</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>987.1</v>
+        <v>1314.7</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7650</v>
+        <v>8955</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2399</v>
+        <v>2866</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>6635</v>
+        <v>7865</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2163</v>
+        <v>2691</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>86.7</v>
+        <v>87.8</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>7.9</v>
+        <v>15.4</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2170.9</v>
+        <v>2706.4</v>
       </c>
     </row>
     <row r="7">
@@ -677,31 +677,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3492</v>
+        <v>4382</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1241</v>
+        <v>1592</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3123</v>
+        <v>3798</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1172</v>
+        <v>1497</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>89.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1175.4</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="8">
@@ -711,31 +711,31 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3605</v>
+        <v>4010</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>517</v>
+        <v>607</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3034</v>
+        <v>3519</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>455</v>
+        <v>577</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>84.2</v>
+        <v>87.8</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>455.8</v>
+        <v>578.8</v>
       </c>
     </row>
     <row r="9">
@@ -745,31 +745,31 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>29075</v>
+        <v>32350</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6796</v>
+        <v>7888</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>28671</v>
+        <v>32458</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6897</v>
+        <v>7958</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>100.3</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>89.2</v>
+        <v>108</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6986.2</v>
+        <v>8066</v>
       </c>
     </row>
     <row r="10">
@@ -779,31 +779,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>14790</v>
+        <v>15180</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3214</v>
+        <v>3477</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14057</v>
+        <v>14888</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3184</v>
+        <v>3521</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>95</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>60.7</v>
+        <v>33.7</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3244.7</v>
+        <v>3554.7</v>
       </c>
     </row>
     <row r="11">
@@ -813,31 +813,31 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>21300</v>
+        <v>21305</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5037</v>
+        <v>5282</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>21219</v>
+        <v>21408</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5076</v>
+        <v>5337</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>99.59999999999999</v>
+        <v>100.5</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>124.5</v>
+        <v>106.5</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5200.5</v>
+        <v>5443.5</v>
       </c>
     </row>
     <row r="12">
@@ -847,31 +847,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>18080</v>
+        <v>18300</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2770</v>
+        <v>3424</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>16845</v>
+        <v>16080</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>143</v>
+        <v>202</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2403</v>
+        <v>3254</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>93.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>106.7</v>
+        <v>200.8</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2509.7</v>
+        <v>3454.8</v>
       </c>
     </row>
     <row r="13">
@@ -881,31 +881,31 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>10675</v>
+        <v>11100</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2705</v>
+        <v>2876</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>11528</v>
+        <v>11820</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3115</v>
+        <v>3234</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>108</v>
+        <v>106.5</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>50.2</v>
+        <v>49.2</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3165.2</v>
+        <v>3283.2</v>
       </c>
     </row>
     <row r="14">
@@ -915,31 +915,31 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5290</v>
+        <v>5545</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>928</v>
+        <v>1066</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4290</v>
+        <v>5278</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>823</v>
+        <v>1084</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>81.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12.4</v>
+        <v>10.7</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>835.4</v>
+        <v>1094.7</v>
       </c>
     </row>
     <row r="15">
@@ -949,31 +949,31 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>11470</v>
+        <v>12590</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2188</v>
+        <v>2548</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>10813</v>
+        <v>12074</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2256</v>
+        <v>2606</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>94.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>164.4</v>
+        <v>196</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2420.4</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="16">
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>12080</v>
+        <v>13660</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2244</v>
+        <v>2657</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>11700</v>
+        <v>13560</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2332</v>
+        <v>2723</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>96.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>193.2</v>
+        <v>207.3</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2525.2</v>
+        <v>2930.3</v>
       </c>
     </row>
     <row r="17">
@@ -1017,31 +1017,31 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5400</v>
+        <v>6190</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1570</v>
+        <v>1858</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4547</v>
+        <v>5759</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1350</v>
+        <v>1720</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>84.2</v>
+        <v>93</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>117.4</v>
+        <v>70.3</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1467.4</v>
+        <v>1790.3</v>
       </c>
     </row>
     <row r="18">
@@ -1051,31 +1051,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>12610</v>
+        <v>14120</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>3120</v>
+        <v>3700</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12019</v>
+        <v>13896</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3145</v>
+        <v>3704</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>95.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>107.2</v>
+        <v>63.3</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3252.2</v>
+        <v>3767.3</v>
       </c>
     </row>
     <row r="19">
@@ -1085,31 +1085,31 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>15510</v>
+        <v>16710</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3531</v>
+        <v>4149</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>12480</v>
+        <v>15150</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3226</v>
+        <v>4037</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>80.5</v>
+        <v>90.7</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>45.3</v>
+        <v>63</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3271.3</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="20">
@@ -1119,31 +1119,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>10450</v>
+        <v>10130</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1984</v>
+        <v>2063</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9632</v>
+        <v>9480</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2011</v>
+        <v>2096</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>92.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>21.7</v>
+        <v>13.2</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2032.7</v>
+        <v>2109.2</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>6150</v>
+        <v>6280</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1432</v>
+        <v>1549</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5483</v>
+        <v>5921</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1267</v>
+        <v>1467</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>89.2</v>
+        <v>94.3</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>19.7</v>
+        <v>29.6</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1286.7</v>
+        <v>1496.6</v>
       </c>
     </row>
     <row r="22">
@@ -1187,31 +1187,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>17010</v>
+        <v>16100</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2221</v>
+        <v>2257</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17722</v>
+        <v>15030</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2342</v>
+        <v>2329</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>104.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>151.9</v>
+        <v>136.7</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2493.9</v>
+        <v>2465.7</v>
       </c>
     </row>
     <row r="23">
@@ -1221,31 +1221,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5820</v>
+        <v>6470</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>711</v>
+        <v>884</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5505</v>
+        <v>6345</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>799</v>
+        <v>909</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>94.59999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>103.9</v>
+        <v>70.8</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>902.9</v>
+        <v>979.8</v>
       </c>
     </row>
     <row r="24">
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>12490</v>
+        <v>12300</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4414</v>
+        <v>4493</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>11168</v>
+        <v>11858</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>4059</v>
+        <v>4373</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>89.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>27.6</v>
+        <v>24.7</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4086.6</v>
+        <v>4397.7</v>
       </c>
     </row>
     <row r="25">
@@ -1289,31 +1289,31 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2305</v>
+        <v>2455</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>754</v>
+        <v>898</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2475</v>
+        <v>2430</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>820</v>
+        <v>882</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>107.4</v>
+        <v>99</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>16.5</v>
+        <v>16.9</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>836.5</v>
+        <v>898.9</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>56977</v>
+        <v>66257</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1536.6</v>
+        <v>1578.8</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>58513.6</v>
+        <v>67835.8</v>
       </c>
     </row>
     <row r="27"/>
@@ -1340,25 +1340,25 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>51409</v>
+        <v>62999</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>12051</v>
+        <v>15128</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>48536</v>
+        <v>58151</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>11873</v>
+        <v>15024</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>94.40000000000001</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="29">
@@ -1368,25 +1368,25 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>97020</v>
+        <v>102180</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>20758</v>
+        <v>23517</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>94080</v>
+        <v>99338</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>20635</v>
+        <v>23559</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>97</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="30">
@@ -1396,25 +1396,25 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>33610</v>
+        <v>32510</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>5637</v>
+        <v>5869</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>32837</v>
+        <v>30431</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5620</v>
+        <v>5892</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>97.7</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1424,25 +1424,25 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>79875</v>
+        <v>86095</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>19224</v>
+        <v>21681</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>73237</v>
+        <v>83666</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>18850</v>
+        <v>21783</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>91.7</v>
+        <v>97.2</v>
       </c>
     </row>
   </sheetData>
@@ -1468,7 +1468,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST 세그먼트별 - 2026-07</t>
+          <t>RM FCST 세그먼트별 - 2026-08</t>
         </is>
       </c>
     </row>
@@ -1546,34 +1546,34 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>8800</v>
+        <v>11500</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1690</v>
+        <v>2358</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>10110</v>
+        <v>12000</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2119</v>
+        <v>2830</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>114.9</v>
+        <v>104.3</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1310</v>
+        <v>500</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>81.8</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="4">
@@ -1588,34 +1588,34 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>599</v>
+        <v>574</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>510</v>
+        <v>738</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>74.09999999999999</v>
+        <v>107.1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-700</v>
+        <v>200</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="5">
@@ -1633,31 +1633,31 @@
         <v>300</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>163</v>
+        <v>124</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-225</v>
+        <v>-220</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>37.5</v>
+        <v>45.6</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6">
@@ -1672,34 +1672,34 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2050</v>
+        <v>2060</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>254</v>
+        <v>297</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>521</v>
+        <v>612</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1450</v>
+        <v>2200</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>487</v>
+        <v>697</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>70.7</v>
+        <v>106.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-600</v>
+        <v>140</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>11.7</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="7">
@@ -1714,34 +1714,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>860</v>
+        <v>1010</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>242</v>
+        <v>303</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>560</v>
+        <v>900</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>181</v>
+        <v>275</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-300</v>
+        <v>-110</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
@@ -1765,25 +1765,25 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>298</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>37.5</v>
+        <v>45.6</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1798,34 +1798,34 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>800</v>
+        <v>1150</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>302</v>
+        <v>424</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>690</v>
+        <v>1000</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>262</v>
+        <v>400</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>86.2</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-110</v>
+        <v>-150</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1840,34 +1840,34 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>820</v>
+        <v>950</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>324</v>
+        <v>380</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>465</v>
+        <v>650</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>56.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-355</v>
+        <v>-300</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>37.5</v>
+        <v>45.6</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -1924,34 +1924,34 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2080</v>
+        <v>2400</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>692</v>
+        <v>833</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1900</v>
+        <v>2300</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>674</v>
+        <v>856</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>91.3</v>
+        <v>95.8</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-180</v>
+        <v>-100</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -1966,34 +1966,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1420</v>
+        <v>1600</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>510</v>
+        <v>550</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>820</v>
+        <v>1250</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>313</v>
+        <v>471</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>57.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-600</v>
+        <v>-350</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="14">
@@ -2050,34 +2050,34 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>800</v>
+        <v>1150</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>302</v>
+        <v>451</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>795</v>
+        <v>1100</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>336</v>
+        <v>474</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-5</v>
+        <v>-50</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="16">
@@ -2092,34 +2092,34 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>62.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-225</v>
+        <v>-200</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="17">
@@ -2176,34 +2176,34 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>82.5</v>
+        <v>111.1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-70</v>
+        <v>50</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19">
@@ -2218,31 +2218,31 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>230</v>
+        <v>340</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>65.7</v>
+        <v>107.9</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-120</v>
+        <v>25</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="L19" s="4" t="n">
         <v>0.2</v>
@@ -2263,7 +2263,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>1</v>
@@ -2284,7 +2284,7 @@
         <v>-20</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>10.8</v>
+        <v>3.6</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>0</v>
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4350</v>
+        <v>5610</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1217</v>
+        <v>1613</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5255</v>
+        <v>6050</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1475</v>
+        <v>1709</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>120.8</v>
+        <v>107.8</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>905</v>
+        <v>440</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>71.3</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="22">
@@ -2344,34 +2344,34 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3670</v>
+        <v>3700</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>956</v>
+        <v>925</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3175</v>
+        <v>4230</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>940</v>
+        <v>1108</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>86.5</v>
+        <v>114.3</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-495</v>
+        <v>530</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5.3</v>
+        <v>7.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>16.8</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="23">
@@ -2386,34 +2386,34 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>58</v>
+        <v>190</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-21</v>
+        <v>18</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>38.2</v>
+        <v>24.8</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24">
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2420</v>
+        <v>2050</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>577</v>
+        <v>542</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2436</v>
+        <v>2050</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>100.7</v>
+        <v>100</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>19.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>47.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -2470,34 +2470,34 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1350</v>
+        <v>1200</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1448</v>
+        <v>1600</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>107.3</v>
+        <v>133.3</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>98</v>
+        <v>400</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="26">
@@ -2536,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L26" s="4" t="n">
         <v>0</v>
@@ -2554,34 +2554,34 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>875</v>
+        <v>846</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3886</v>
+        <v>3050</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>252</v>
+        <v>290</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>980</v>
+        <v>883</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>111</v>
+        <v>101.7</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>386</v>
+        <v>50</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>19.1</v>
+        <v>17.1</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>74.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="28">
@@ -2596,34 +2596,34 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2900</v>
+        <v>1400</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>690</v>
+        <v>392</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2360</v>
+        <v>1950</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>573</v>
+        <v>517</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>81.40000000000001</v>
+        <v>139.3</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>-540</v>
+        <v>550</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>21.3</v>
+        <v>27.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>50.2</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="29">
@@ -2662,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>54.5</v>
+        <v>55.9</v>
       </c>
       <c r="L29" s="4" t="n">
         <v>0</v>
@@ -2680,34 +2680,34 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4250</v>
+        <v>5150</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>799</v>
+        <v>1018</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2788</v>
+        <v>5100</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>618</v>
+        <v>1142</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>65.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1462</v>
+        <v>-50</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>85.5</v>
+        <v>155.1</v>
       </c>
     </row>
     <row r="31">
@@ -2722,34 +2722,34 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2200</v>
+        <v>3000</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>401</v>
+        <v>568</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1275</v>
+        <v>2820</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>288</v>
+        <v>606</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-925</v>
+        <v>-180</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>19.9</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="32">
@@ -2764,34 +2764,34 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>172.5</v>
+        <v>37</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>58</v>
+        <v>-63</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="33">
@@ -2806,34 +2806,34 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1670</v>
+        <v>1725</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>487</v>
+        <v>520</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2395</v>
+        <v>2300</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>329</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>789</v>
+        <v>757</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>143.4</v>
+        <v>133.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>725</v>
+        <v>575</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>46.1</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="34">
@@ -2848,34 +2848,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1125</v>
+        <v>1165</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1170</v>
+        <v>1400</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>359</v>
+        <v>441</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>104</v>
+        <v>120.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>45</v>
+        <v>235</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="35">
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1165</v>
+        <v>1175</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1050</v>
+        <v>1200</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>219</v>
+        <v>282</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>90.09999999999999</v>
+        <v>102.1</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-115</v>
+        <v>25</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="37">
@@ -2974,34 +2974,34 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>600</v>
+        <v>730</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>526</v>
+        <v>810</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>117</v>
+        <v>189</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>87.7</v>
+        <v>111</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>-74</v>
+        <v>80</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="38">
@@ -3019,31 +3019,31 @@
         <v>20</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>213</v>
+        <v>132</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>38.8</v>
+        <v>42.4</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="39">
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2750</v>
+        <v>3450</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>549</v>
+        <v>719</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3045</v>
+        <v>3500</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>687</v>
+        <v>781</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>110.7</v>
+        <v>101.4</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>295</v>
+        <v>50</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>133.6</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="40">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1266</v>
+        <v>1820</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>281</v>
+        <v>413</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>90.40000000000001</v>
+        <v>121.3</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-134</v>
+        <v>320</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>29.6</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="41">
@@ -3151,25 +3151,25 @@
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3184,34 +3184,34 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2200</v>
+        <v>2600</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>439</v>
+        <v>577</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2647</v>
+        <v>2700</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>565</v>
+        <v>612</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>120.3</v>
+        <v>103.8</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>447</v>
+        <v>100</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>64</v>
+        <v>62.5</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>169.3</v>
+        <v>168.8</v>
       </c>
     </row>
     <row r="43">
@@ -3226,34 +3226,34 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1600</v>
+        <v>1450</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1323</v>
+        <v>1500</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>82.7</v>
+        <v>103.4</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>-277</v>
+        <v>50</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>18</v>
+        <v>25.7</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>23.8</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="44">
@@ -3310,34 +3310,34 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>333</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="F45" s="3" t="n">
         <v>550</v>
       </c>
-      <c r="D45" s="3" t="n">
-        <v>321</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>177</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>330</v>
-      </c>
       <c r="G45" s="3" t="n">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-220</v>
+        <v>-200</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>176.1</v>
+        <v>79.7</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>58.1</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="46">
@@ -3352,34 +3352,34 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>258</v>
+        <v>333</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>750</v>
+        <v>1050</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>258</v>
+        <v>363</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>93.8</v>
+        <v>105</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>78.3</v>
+        <v>24.2</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>58.7</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="47">
@@ -3403,25 +3403,25 @@
         <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>34</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="48">
@@ -3436,34 +3436,34 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>565</v>
+        <v>684</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2232</v>
+        <v>2850</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>673</v>
+        <v>864</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>101.5</v>
+        <v>118.8</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>32</v>
+        <v>450</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>31.9</v>
+        <v>13.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>71.2</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="49">
@@ -3478,34 +3478,34 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>372</v>
+        <v>488</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1550</v>
+        <v>1800</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>289</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>448</v>
+        <v>520</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>103.3</v>
+        <v>102.9</v>
       </c>
       <c r="J49" s="3" t="n">
         <v>50</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>23.2</v>
+        <v>14.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>36</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="50">
@@ -3562,34 +3562,34 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3450</v>
+        <v>3300</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>233</v>
+        <v>270</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>804</v>
+        <v>891</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2760</v>
+        <v>3220</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>754</v>
+        <v>981</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>80</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-690</v>
+        <v>-80</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>31.6</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="52">
@@ -3604,34 +3604,34 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>627</v>
+        <v>680</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1864</v>
+        <v>2410</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>510</v>
+        <v>703</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>-936</v>
+        <v>-190</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>7.4</v>
+        <v>11.1</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>13.7</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="53">
@@ -3688,34 +3688,34 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>211</v>
+        <v>257</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1007</v>
+        <v>1200</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>91.5</v>
+        <v>100</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>-93</v>
+        <v>0</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>9.1</v>
+        <v>6.8</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="55">
@@ -3730,34 +3730,34 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>433</v>
+        <v>483</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>2180</v>
+        <v>1850</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-20</v>
+        <v>-450</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>12.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="56">
@@ -3781,25 +3781,25 @@
         <v>0</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>205</v>
+        <v>73</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>23.8</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="57">
@@ -3814,34 +3814,34 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>77.59999999999999</v>
+        <v>105.3</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-130</v>
+        <v>30</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>25.9</v>
+        <v>24.7</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>11.7</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="58">
@@ -3856,34 +3856,34 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>245</v>
+        <v>284</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>700</v>
+        <v>780</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>101.4</v>
+        <v>114.7</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>11.6</v>
+        <v>18.9</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>8.1</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="59">
@@ -3922,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="L59" s="4" t="n">
         <v>0</v>
@@ -3940,34 +3940,34 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1050</v>
+        <v>1700</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>192</v>
+        <v>322</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>845</v>
+        <v>1500</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>192</v>
+        <v>345</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>80.5</v>
+        <v>88.2</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-205</v>
+        <v>-200</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>10.7</v>
+        <v>14.3</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>9.1</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="61">
@@ -3982,34 +3982,34 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2380</v>
+        <v>2600</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>510</v>
+        <v>572</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>88.09999999999999</v>
+        <v>104</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-320</v>
+        <v>100</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -4024,34 +4024,34 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>92</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>331</v>
+        <v>276</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>3709</v>
+        <v>2850</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>329</v>
+        <v>285</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>109</v>
+        <v>-150</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>37.3</v>
+        <v>39.4</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>138.3</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="63">
@@ -4066,34 +4066,34 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>475</v>
+        <v>600</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>55.9</v>
+        <v>75</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-375</v>
+        <v>-200</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>81.40000000000001</v>
+        <v>37.1</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>38.7</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="64">
@@ -4108,34 +4108,34 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>950</v>
+        <v>1500</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>156</v>
+        <v>232</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>79.2</v>
+        <v>100</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>-250</v>
+        <v>0</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>31.3</v>
+        <v>8.1</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>29.7</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="65">
@@ -4150,34 +4150,34 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1173</v>
+        <v>1206</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>195.5</v>
+        <v>172.3</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>573</v>
+        <v>506</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="66">
@@ -4192,34 +4192,34 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1930</v>
+        <v>1860</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>388</v>
+        <v>425</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>750</v>
+        <v>791</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2314</v>
+        <v>2450</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>937</v>
+        <v>1041</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>119.9</v>
+        <v>131.7</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>384</v>
+        <v>590</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="67">
@@ -4234,34 +4234,34 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1040</v>
+        <v>980</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1674</v>
+        <v>1500</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>675</v>
+        <v>617</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>161</v>
+        <v>153.1</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>634</v>
+        <v>520</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>23.4</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="68">
@@ -4318,34 +4318,34 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>775</v>
+        <v>879</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>315</v>
+        <v>354</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>244</v>
+        <v>311</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>110.7</v>
+        <v>109.9</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>10.5</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="70">
@@ -4360,34 +4360,34 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>587</v>
+        <v>490</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>110.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>57</v>
+        <v>-60</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전년 2025-07 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-08 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>6866</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>33771</v>
+        <v>32601</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>7266</v>
+        <v>6970</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>95</v>
+        <v>91.7</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>119.2</v>
+        <v>111.5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>7385.2</v>
+        <v>7081.5</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>1757</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5892</v>
+        <v>6984</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1689</v>
+        <v>1871</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>94</v>
+        <v>111.5</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1712</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>1440</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3306</v>
+        <v>3309</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1303</v>
+        <v>1313</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>86.2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>11.7</v>
+        <v>10.9</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1314.7</v>
+        <v>1323.9</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>2866</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7865</v>
+        <v>7750</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2691</v>
+        <v>2610</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>87.8</v>
+        <v>86.5</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2706.4</v>
+        <v>2625.2</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>1592</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3798</v>
+        <v>3832</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1497</v>
+        <v>1482</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>86.7</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1504</v>
+        <v>1489.8</v>
       </c>
     </row>
     <row r="8">
@@ -723,10 +723,10 @@
         <v>3519</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>87.8</v>
@@ -735,7 +735,7 @@
         <v>1.8</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>578.8</v>
+        <v>583.8</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>7888</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>32458</v>
+        <v>32287</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>7958</v>
+        <v>7953</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>100.3</v>
+        <v>99.8</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>108</v>
+        <v>107.4</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8066</v>
+        <v>8060.4</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>3477</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14888</v>
+        <v>14950</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3521</v>
+        <v>3532</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>98.09999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>33.7</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3554.7</v>
+        <v>3565.7</v>
       </c>
     </row>
     <row r="11">
@@ -828,16 +828,16 @@
         <v>249</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5337</v>
+        <v>5320</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>100.5</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>106.5</v>
+        <v>108.8</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5443.5</v>
+        <v>5428.8</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>3424</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>16080</v>
+        <v>16155</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>202</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>3254</v>
+        <v>3262</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>200.8</v>
+        <v>202.4</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3454.8</v>
+        <v>3464.4</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2876</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>11820</v>
+        <v>12095</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>274</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3234</v>
+        <v>3310</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>106.5</v>
+        <v>109</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>49.2</v>
+        <v>52</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3283.2</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="14">
@@ -927,19 +927,19 @@
         <v>5278</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>95.2</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1094.7</v>
+        <v>1097.1</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>2548</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>12074</v>
+        <v>12220</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2606</v>
+        <v>2627</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>95.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>196</v>
+        <v>202.8</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2802</v>
+        <v>2829.8</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>2657</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>13560</v>
+        <v>13490</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2723</v>
+        <v>2697</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>207.3</v>
+        <v>202.9</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2930.3</v>
+        <v>2899.9</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1858</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5759</v>
+        <v>5849</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1720</v>
+        <v>1740</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>93</v>
+        <v>94.5</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>70.3</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1790.3</v>
+        <v>1810.3</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>3700</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>13896</v>
+        <v>14175</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3704</v>
+        <v>3767</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>98.40000000000001</v>
+        <v>100.4</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>63.3</v>
+        <v>66</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3767.3</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>4149</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>15150</v>
+        <v>15205</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>4037</v>
+        <v>3992</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>90.7</v>
+        <v>91</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>63</v>
+        <v>63.3</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4100</v>
+        <v>4055.3</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>2063</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9480</v>
+        <v>9620</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2096</v>
+        <v>2103</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>93.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2109.2</v>
+        <v>2116.3</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1549</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5921</v>
+        <v>6217</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>248</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1467</v>
+        <v>1539</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>94.3</v>
+        <v>99</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>29.6</v>
+        <v>35.5</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1496.6</v>
+        <v>1574.5</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2257</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>15030</v>
+        <v>14720</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2329</v>
+        <v>2266</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>136.7</v>
+        <v>135.2</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2465.7</v>
+        <v>2401.2</v>
       </c>
     </row>
     <row r="23">
@@ -1230,22 +1230,22 @@
         <v>884</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6345</v>
+        <v>6414</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>909</v>
+        <v>937</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>98.09999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>70.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>979.8</v>
+        <v>1007.1</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>4493</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>11858</v>
+        <v>12140</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>4373</v>
+        <v>4444</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>96.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>24.7</v>
+        <v>26</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4397.7</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>898</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2430</v>
+        <v>2455</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>898.9</v>
+        <v>904</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>66257</v>
+        <v>66290</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1578.8</v>
+        <v>1593</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>67835.8</v>
+        <v>67883</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>15128</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>58151</v>
+        <v>57995</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>15024</v>
+        <v>14828</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>92.3</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>23517</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>99338</v>
+        <v>99475</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>237</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>23559</v>
+        <v>23580</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5869</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>30431</v>
+        <v>30557</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5892</v>
+        <v>5908</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>93.59999999999999</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>21681</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>83666</v>
+        <v>84646</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>260</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>21783</v>
+        <v>21974</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>97.2</v>
+        <v>98.3</v>
       </c>
     </row>
   </sheetData>
@@ -1555,25 +1555,25 @@
         <v>2358</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>12000</v>
+        <v>11200</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>236</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2830</v>
+        <v>2643</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>104.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>500</v>
+        <v>-300</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>100.1</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1597,25 +1597,25 @@
         <v>574</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>738</v>
+        <v>692</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>107.1</v>
+        <v>100</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>15.5</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="5">
@@ -1642,7 +1642,7 @@
         <v>80</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>10</v>
@@ -1681,25 +1681,25 @@
         <v>612</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2200</v>
+        <v>2800</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>697</v>
+        <v>798</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>106.8</v>
+        <v>135.9</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>140</v>
+        <v>740</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>18.3</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="7">
@@ -1726,10 +1726,10 @@
         <v>900</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>89.09999999999999</v>
@@ -1807,25 +1807,25 @@
         <v>424</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>400</v>
+        <v>371</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>87</v>
+        <v>78.3</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-150</v>
+        <v>-250</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
@@ -1852,10 +1852,10 @@
         <v>650</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>68.40000000000001</v>
@@ -1933,25 +1933,25 @@
         <v>833</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2300</v>
+        <v>2220</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>856</v>
+        <v>821</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>95.8</v>
+        <v>92.5</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-100</v>
+        <v>-180</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="13">
@@ -1975,25 +1975,25 @@
         <v>550</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>78.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-350</v>
+        <v>-300</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="14">
@@ -2059,25 +2059,25 @@
         <v>451</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1100</v>
+        <v>1250</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>474</v>
+        <v>521</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>95.7</v>
+        <v>108.7</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -2101,25 +2101,25 @@
         <v>266</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-200</v>
+        <v>-170</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="17">
@@ -2188,10 +2188,10 @@
         <v>500</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>111.1</v>
@@ -2227,19 +2227,19 @@
         <v>55</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>189</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>107.9</v>
+        <v>112.7</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>0.7</v>
@@ -2311,25 +2311,25 @@
         <v>1613</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6050</v>
+        <v>5950</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1709</v>
+        <v>1720</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>107.8</v>
+        <v>106.1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>440</v>
+        <v>340</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>12.6</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>76.2</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>925</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>4230</v>
+        <v>4350</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1108</v>
+        <v>1157</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>114.3</v>
+        <v>117.6</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>530</v>
+        <v>650</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>7.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>30.9</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="23">
@@ -2395,25 +2395,25 @@
         <v>2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>5</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>24.8</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24">
@@ -2440,10 +2440,10 @@
         <v>2050</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>100</v>
@@ -2482,10 +2482,10 @@
         <v>1600</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="I25" s="4" t="n">
         <v>133.3</v>
@@ -2563,25 +2563,25 @@
         <v>846</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3050</v>
+        <v>3100</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>290</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>883</v>
+        <v>899</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>101.7</v>
+        <v>103.3</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>17.1</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>52.2</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="28">
@@ -2605,25 +2605,25 @@
         <v>392</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>265</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>139.3</v>
+        <v>142.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>27.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>54.3</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="29">
@@ -2689,25 +2689,25 @@
         <v>1018</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>224</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1142</v>
+        <v>1132</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>99</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>30.4</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>155.1</v>
+        <v>153.6</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>568</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2820</v>
+        <v>3000</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>606</v>
+        <v>642</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>15.9</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>44.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="32">
@@ -2773,25 +2773,25 @@
         <v>10</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-63</v>
+        <v>-49</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>22.6</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="33">
@@ -2815,25 +2815,25 @@
         <v>520</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2300</v>
+        <v>2420</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>757</v>
+        <v>811</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>133.3</v>
+        <v>140.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>575</v>
+        <v>695</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>44.2</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>352</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1400</v>
+        <v>1540</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>441</v>
+        <v>481</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>120.2</v>
+        <v>132.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>235</v>
+        <v>375</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>237</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1200</v>
+        <v>1240</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>102.1</v>
+        <v>105.5</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>6.6</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2983,25 +2983,25 @@
         <v>145</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>810</v>
+        <v>850</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>111</v>
+        <v>116.4</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="38">
@@ -3067,25 +3067,25 @@
         <v>719</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3500</v>
+        <v>3450</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>223</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>101.4</v>
+        <v>100</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>153.5</v>
+        <v>151.3</v>
       </c>
     </row>
     <row r="40">
@@ -3109,25 +3109,25 @@
         <v>306</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1820</v>
+        <v>2203</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>413</v>
+        <v>485</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>121.3</v>
+        <v>146.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>320</v>
+        <v>703</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>42.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="41">
@@ -3193,25 +3193,25 @@
         <v>577</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>103.8</v>
+        <v>101.9</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>62.5</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>168.8</v>
+        <v>165.6</v>
       </c>
     </row>
     <row r="43">
@@ -3235,25 +3235,25 @@
         <v>300</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1500</v>
+        <v>1450</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>103.4</v>
+        <v>100</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>25.7</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>38.5</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="44">
@@ -3322,10 +3322,10 @@
         <v>550</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I45" s="4" t="n">
         <v>73.3</v>
@@ -3364,10 +3364,10 @@
         <v>1050</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>105</v>
@@ -3445,25 +3445,25 @@
         <v>684</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2850</v>
+        <v>3000</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>864</v>
+        <v>914</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>118.8</v>
+        <v>125</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>13.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>488</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1800</v>
+        <v>1850</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>289</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>102.9</v>
+        <v>105.7</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>14.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>891</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>3220</v>
+        <v>3250</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>97.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-80</v>
+        <v>-50</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>11.3</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="52">
@@ -3616,10 +3616,10 @@
         <v>2410</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>703</v>
+        <v>680</v>
       </c>
       <c r="I52" s="4" t="n">
         <v>92.7</v>
@@ -3700,10 +3700,10 @@
         <v>1200</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="I54" s="4" t="n">
         <v>100</v>
@@ -3739,25 +3739,25 @@
         <v>483</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1850</v>
+        <v>1880</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>80.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-450</v>
+        <v>-420</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="56">
@@ -3823,25 +3823,25 @@
         <v>167</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>167</v>
+        <v>218</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>105.3</v>
+        <v>131.6</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>24.7</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>14.8</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="58">
@@ -3865,25 +3865,25 @@
         <v>193</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>780</v>
+        <v>900</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>114.7</v>
+        <v>132.4</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>18.9</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>14.8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59">
@@ -3949,25 +3949,25 @@
         <v>322</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>345</v>
+        <v>315</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>88.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>14.3</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>21.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -3991,25 +3991,25 @@
         <v>471</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2600</v>
+        <v>2550</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="62">
@@ -4036,10 +4036,10 @@
         <v>2850</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>95</v>
@@ -4075,25 +4075,25 @@
         <v>106</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>75</v>
+        <v>68.8</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-200</v>
+        <v>-250</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>37.1</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>22.3</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="64">
@@ -4117,25 +4117,25 @@
         <v>200</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>100</v>
+        <v>103.3</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="65">
@@ -4159,25 +4159,25 @@
         <v>61</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1206</v>
+        <v>1230</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>91</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>172.3</v>
+        <v>175.7</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>506</v>
+        <v>530</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>36.5</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="66">
@@ -4201,19 +4201,19 @@
         <v>791</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2450</v>
+        <v>2430</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>1041</v>
+        <v>1018</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>131.7</v>
+        <v>130.6</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.8</v>
@@ -4243,25 +4243,25 @@
         <v>413</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>153.1</v>
+        <v>163.3</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>520</v>
+        <v>620</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>20.2</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="68">
@@ -4327,19 +4327,19 @@
         <v>304</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>109.9</v>
+        <v>110</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
@@ -4369,25 +4369,25 @@
         <v>210</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>89.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.07.28.pdf</t>
+          <t>Revenue Meeting_2026.08.04.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29T17:21:21.216784Z</t>
+          <t>2026-08-05T07:53:41.457796Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.07.28</t>
+          <t>2026.08.04</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>6866</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>32601</v>
+        <v>32090</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6970</v>
+        <v>6804</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>91.7</v>
+        <v>90.3</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>111.5</v>
+        <v>106.6</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>7081.5</v>
+        <v>6910.6</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>1757</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>6984</v>
+        <v>7607</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1871</v>
+        <v>2012</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>111.5</v>
+        <v>121.4</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1899</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>1440</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3309</v>
+        <v>3310</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1313</v>
+        <v>1306</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1323.9</v>
+        <v>1316.7</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>2866</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7750</v>
+        <v>7605</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2610</v>
+        <v>2553</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>86.5</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>15.2</v>
+        <v>14.3</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2625.2</v>
+        <v>2567.3</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>1592</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3832</v>
+        <v>3834</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1482</v>
+        <v>1472</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>87.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1489.8</v>
+        <v>1479.7</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>607</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3519</v>
+        <v>3439</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>87.8</v>
+        <v>85.8</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>583.8</v>
+        <v>572.7</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>7888</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>32287</v>
+        <v>32353</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>246</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>7953</v>
+        <v>7956</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>107.4</v>
+        <v>106.9</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8060.4</v>
+        <v>8062.9</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>3477</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14950</v>
+        <v>14885</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3532</v>
+        <v>3503</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>98.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>33.7</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3565.7</v>
+        <v>3536.7</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>5282</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>21408</v>
+        <v>21349</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5320</v>
+        <v>5293</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>100.5</v>
+        <v>100.2</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>108.8</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5428.8</v>
+        <v>5401.8</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>3424</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>16155</v>
+        <v>16335</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>3262</v>
+        <v>3285</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>88.3</v>
+        <v>89.3</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>202.4</v>
+        <v>209.3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3464.4</v>
+        <v>3494.3</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2876</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>12095</v>
+        <v>12320</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>274</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3310</v>
+        <v>3376</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>52</v>
+        <v>54.6</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3362</v>
+        <v>3430.6</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>1066</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>5278</v>
+        <v>5340</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>95.2</v>
+        <v>96.3</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>11.1</v>
+        <v>10.6</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1097.1</v>
+        <v>1098.6</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>2548</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>12220</v>
+        <v>12295</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2627</v>
+        <v>2636</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>202.8</v>
+        <v>202.9</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2829.8</v>
+        <v>2838.9</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>2657</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>13490</v>
+        <v>13509</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2697</v>
+        <v>2683</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>202.9</v>
+        <v>196.6</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2899.9</v>
+        <v>2879.6</v>
       </c>
     </row>
     <row r="17">
@@ -1032,16 +1032,16 @@
         <v>298</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1740</v>
+        <v>1744</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>94.5</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>70.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1810.3</v>
+        <v>1816.1</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>3700</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>14175</v>
+        <v>14228</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3767</v>
+        <v>3796</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>100.4</v>
+        <v>100.8</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>66</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3833</v>
+        <v>3864.1</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>4149</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>15205</v>
+        <v>14735</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3992</v>
+        <v>3834</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>91</v>
+        <v>88.2</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>63.3</v>
+        <v>57.4</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4055.3</v>
+        <v>3891.4</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>2063</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9620</v>
+        <v>9850</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>219</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2103</v>
+        <v>2153</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>95</v>
+        <v>97.2</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2116.3</v>
+        <v>2166.6</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1549</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>6217</v>
+        <v>6756</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1539</v>
+        <v>1667</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>99</v>
+        <v>107.6</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>35.5</v>
+        <v>39.9</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1574.5</v>
+        <v>1706.9</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2257</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>14720</v>
+        <v>14230</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2266</v>
+        <v>2206</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>91.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>135.2</v>
+        <v>118.5</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2401.2</v>
+        <v>2324.5</v>
       </c>
     </row>
     <row r="23">
@@ -1230,22 +1230,22 @@
         <v>884</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6414</v>
+        <v>6485</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>937</v>
+        <v>957</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>100.2</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>70.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1007.1</v>
+        <v>1029.7</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>4493</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>12140</v>
+        <v>12390</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>4444</v>
+        <v>4495</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>98.7</v>
+        <v>100.7</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>26</v>
+        <v>26.6</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4470</v>
+        <v>4521.6</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>898</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2455</v>
+        <v>2513</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>887</v>
+        <v>916</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>100</v>
+        <v>102.4</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>904</v>
+        <v>933.3</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>66290</v>
+        <v>66306</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1593</v>
+        <v>1582.6</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>67883</v>
+        <v>67888.60000000001</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>15128</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>57995</v>
+        <v>57885</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>14828</v>
+        <v>14717</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>92.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>23517</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>99475</v>
+        <v>99730</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>237</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>23580</v>
+        <v>23590</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>97.40000000000001</v>
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5869</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>30557</v>
+        <v>30836</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5908</v>
+        <v>6025</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>94</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>21681</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>84646</v>
+        <v>84856</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>21974</v>
+        <v>21973</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>98.3</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1555,25 +1555,25 @@
         <v>2358</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>11200</v>
+        <v>10500</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2643</v>
+        <v>2468</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-300</v>
+        <v>-1000</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1597,25 +1597,25 @@
         <v>574</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2800</v>
+        <v>3100</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>692</v>
+        <v>753</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>100</v>
+        <v>110.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>14.4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -1639,25 +1639,25 @@
         <v>43</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>26.7</v>
+        <v>22</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-220</v>
+        <v>-234</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>45.6</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1681,25 +1681,25 @@
         <v>612</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2800</v>
+        <v>3250</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>798</v>
+        <v>897</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>135.9</v>
+        <v>157.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>740</v>
+        <v>1190</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>23.4</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="7">
@@ -1723,25 +1723,25 @@
         <v>303</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>89.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-110</v>
+        <v>-60</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="8">
@@ -1807,25 +1807,25 @@
         <v>424</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>78.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-250</v>
+        <v>-300</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
@@ -1849,25 +1849,25 @@
         <v>380</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-300</v>
+        <v>-250</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11">
@@ -1933,25 +1933,25 @@
         <v>833</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2220</v>
+        <v>2000</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>821</v>
+        <v>744</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>92.5</v>
+        <v>83.3</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-180</v>
+        <v>-400</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>10.6</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="13">
@@ -1975,25 +1975,25 @@
         <v>550</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>81.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-300</v>
+        <v>-250</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="14">
@@ -2059,25 +2059,25 @@
         <v>451</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1250</v>
+        <v>1215</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>108.7</v>
+        <v>105.7</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="16">
@@ -2104,10 +2104,10 @@
         <v>530</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>75.7</v>
@@ -2185,25 +2185,25 @@
         <v>82</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="H18" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="I18" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="I18" s="4" t="n">
-        <v>111.1</v>
-      </c>
       <c r="J18" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="19">
@@ -2227,19 +2227,19 @@
         <v>55</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>67</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>112.7</v>
+        <v>111.1</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>0.7</v>
@@ -2311,25 +2311,25 @@
         <v>1613</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5950</v>
+        <v>5850</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1720</v>
+        <v>1708</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>106.1</v>
+        <v>104.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>340</v>
+        <v>240</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>12.6</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>925</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>4350</v>
+        <v>4450</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>266</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1157</v>
+        <v>1184</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>117.6</v>
+        <v>120.3</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>7.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>31.7</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="23">
@@ -2482,10 +2482,10 @@
         <v>1600</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I25" s="4" t="n">
         <v>133.3</v>
@@ -2566,10 +2566,10 @@
         <v>3100</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="I27" s="4" t="n">
         <v>103.3</v>
@@ -2608,10 +2608,10 @@
         <v>2000</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>142.9</v>
@@ -2689,25 +2689,25 @@
         <v>1018</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5050</v>
+        <v>5250</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>224</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1132</v>
+        <v>1177</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>98.09999999999999</v>
+        <v>101.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>30.4</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>153.6</v>
+        <v>159.7</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>568</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3000</v>
+        <v>3050</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>100</v>
+        <v>101.7</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>15.9</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>47.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="32">
@@ -2773,25 +2773,25 @@
         <v>10</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>5</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>22.6</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="33">
@@ -2815,25 +2815,25 @@
         <v>520</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2420</v>
+        <v>2550</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>811</v>
+        <v>862</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>140.3</v>
+        <v>147.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>695</v>
+        <v>825</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>46.6</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>352</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1540</v>
+        <v>1570</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>132.2</v>
+        <v>134.8</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>237</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1240</v>
+        <v>1150</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>237</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>105.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>65</v>
+        <v>-25</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>6.6</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="37">
@@ -2983,25 +2983,25 @@
         <v>145</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>850</v>
+        <v>905</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>116.4</v>
+        <v>124</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="38">
@@ -3070,10 +3070,10 @@
         <v>3450</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>100</v>
@@ -3109,25 +3109,25 @@
         <v>306</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>2203</v>
+        <v>2207</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>146.9</v>
+        <v>147.1</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="41">
@@ -3193,25 +3193,25 @@
         <v>577</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2650</v>
+        <v>2550</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>101.9</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>62.5</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>165.6</v>
+        <v>159.4</v>
       </c>
     </row>
     <row r="43">
@@ -3238,10 +3238,10 @@
         <v>1450</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="I43" s="4" t="n">
         <v>100</v>
@@ -3322,10 +3322,10 @@
         <v>550</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I45" s="4" t="n">
         <v>73.3</v>
@@ -3361,25 +3361,25 @@
         <v>333</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1050</v>
+        <v>1123</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>105</v>
+        <v>112.3</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>24.2</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>25.4</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="47">
@@ -3445,25 +3445,25 @@
         <v>684</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3000</v>
+        <v>3050</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>914</v>
+        <v>946</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>125</v>
+        <v>127.1</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>13.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>39.7</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>488</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1850</v>
+        <v>1950</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>534</v>
+        <v>566</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>105.7</v>
+        <v>111.4</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>14.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>26.3</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>891</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>3250</v>
+        <v>2900</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>985</v>
+        <v>873</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>98.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-50</v>
+        <v>-400</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>11.3</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>36.6</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="52">
@@ -3613,25 +3613,25 @@
         <v>680</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2410</v>
+        <v>2230</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>680</v>
+        <v>624</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>92.7</v>
+        <v>85.8</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>-190</v>
+        <v>-370</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>11.1</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>26.7</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="53">
@@ -3700,10 +3700,10 @@
         <v>1200</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I54" s="4" t="n">
         <v>100</v>
@@ -3739,25 +3739,25 @@
         <v>483</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1880</v>
+        <v>1980</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>441</v>
+        <v>468</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>81.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-420</v>
+        <v>-320</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -3823,25 +3823,25 @@
         <v>167</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>750</v>
+        <v>820</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>131.6</v>
+        <v>143.9</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>24.7</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>18.5</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="58">
@@ -3865,25 +3865,25 @@
         <v>193</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>900</v>
+        <v>1040</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>132.4</v>
+        <v>152.9</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>220</v>
+        <v>360</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>18.9</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>17</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="59">
@@ -3949,25 +3949,25 @@
         <v>322</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>315</v>
+        <v>274</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>82.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>14.3</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>20</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="61">
@@ -3991,19 +3991,19 @@
         <v>471</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2550</v>
+        <v>2500</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>1.2</v>
@@ -4033,25 +4033,25 @@
         <v>276</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2850</v>
+        <v>2500</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>95</v>
+        <v>83.3</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>-150</v>
+        <v>-500</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>39.4</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>112.2</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="63">
@@ -4075,25 +4075,25 @@
         <v>106</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>68.8</v>
+        <v>66.2</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-250</v>
+        <v>-270</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>37.1</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>20.4</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="64">
@@ -4117,25 +4117,25 @@
         <v>200</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1550</v>
+        <v>1700</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>103.3</v>
+        <v>113.3</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>12.5</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="65">
@@ -4159,25 +4159,25 @@
         <v>61</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1230</v>
+        <v>1300</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>175.7</v>
+        <v>185.7</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>530</v>
+        <v>600</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>37.2</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="66">
@@ -4201,25 +4201,25 @@
         <v>791</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2430</v>
+        <v>2400</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>1018</v>
+        <v>991</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>130.6</v>
+        <v>129</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="67">
@@ -4243,25 +4243,25 @@
         <v>413</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>637</v>
+        <v>652</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>163.3</v>
+        <v>168.4</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>620</v>
+        <v>670</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="68">
@@ -4327,25 +4327,25 @@
         <v>304</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>880</v>
+        <v>895</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>110</v>
+        <v>111.9</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>210</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.08.04.pdf</t>
+          <t>Revenue Meeting_2026.08.10.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-05T07:53:41.457796Z</t>
+          <t>2026-08-11T15:53:51.983209Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.08.04</t>
+          <t>2026.08.10</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 총괄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -550,22 +550,22 @@
         <v>6866</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>32090</v>
+        <v>31430</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>212</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6804</v>
+        <v>6670</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>90.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>106.6</v>
+        <v>100.8</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>6910.6</v>
+        <v>6770.8</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>1757</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7607</v>
+        <v>7873</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2012</v>
+        <v>2079</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>121.4</v>
+        <v>125.7</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>32</v>
+        <v>32.8</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>2044</v>
+        <v>2111.8</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>1440</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3310</v>
+        <v>3313</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>86.3</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1316.7</v>
+        <v>1312.6</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>2866</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7605</v>
+        <v>7679</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2553</v>
+        <v>2568</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>14.3</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2567.3</v>
+        <v>2582.3</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>1592</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3834</v>
+        <v>3864</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>384</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1472</v>
+        <v>1483</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>87.5</v>
+        <v>88.2</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1479.7</v>
+        <v>1490.5</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>607</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3439</v>
+        <v>3347</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>85.8</v>
+        <v>83.5</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>572.7</v>
+        <v>559.6</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>7888</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>32353</v>
+        <v>32449</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>246</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>7956</v>
+        <v>7967</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>100</v>
+        <v>100.3</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>106.9</v>
+        <v>106</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8062.9</v>
+        <v>8073</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>3477</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14885</v>
+        <v>14770</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3503</v>
+        <v>3480</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>98.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>33.7</v>
+        <v>32.8</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3536.7</v>
+        <v>3512.8</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>5282</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>21349</v>
+        <v>21370</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5293</v>
+        <v>5289</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>100.2</v>
+        <v>100.3</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>108.8</v>
+        <v>105.1</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5401.8</v>
+        <v>5394.1</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>3424</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>16335</v>
+        <v>16610</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>3285</v>
+        <v>3300</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>89.3</v>
+        <v>90.8</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>209.3</v>
+        <v>204.7</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3494.3</v>
+        <v>3504.7</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2876</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>12320</v>
+        <v>12550</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>274</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3376</v>
+        <v>3436</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>111</v>
+        <v>113.1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>54.6</v>
+        <v>55.7</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3430.6</v>
+        <v>3491.7</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>1066</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>5340</v>
+        <v>5278</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1088</v>
+        <v>1069</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>96.3</v>
+        <v>95.2</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1098.6</v>
+        <v>1079.2</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>2548</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>12295</v>
+        <v>12420</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2636</v>
+        <v>2649</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>97.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>202.9</v>
+        <v>207</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2838.9</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>2657</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>13509</v>
+        <v>13780</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2683</v>
+        <v>2723</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>100.9</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>196.6</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2879.6</v>
+        <v>2919.6</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1858</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5849</v>
+        <v>5769</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1744</v>
+        <v>1727</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>94.5</v>
+        <v>93.2</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>72.09999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1816.1</v>
+        <v>1794.2</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>3700</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>14228</v>
+        <v>13700</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>267</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3796</v>
+        <v>3659</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>100.8</v>
+        <v>97</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>68.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3864.1</v>
+        <v>3725.8</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>4149</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>14735</v>
+        <v>14767</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3834</v>
+        <v>3819</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>88.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>57.4</v>
+        <v>57.7</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3891.4</v>
+        <v>3876.7</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>2063</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9850</v>
+        <v>9870</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2153</v>
+        <v>2167</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2166.6</v>
+        <v>2180.3</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1549</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>6756</v>
+        <v>6804</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>107.6</v>
+        <v>108.3</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>39.9</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1706.9</v>
+        <v>1705.9</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2257</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>14230</v>
+        <v>14265</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2206</v>
+        <v>2228</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>88.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>118.5</v>
+        <v>118.4</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2324.5</v>
+        <v>2346.4</v>
       </c>
     </row>
     <row r="23">
@@ -1230,22 +1230,22 @@
         <v>884</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6485</v>
+        <v>6566</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>957</v>
+        <v>984</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>100.2</v>
+        <v>101.5</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>72.7</v>
+        <v>75</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1029.7</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>4493</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>12390</v>
+        <v>12620</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>4495</v>
+        <v>4592</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>100.7</v>
+        <v>102.6</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>26.6</v>
+        <v>27.1</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4521.6</v>
+        <v>4619.1</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>898</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2513</v>
+        <v>2540</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>916</v>
+        <v>933</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>102.4</v>
+        <v>103.5</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>933.3</v>
+        <v>950.2</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>66306</v>
+        <v>66348</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1582.6</v>
+        <v>1568.3</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>67888.60000000001</v>
+        <v>67916.3</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>15128</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>57885</v>
+        <v>57506</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>14717</v>
+        <v>14660</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>91.90000000000001</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>23517</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>99730</v>
+        <v>100159</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>23590</v>
+        <v>23618</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>97.59999999999999</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5869</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>30836</v>
+        <v>30939</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>6025</v>
+        <v>6061</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>21681</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>84856</v>
+        <v>85030</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>259</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>21973</v>
+        <v>22008</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>98.59999999999999</v>
+        <v>98.8</v>
       </c>
     </row>
   </sheetData>
@@ -1555,25 +1555,25 @@
         <v>2358</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>10500</v>
+        <v>9700</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2468</v>
+        <v>2303</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>91.3</v>
+        <v>84.3</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-1000</v>
+        <v>-1800</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>87.59999999999999</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1597,25 +1597,25 @@
         <v>574</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3100</v>
+        <v>3250</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>243</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>753</v>
+        <v>790</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>110.7</v>
+        <v>116.1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>16</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="5">
@@ -1639,25 +1639,25 @@
         <v>43</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>122</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-234</v>
+        <v>-230</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>45.6</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -1681,25 +1681,25 @@
         <v>612</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3250</v>
+        <v>3350</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>897</v>
+        <v>921</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>157.8</v>
+        <v>162.6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1190</v>
+        <v>1290</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>27.1</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="7">
@@ -1726,10 +1726,10 @@
         <v>950</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>94.09999999999999</v>
@@ -1807,25 +1807,25 @@
         <v>424</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>73.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-300</v>
+        <v>-350</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
@@ -1849,25 +1849,25 @@
         <v>380</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>700</v>
+        <v>760</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>73.7</v>
+        <v>80</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-250</v>
+        <v>-190</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="11">
@@ -1936,10 +1936,10 @@
         <v>2000</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>83.3</v>
@@ -1978,10 +1978,10 @@
         <v>1350</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>84.40000000000001</v>
@@ -2059,25 +2059,25 @@
         <v>451</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1215</v>
+        <v>1170</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>105.7</v>
+        <v>101.7</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="16">
@@ -2185,25 +2185,25 @@
         <v>82</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="19">
@@ -2230,7 +2230,7 @@
         <v>350</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>67</v>
@@ -2311,25 +2311,25 @@
         <v>1613</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5850</v>
+        <v>5750</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1708</v>
+        <v>1691</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>104.3</v>
+        <v>102.5</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>12.6</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>73.7</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>925</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>4450</v>
+        <v>4500</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1184</v>
+        <v>1193</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>120.3</v>
+        <v>121.6</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>7.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>32.5</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="23">
@@ -2437,25 +2437,25 @@
         <v>542</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2050</v>
+        <v>2000</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="25">
@@ -2479,25 +2479,25 @@
         <v>270</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1600</v>
+        <v>1550</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>235</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>133.3</v>
+        <v>129.2</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="26">
@@ -2563,25 +2563,25 @@
         <v>846</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3100</v>
+        <v>3050</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>910</v>
+        <v>891</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>103.3</v>
+        <v>101.7</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>17.1</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>53.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="28">
@@ -2605,25 +2605,25 @@
         <v>392</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>142.9</v>
+        <v>135.7</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>27.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>55.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="29">
@@ -2689,25 +2689,25 @@
         <v>1018</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5250</v>
+        <v>5100</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1177</v>
+        <v>1145</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>101.9</v>
+        <v>99</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>30.4</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>159.7</v>
+        <v>155.1</v>
       </c>
     </row>
     <row r="31">
@@ -2734,10 +2734,10 @@
         <v>3050</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>101.7</v>
@@ -2773,19 +2773,19 @@
         <v>10</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>5</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-50</v>
+        <v>-52</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>22.6</v>
@@ -2815,25 +2815,25 @@
         <v>520</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2550</v>
+        <v>2600</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>338</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>862</v>
+        <v>879</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>147.8</v>
+        <v>150.7</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>825</v>
+        <v>875</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>49.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>352</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1570</v>
+        <v>1600</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>134.8</v>
+        <v>137.3</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>405</v>
+        <v>435</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>237</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1150</v>
+        <v>1080</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>97.90000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-25</v>
+        <v>-95</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>6.6</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="37">
@@ -2983,25 +2983,25 @@
         <v>145</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>905</v>
+        <v>870</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>124</v>
+        <v>119.2</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="38">
@@ -3025,7 +3025,7 @@
         <v>5</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>132</v>
@@ -3034,16 +3034,16 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>42.4</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39">
@@ -3067,25 +3067,25 @@
         <v>719</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3450</v>
+        <v>3600</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>773</v>
+        <v>796</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>100</v>
+        <v>104.3</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>151.3</v>
+        <v>157.9</v>
       </c>
     </row>
     <row r="40">
@@ -3109,25 +3109,25 @@
         <v>306</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>2207</v>
+        <v>2100</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>480</v>
+        <v>454</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>147.1</v>
+        <v>140</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>707</v>
+        <v>600</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>51.5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41">
@@ -3196,10 +3196,10 @@
         <v>2550</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="I42" s="4" t="n">
         <v>98.09999999999999</v>
@@ -3238,10 +3238,10 @@
         <v>1450</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I43" s="4" t="n">
         <v>100</v>
@@ -3319,25 +3319,25 @@
         <v>250</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-200</v>
+        <v>-250</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>79.7</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>43.8</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="46">
@@ -3361,25 +3361,25 @@
         <v>333</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1123</v>
+        <v>1085</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>112.3</v>
+        <v>108.5</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>24.2</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>27.1</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="47">
@@ -3403,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>170</v>
@@ -3415,13 +3415,13 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>34</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="48">
@@ -3445,25 +3445,25 @@
         <v>684</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3050</v>
+        <v>3000</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>946</v>
+        <v>932</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>127.1</v>
+        <v>125</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>13.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>40.3</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>488</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1950</v>
+        <v>1908</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>566</v>
+        <v>552</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>111.4</v>
+        <v>109</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>14.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>27.7</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>891</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2900</v>
+        <v>2940</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-400</v>
+        <v>-360</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>11.3</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>32.7</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="52">
@@ -3613,25 +3613,25 @@
         <v>680</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>85.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>-370</v>
+        <v>-380</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>11.1</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="53">
@@ -3697,25 +3697,25 @@
         <v>257</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>6.8</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="55">
@@ -3739,25 +3739,25 @@
         <v>483</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1980</v>
+        <v>2000</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>236</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-320</v>
+        <v>-300</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="56">
@@ -3823,25 +3823,25 @@
         <v>167</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>143.9</v>
+        <v>142.1</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>24.7</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
@@ -3865,25 +3865,25 @@
         <v>193</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>278</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>152.9</v>
+        <v>154.4</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>18.9</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="59">
@@ -3952,10 +3952,10 @@
         <v>1200</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>70.59999999999999</v>
@@ -3991,25 +3991,25 @@
         <v>471</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>221</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>553</v>
+        <v>531</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="62">
@@ -4075,25 +4075,25 @@
         <v>106</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>66.2</v>
+        <v>67.5</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-270</v>
+        <v>-260</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>37.1</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>19.7</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="64">
@@ -4117,25 +4117,25 @@
         <v>200</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1700</v>
+        <v>1770</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>113.3</v>
+        <v>118</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="65">
@@ -4159,25 +4159,25 @@
         <v>61</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1300</v>
+        <v>1346</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>185.7</v>
+        <v>192.3</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>600</v>
+        <v>646</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>39.3</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="66">
@@ -4201,25 +4201,25 @@
         <v>791</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2400</v>
+        <v>2260</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>991</v>
+        <v>930</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>129</v>
+        <v>121.5</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>540</v>
+        <v>400</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="67">
@@ -4243,25 +4243,25 @@
         <v>413</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>652</v>
+        <v>674</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>168.4</v>
+        <v>173.5</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>670</v>
+        <v>720</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="68">
@@ -4330,10 +4330,10 @@
         <v>895</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I69" s="4" t="n">
         <v>111.9</v>
@@ -4369,25 +4369,25 @@
         <v>210</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>92.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.08.10.pdf</t>
+          <t>Revenue Meeting_2026.08.18.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-11T15:53:51.983209Z</t>
+          <t>2026-08-19T09:49:05.621963Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.08.10</t>
+          <t>2026.08.18</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>6866</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>31430</v>
+        <v>30942</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6670</v>
+        <v>6544</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>88.40000000000001</v>
+        <v>87</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>100.8</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>6770.8</v>
+        <v>6641.4</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>1757</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7873</v>
+        <v>7907</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>264</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2079</v>
+        <v>2086</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>125.7</v>
+        <v>126.2</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>32.8</v>
+        <v>33.3</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>2111.8</v>
+        <v>2119.3</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>1440</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3313</v>
+        <v>3320</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>86.3</v>
+        <v>86.5</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1312.6</v>
+        <v>1308.4</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>2866</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7679</v>
+        <v>7612</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>334</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2568</v>
+        <v>2546</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>85.8</v>
+        <v>85</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2582.3</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>1592</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3864</v>
+        <v>3879</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>384</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1483</v>
+        <v>1488</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>88.2</v>
+        <v>88.5</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1490.5</v>
+        <v>1495.3</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>607</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3347</v>
+        <v>3294</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>83.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>559.6</v>
+        <v>549.5</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>7888</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>32449</v>
+        <v>32780</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>7967</v>
+        <v>7998</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>100.3</v>
+        <v>101.3</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8073</v>
+        <v>8102</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>3477</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14770</v>
+        <v>14792</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3480</v>
+        <v>3478</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>97.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3512.8</v>
+        <v>3510.2</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>5282</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>21370</v>
+        <v>21500</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>247</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5289</v>
+        <v>5304</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>100.3</v>
+        <v>100.9</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>105.1</v>
+        <v>101.4</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5394.1</v>
+        <v>5405.4</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>3424</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>16610</v>
+        <v>17200</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>3300</v>
+        <v>3380</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>90.8</v>
+        <v>94</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>204.7</v>
+        <v>215.4</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3504.7</v>
+        <v>3595.4</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2876</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>12550</v>
+        <v>12610</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>274</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3436</v>
+        <v>3461</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>113.1</v>
+        <v>113.6</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>55.7</v>
+        <v>56</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3491.7</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="14">
@@ -924,22 +924,22 @@
         <v>1066</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>5278</v>
+        <v>5440</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1069</v>
+        <v>1089</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>95.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1079.2</v>
+        <v>1099.3</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>2548</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>12420</v>
+        <v>12463</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2649</v>
+        <v>2642</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>207</v>
+        <v>205.4</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2856</v>
+        <v>2847.4</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>2657</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>13780</v>
+        <v>13840</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2723</v>
+        <v>2715</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>100.9</v>
+        <v>101.3</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>196.6</v>
+        <v>196.2</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2919.6</v>
+        <v>2911.2</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1858</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5769</v>
+        <v>5795</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1727</v>
+        <v>1737</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>93.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>67.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1794.2</v>
+        <v>1802.9</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>3700</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>13700</v>
+        <v>13455</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>267</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3659</v>
+        <v>3596</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>97</v>
+        <v>95.3</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>66.8</v>
+        <v>62.9</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3725.8</v>
+        <v>3658.9</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>4149</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>14767</v>
+        <v>15010</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3819</v>
+        <v>3873</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>88.40000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>57.7</v>
+        <v>59.6</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3876.7</v>
+        <v>3932.6</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>2063</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9870</v>
+        <v>10080</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2167</v>
+        <v>2210</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2180.3</v>
+        <v>2223.6</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1549</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>6804</v>
+        <v>6970</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1666</v>
+        <v>1690</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>108.3</v>
+        <v>111</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>39.9</v>
+        <v>40.5</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1705.9</v>
+        <v>1730.5</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2257</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>14265</v>
+        <v>13988</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2228</v>
+        <v>2207</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>88.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>118.4</v>
+        <v>113</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2346.4</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="23">
@@ -1230,22 +1230,22 @@
         <v>884</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6566</v>
+        <v>6622</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>984</v>
+        <v>1002</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>101.5</v>
+        <v>102.3</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1059</v>
+        <v>1076.9</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>4493</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>12620</v>
+        <v>12746</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>364</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>4592</v>
+        <v>4639</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>102.6</v>
+        <v>103.6</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>27.1</v>
+        <v>26.5</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4619.1</v>
+        <v>4665.5</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>898</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2540</v>
+        <v>2575</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>367</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>933</v>
+        <v>945</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>103.5</v>
+        <v>104.9</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>950.2</v>
+        <v>962.4</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>66348</v>
+        <v>66476</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1568.3</v>
+        <v>1559.1</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>67916.3</v>
+        <v>68035.10000000001</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>15128</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>57506</v>
+        <v>56954</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>255</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>14660</v>
+        <v>14511</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>91.3</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>23517</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>100159</v>
+        <v>101310</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>23618</v>
+        <v>23747</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>98</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5869</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>30939</v>
+        <v>31038</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>6061</v>
+        <v>6107</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>95.2</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>21681</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>85030</v>
+        <v>85518</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>259</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>22008</v>
+        <v>22111</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>98.8</v>
+        <v>99.3</v>
       </c>
     </row>
   </sheetData>
@@ -1555,25 +1555,25 @@
         <v>2358</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>9700</v>
+        <v>9350</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>237</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2303</v>
+        <v>2220</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>84.3</v>
+        <v>81.3</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-1800</v>
+        <v>-2150</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>80.90000000000001</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
@@ -1597,25 +1597,25 @@
         <v>574</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3250</v>
+        <v>3170</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>243</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>790</v>
+        <v>770</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>116.1</v>
+        <v>113.2</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>450</v>
+        <v>370</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="5">
@@ -1639,25 +1639,25 @@
         <v>43</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>23.3</v>
+        <v>22.7</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-230</v>
+        <v>-232</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>45.6</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -1681,25 +1681,25 @@
         <v>612</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3350</v>
+        <v>3440</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>921</v>
+        <v>939</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>162.6</v>
+        <v>167</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1290</v>
+        <v>1380</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>27.9</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="7">
@@ -1723,25 +1723,25 @@
         <v>303</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>950</v>
+        <v>900</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>94.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-60</v>
+        <v>-110</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
@@ -1807,25 +1807,25 @@
         <v>424</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-350</v>
+        <v>-370</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
@@ -1849,19 +1849,19 @@
         <v>380</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>80</v>
+        <v>79.5</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-190</v>
+        <v>-195</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>5.2</v>
@@ -1933,25 +1933,25 @@
         <v>833</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2000</v>
+        <v>1920</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>83.3</v>
+        <v>80</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-400</v>
+        <v>-480</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1975,25 +1975,25 @@
         <v>550</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1350</v>
+        <v>1360</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>362</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>84.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-250</v>
+        <v>-240</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="14">
@@ -2059,25 +2059,25 @@
         <v>451</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1170</v>
+        <v>1140</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>101.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>20</v>
+        <v>-10</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="16">
@@ -2185,25 +2185,25 @@
         <v>82</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>214</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-30</v>
+        <v>-60</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="19">
@@ -2230,10 +2230,10 @@
         <v>350</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>111.1</v>
@@ -2311,25 +2311,25 @@
         <v>1613</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5750</v>
+        <v>5650</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>294</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1691</v>
+        <v>1661</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>102.5</v>
+        <v>100.7</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>12.6</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>925</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1193</v>
+        <v>1159</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>121.6</v>
+        <v>118.9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>7.3</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>32.8</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="23">
@@ -2437,25 +2437,25 @@
         <v>542</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2000</v>
+        <v>1990</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>97.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="25">
@@ -2479,25 +2479,25 @@
         <v>270</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>235</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>129.2</v>
+        <v>125</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="26">
@@ -2563,25 +2563,25 @@
         <v>846</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3050</v>
+        <v>2960</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>891</v>
+        <v>861</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>101.7</v>
+        <v>98.7</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>50</v>
+        <v>-40</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>17.1</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>52.2</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="28">
@@ -2605,25 +2605,25 @@
         <v>392</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1900</v>
+        <v>1821</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>135.7</v>
+        <v>130.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>500</v>
+        <v>421</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>27.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>52.9</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="29">
@@ -2689,25 +2689,25 @@
         <v>1018</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5100</v>
+        <v>5365</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1145</v>
+        <v>1186</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>99</v>
+        <v>104.2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-50</v>
+        <v>215</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>30.4</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>155.1</v>
+        <v>163.2</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>568</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3050</v>
+        <v>3215</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>639</v>
+        <v>667</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>101.7</v>
+        <v>107.2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>50</v>
+        <v>215</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>15.9</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>48.5</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="32">
@@ -2773,19 +2773,19 @@
         <v>10</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>5</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-52</v>
+        <v>-50</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>22.6</v>
@@ -2815,25 +2815,25 @@
         <v>520</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2600</v>
+        <v>2620</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>150.7</v>
+        <v>151.9</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>875</v>
+        <v>895</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="34">
@@ -2860,10 +2860,10 @@
         <v>1600</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="I34" s="4" t="n">
         <v>137.3</v>
@@ -2941,25 +2941,25 @@
         <v>237</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1080</v>
+        <v>1125</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>91.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-95</v>
+        <v>-50</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>6.6</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="37">
@@ -2983,19 +2983,19 @@
         <v>145</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>119.2</v>
+        <v>120.5</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>3</v>
@@ -3025,7 +3025,7 @@
         <v>5</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>132</v>
@@ -3034,16 +3034,16 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>42.4</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="39">
@@ -3067,25 +3067,25 @@
         <v>719</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3600</v>
+        <v>3570</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>221</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>104.3</v>
+        <v>103.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>157.9</v>
+        <v>156.6</v>
       </c>
     </row>
     <row r="40">
@@ -3109,25 +3109,25 @@
         <v>306</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>140</v>
+        <v>139.3</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="41">
@@ -3193,25 +3193,25 @@
         <v>577</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2550</v>
+        <v>2527</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>98.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>-50</v>
+        <v>-73</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>62.5</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>159.4</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43">
@@ -3235,25 +3235,25 @@
         <v>300</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1450</v>
+        <v>1490</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>100</v>
+        <v>102.8</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>25.7</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>37.2</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="44">
@@ -3319,25 +3319,25 @@
         <v>250</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>365</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>66.7</v>
+        <v>64</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-250</v>
+        <v>-270</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>79.7</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>39.8</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="46">
@@ -3361,25 +3361,25 @@
         <v>333</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1085</v>
+        <v>1100</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>343</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>108.5</v>
+        <v>110</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>24.2</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>26.2</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="47">
@@ -3403,10 +3403,10 @@
         <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>6</v>
@@ -3415,13 +3415,13 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>34</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="48">
@@ -3445,25 +3445,25 @@
         <v>684</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>932</v>
+        <v>906</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>125</v>
+        <v>120.8</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>13.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>39.7</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>488</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1908</v>
+        <v>1730</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>552</v>
+        <v>499</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>109</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>158</v>
+        <v>-20</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>14.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>27.1</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>891</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2940</v>
+        <v>3045</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>874</v>
+        <v>896</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>89.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-360</v>
+        <v>-255</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>11.3</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>33.1</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="52">
@@ -3613,25 +3613,25 @@
         <v>680</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2220</v>
+        <v>2280</v>
       </c>
       <c r="G52" s="3" t="n">
         <v>279</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>620</v>
+        <v>636</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>85.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>-380</v>
+        <v>-320</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>11.1</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>24.6</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="53">
@@ -3697,25 +3697,25 @@
         <v>257</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1150</v>
+        <v>1170</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>273</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>95.8</v>
+        <v>97.5</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>6.8</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="55">
@@ -3739,25 +3739,25 @@
         <v>483</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>2000</v>
+        <v>2060</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>87</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-300</v>
+        <v>-240</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="56">
@@ -3823,25 +3823,25 @@
         <v>167</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>142.1</v>
+        <v>143</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>24.7</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="58">
@@ -3865,25 +3865,25 @@
         <v>193</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>154.4</v>
+        <v>158.1</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>18.9</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>19.9</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="59">
@@ -3949,25 +3949,25 @@
         <v>322</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1200</v>
+        <v>1050</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>70.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-500</v>
+        <v>-650</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>14.3</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>17.1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
@@ -3991,25 +3991,25 @@
         <v>471</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2400</v>
+        <v>2350</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-100</v>
+        <v>-150</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="62">
@@ -4033,25 +4033,25 @@
         <v>276</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2500</v>
+        <v>2420</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>100</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>83.3</v>
+        <v>80.7</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>-500</v>
+        <v>-580</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>39.4</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>98.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="63">
@@ -4075,25 +4075,25 @@
         <v>106</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="G63" s="3" t="n">
         <v>178</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>67.5</v>
+        <v>68.8</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-260</v>
+        <v>-250</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>37.1</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="64">
@@ -4117,25 +4117,25 @@
         <v>200</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1770</v>
+        <v>1790</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>118</v>
+        <v>119.3</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="65">
@@ -4159,25 +4159,25 @@
         <v>61</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1346</v>
+        <v>1325</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>192.3</v>
+        <v>189.3</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>646</v>
+        <v>625</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>40.7</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="66">
@@ -4201,25 +4201,25 @@
         <v>791</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2260</v>
+        <v>2380</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>930</v>
+        <v>972</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>121.5</v>
+        <v>128</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>400</v>
+        <v>520</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="67">
@@ -4243,25 +4243,25 @@
         <v>413</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1700</v>
+        <v>1640</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>674</v>
+        <v>652</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>173.5</v>
+        <v>167.3</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>720</v>
+        <v>660</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="68">
@@ -4327,25 +4327,25 @@
         <v>304</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>895</v>
+        <v>925</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>111.9</v>
+        <v>115.6</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>210</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>-50</v>
+        <v>-70</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.08.18.pdf</t>
+          <t>Revenue Meeting_2026.08.25.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-19T09:49:05.621963Z</t>
+          <t>2026-08-26T12:06:59.463747Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.08.18</t>
+          <t>2026.08.25</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -478,7 +478,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST - 2026-08</t>
+          <t>RM FCST - 2026-09</t>
         </is>
       </c>
     </row>
@@ -541,31 +541,31 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>35550</v>
+        <v>17100</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6866</v>
+        <v>2410</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>30942</v>
+        <v>15870</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>211</v>
+        <v>162</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6544</v>
+        <v>2566</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>87</v>
+        <v>92.8</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>6641.4</v>
+        <v>2662.3</v>
       </c>
     </row>
     <row r="4">
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6265</v>
+        <v>3420</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1757</v>
+        <v>833</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7907</v>
+        <v>3091</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>264</v>
+        <v>226</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2086</v>
+        <v>700</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>126.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>33.3</v>
+        <v>20.4</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>2119.3</v>
+        <v>720.4</v>
       </c>
     </row>
     <row r="5">
@@ -609,31 +609,31 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3837</v>
+        <v>2210</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1440</v>
+        <v>752</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3320</v>
+        <v>2074</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1298</v>
+        <v>708</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>86.5</v>
+        <v>93.8</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>10.4</v>
+        <v>14</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1308.4</v>
+        <v>722</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8955</v>
+        <v>4500</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>320</v>
+        <v>264</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2866</v>
+        <v>1188</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7612</v>
+        <v>4305</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>334</v>
+        <v>292</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2546</v>
+        <v>1257</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>85</v>
+        <v>95.7</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2560</v>
+        <v>1274.5</v>
       </c>
     </row>
     <row r="7">
@@ -677,31 +677,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>4382</v>
+        <v>2732</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>363</v>
+        <v>308</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1592</v>
+        <v>841</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3879</v>
+        <v>2651</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>384</v>
+        <v>329</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1488</v>
+        <v>872</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>88.5</v>
+        <v>97</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.3</v>
+        <v>10.2</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1495.3</v>
+        <v>882.2</v>
       </c>
     </row>
     <row r="8">
@@ -711,31 +711,31 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>4010</v>
+        <v>3355</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>607</v>
+        <v>430</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3294</v>
+        <v>2913</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>548</v>
+        <v>409</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>82.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>549.5</v>
+        <v>410.7</v>
       </c>
     </row>
     <row r="9">
@@ -745,31 +745,31 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>32350</v>
+        <v>20345</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>7888</v>
+        <v>4445</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>32780</v>
+        <v>19051</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>7998</v>
+        <v>4390</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>101.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>104</v>
+        <v>123.2</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8102</v>
+        <v>4513.2</v>
       </c>
     </row>
     <row r="10">
@@ -779,31 +779,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>15180</v>
+        <v>10645</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>229</v>
+        <v>181</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3477</v>
+        <v>1924</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14792</v>
+        <v>9120</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>235</v>
+        <v>194</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3478</v>
+        <v>1768</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>32.2</v>
+        <v>35.3</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3510.2</v>
+        <v>1803.3</v>
       </c>
     </row>
     <row r="11">
@@ -813,31 +813,31 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>21305</v>
+        <v>17890</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5282</v>
+        <v>3730</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>21500</v>
+        <v>16350</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5304</v>
+        <v>3452</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>100.9</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>101.4</v>
+        <v>63.3</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5405.4</v>
+        <v>3515.3</v>
       </c>
     </row>
     <row r="12">
@@ -847,31 +847,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>18300</v>
+        <v>12830</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>3424</v>
+        <v>2051</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>17200</v>
+        <v>10580</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>3380</v>
+        <v>1872</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>94</v>
+        <v>82.5</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>215.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3595.4</v>
+        <v>1952.4</v>
       </c>
     </row>
     <row r="13">
@@ -881,31 +881,31 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>11100</v>
+        <v>9195</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2876</v>
+        <v>2109</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>12610</v>
+        <v>10350</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3461</v>
+        <v>2423</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>113.6</v>
+        <v>112.6</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>56</v>
+        <v>44.9</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3517</v>
+        <v>2467.9</v>
       </c>
     </row>
     <row r="14">
@@ -915,31 +915,31 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5545</v>
+        <v>4250</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1066</v>
+        <v>657</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>5440</v>
+        <v>4360</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1089</v>
+        <v>754</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>98.09999999999999</v>
+        <v>102.6</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10.3</v>
+        <v>18.8</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1099.3</v>
+        <v>772.8</v>
       </c>
     </row>
     <row r="15">
@@ -949,31 +949,31 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>12590</v>
+        <v>7800</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2548</v>
+        <v>1280</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>12463</v>
+        <v>7586</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2642</v>
+        <v>1341</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>99</v>
+        <v>97.3</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>205.4</v>
+        <v>105.5</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2847.4</v>
+        <v>1446.5</v>
       </c>
     </row>
     <row r="16">
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>13660</v>
+        <v>9000</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2657</v>
+        <v>1444</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>13840</v>
+        <v>7821</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2715</v>
+        <v>1379</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>101.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>196.2</v>
+        <v>113.2</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2911.2</v>
+        <v>1492.2</v>
       </c>
     </row>
     <row r="17">
@@ -1017,31 +1017,31 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>6190</v>
+        <v>4860</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>300</v>
+        <v>248</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1858</v>
+        <v>1204</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5795</v>
+        <v>4500</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1737</v>
+        <v>1179</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>93.59999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1802.9</v>
+        <v>1233.8</v>
       </c>
     </row>
     <row r="18">
@@ -1051,31 +1051,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>14120</v>
+        <v>8570</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>262</v>
+        <v>206</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>3700</v>
+        <v>1769</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>13455</v>
+        <v>7050</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>267</v>
+        <v>229</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>3596</v>
+        <v>1614</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>95.3</v>
+        <v>82.3</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>62.9</v>
+        <v>97.3</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3658.9</v>
+        <v>1711.3</v>
       </c>
     </row>
     <row r="19">
@@ -1085,31 +1085,31 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>16710</v>
+        <v>10970</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>248</v>
+        <v>198</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4149</v>
+        <v>2176</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>15010</v>
+        <v>8375</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>258</v>
+        <v>218</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3873</v>
+        <v>1828</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>89.8</v>
+        <v>76.3</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>59.6</v>
+        <v>28.5</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3932.6</v>
+        <v>1856.5</v>
       </c>
     </row>
     <row r="20">
@@ -1119,31 +1119,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>10130</v>
+        <v>9160</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2063</v>
+        <v>1515</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>10080</v>
+        <v>9320</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2210</v>
+        <v>1574</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>99.5</v>
+        <v>101.7</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>13.6</v>
+        <v>11.3</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2223.6</v>
+        <v>1585.3</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>6280</v>
+        <v>6920</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>247</v>
+        <v>203</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1549</v>
+        <v>1404</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>6970</v>
+        <v>6340</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>242</v>
+        <v>201</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1690</v>
+        <v>1272</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>111</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>40.5</v>
+        <v>27.9</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1730.5</v>
+        <v>1299.9</v>
       </c>
     </row>
     <row r="22">
@@ -1187,31 +1187,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>16100</v>
+        <v>15350</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2257</v>
+        <v>2094</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>13988</v>
+        <v>14460</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2207</v>
+        <v>2158</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>86.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>113</v>
+        <v>133.5</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2320</v>
+        <v>2291.5</v>
       </c>
     </row>
     <row r="23">
@@ -1221,31 +1221,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>6470</v>
+        <v>5845</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>884</v>
+        <v>572</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6622</v>
+        <v>5500</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1002</v>
+        <v>538</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>102.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>22.9</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1076.9</v>
+        <v>560.9</v>
       </c>
     </row>
     <row r="24">
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>12300</v>
+        <v>11080</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>365</v>
+        <v>312</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4493</v>
+        <v>3451</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>12746</v>
+        <v>8405</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>364</v>
+        <v>323</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>4639</v>
+        <v>2717</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>103.6</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>26.5</v>
+        <v>7.9</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4665.5</v>
+        <v>2724.9</v>
       </c>
     </row>
     <row r="25">
@@ -1289,31 +1289,31 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2455</v>
+        <v>2150</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>366</v>
+        <v>252</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>898</v>
+        <v>542</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2575</v>
+        <v>2000</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>367</v>
+        <v>251</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>945</v>
+        <v>503</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>104.9</v>
+        <v>93</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>17.4</v>
+        <v>12.8</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>962.4</v>
+        <v>515.8</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>66476</v>
+        <v>37274</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1559.1</v>
+        <v>1141.6</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>68035.10000000001</v>
+        <v>38415.6</v>
       </c>
     </row>
     <row r="27"/>
@@ -1340,25 +1340,25 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>62999</v>
+        <v>33317</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>240</v>
+        <v>194</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>15128</v>
+        <v>6453</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>56954</v>
+        <v>30904</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>255</v>
+        <v>211</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>14511</v>
+        <v>6512</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>90.40000000000001</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="29">
@@ -1368,25 +1368,25 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>102180</v>
+        <v>71660</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>23517</v>
+        <v>13972</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>101310</v>
+        <v>64687</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>23747</v>
+        <v>13326</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>99.09999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="30">
@@ -1396,25 +1396,25 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>32510</v>
+        <v>31430</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>5869</v>
+        <v>5013</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>31038</v>
+        <v>30120</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>6107</v>
+        <v>5004</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>95.5</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="31">
@@ -1424,25 +1424,25 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>86095</v>
+        <v>63770</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>21681</v>
+        <v>13382</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>85518</v>
+        <v>56361</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>259</v>
+        <v>221</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>22111</v>
+        <v>12432</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>99.3</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1468,7 +1468,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RM FCST 세그먼트별 - 2026-08</t>
+          <t>RM FCST 세그먼트별 - 2026-09</t>
         </is>
       </c>
     </row>
@@ -1546,34 +1546,34 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>11500</v>
+        <v>4350</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2358</v>
+        <v>692</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>9350</v>
+        <v>3850</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>237</v>
+        <v>174</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2220</v>
+        <v>670</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>81.3</v>
+        <v>88.5</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-2150</v>
+        <v>-500</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>78</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="4">
@@ -1588,34 +1588,34 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2800</v>
+        <v>1500</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>205</v>
+        <v>157</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>574</v>
+        <v>236</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3170</v>
+        <v>1350</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>770</v>
+        <v>257</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>113.2</v>
+        <v>90</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>370</v>
+        <v>-150</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>16.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="5">
@@ -1630,34 +1630,34 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>68</v>
+        <v>680</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>22.7</v>
+        <v>340</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-232</v>
+        <v>480</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>45.6</v>
+        <v>34.9</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>3.1</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="6">
@@ -1672,34 +1672,34 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2060</v>
+        <v>920</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>297</v>
+        <v>251</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>612</v>
+        <v>231</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3440</v>
+        <v>880</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>939</v>
+        <v>207</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>167</v>
+        <v>95.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1380</v>
+        <v>-40</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>28.7</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="7">
@@ -1714,34 +1714,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1010</v>
+        <v>710</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>300</v>
+        <v>263</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>303</v>
+        <v>187</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>900</v>
+        <v>370</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>262</v>
+        <v>99</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>89.09999999999999</v>
+        <v>52.1</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-110</v>
+        <v>-340</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -1765,25 +1765,25 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>45.6</v>
+        <v>34.9</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -1798,34 +1798,34 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1150</v>
+        <v>650</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>424</v>
+        <v>234</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>780</v>
+        <v>600</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>417</v>
+        <v>343</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>67.8</v>
+        <v>92.3</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-370</v>
+        <v>-50</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="10">
@@ -1840,34 +1840,34 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>950</v>
+        <v>400</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>380</v>
+        <v>140</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>755</v>
+        <v>500</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>408</v>
+        <v>345</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>308</v>
+        <v>173</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>79.5</v>
+        <v>125</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-195</v>
+        <v>100</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="11">
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>45.6</v>
+        <v>34.9</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -1924,34 +1924,34 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2400</v>
+        <v>950</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>347</v>
+        <v>280</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>833</v>
+        <v>266</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1920</v>
+        <v>956</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>373</v>
+        <v>309</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>716</v>
+        <v>295</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>80</v>
+        <v>100.6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-480</v>
+        <v>6</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1966,34 +1966,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>344</v>
+        <v>284</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>550</v>
+        <v>199</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1360</v>
+        <v>750</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>362</v>
+        <v>303</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>493</v>
+        <v>227</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>85</v>
+        <v>107.1</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-240</v>
+        <v>50</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="14">
@@ -2017,25 +2017,25 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>468.4</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="15">
@@ -2050,34 +2050,34 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1150</v>
+        <v>600</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>392</v>
+        <v>340</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>451</v>
+        <v>204</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1140</v>
+        <v>700</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>423</v>
+        <v>354</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>482</v>
+        <v>248</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>116.7</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-10</v>
+        <v>100</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="16">
@@ -2092,34 +2092,34 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>700</v>
+        <v>420</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>380</v>
+        <v>336</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>266</v>
+        <v>141</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>530</v>
+        <v>385</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>404</v>
+        <v>338</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>214</v>
+        <v>130</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>75.7</v>
+        <v>91.7</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-170</v>
+        <v>-35</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="17">
@@ -2179,31 +2179,31 @@
         <v>450</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>214</v>
+        <v>171</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>86.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-60</v>
+        <v>-70</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="19">
@@ -2218,34 +2218,34 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>111.1</v>
+        <v>110</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2260,34 +2260,34 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-20</v>
+        <v>30</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.6</v>
+        <v>29.3</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5610</v>
+        <v>3750</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1613</v>
+        <v>1009</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5650</v>
+        <v>4000</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1661</v>
+        <v>1088</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>100.7</v>
+        <v>106.7</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>12.6</v>
+        <v>25.2</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="22">
@@ -2344,34 +2344,34 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3700</v>
+        <v>2900</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>925</v>
+        <v>652</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>4400</v>
+        <v>3100</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1159</v>
+        <v>766</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>118.9</v>
+        <v>106.9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>32.1</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="23">
@@ -2386,34 +2386,34 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="E23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="H23" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>147</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="I23" s="4" t="n">
-        <v>155</v>
+        <v>48</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>11</v>
+        <v>-26</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>24.8</v>
+        <v>39</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24">
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2050</v>
+        <v>1650</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>264</v>
+        <v>194</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>542</v>
+        <v>320</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1990</v>
+        <v>1550</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>277</v>
+        <v>210</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>550</v>
+        <v>326</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-60</v>
+        <v>-100</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>13.3</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>19.4</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="25">
@@ -2470,34 +2470,34 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1200</v>
+        <v>1550</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>353</v>
+        <v>265</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>125</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>12.8</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="26">
@@ -2536,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="L26" s="4" t="n">
         <v>0</v>
@@ -2554,34 +2554,34 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>282</v>
+        <v>222</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>846</v>
+        <v>799</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2960</v>
+        <v>3450</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>291</v>
+        <v>230</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>861</v>
+        <v>794</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>98.7</v>
+        <v>95.8</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-40</v>
+        <v>-150</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>17.1</v>
+        <v>12.8</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>50.7</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="28">
@@ -2596,34 +2596,34 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1400</v>
+        <v>2400</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>280</v>
+        <v>215</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>392</v>
+        <v>516</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1821</v>
+        <v>2450</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>268</v>
+        <v>222</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>488</v>
+        <v>544</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>130.1</v>
+        <v>102.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>421</v>
+        <v>50</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>27.8</v>
+        <v>7.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>50.7</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="29">
@@ -2680,34 +2680,34 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5150</v>
+        <v>3700</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1018</v>
+        <v>652</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5365</v>
+        <v>2500</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1186</v>
+        <v>504</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>104.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>215</v>
+        <v>-1200</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>30.4</v>
+        <v>22.6</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>163.2</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="31">
@@ -2722,34 +2722,34 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>3000</v>
+        <v>2050</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>568</v>
+        <v>353</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3215</v>
+        <v>1850</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>667</v>
+        <v>362</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>107.2</v>
+        <v>90.2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>215</v>
+        <v>-200</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>15.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>51.1</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="32">
@@ -2764,34 +2764,34 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>22.6</v>
+        <v>42.5</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="33">
@@ -2806,34 +2806,34 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1725</v>
+        <v>1460</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>301</v>
+        <v>265</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>520</v>
+        <v>387</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2620</v>
+        <v>2100</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>339</v>
+        <v>270</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>888</v>
+        <v>567</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>151.9</v>
+        <v>143.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>895</v>
+        <v>640</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>50.4</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="34">
@@ -2848,34 +2848,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1165</v>
+        <v>970</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>352</v>
+        <v>259</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1600</v>
+        <v>1250</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>314</v>
+        <v>247</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>502</v>
+        <v>309</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>137.3</v>
+        <v>128.9</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>435</v>
+        <v>280</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="35">
@@ -2899,10 +2899,10 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0</v>
@@ -2911,13 +2911,13 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="36">
@@ -2932,34 +2932,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1175</v>
+        <v>985</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>237</v>
+        <v>165</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1125</v>
+        <v>1050</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>261</v>
+        <v>206</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>95.7</v>
+        <v>106.6</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-50</v>
+        <v>65</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -2974,34 +2974,34 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="F37" s="3" t="n">
         <v>730</v>
       </c>
-      <c r="D37" s="3" t="n">
-        <v>198</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>880</v>
-      </c>
       <c r="G37" s="3" t="n">
-        <v>232</v>
+        <v>185</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>204</v>
+        <v>135</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>120.5</v>
+        <v>121.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>3</v>
+        <v>11.4</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>2.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -3016,34 +3016,34 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>-14</v>
+        <v>10</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>42.4</v>
+        <v>45.4</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39">
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3450</v>
+        <v>1650</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>719</v>
+        <v>309</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>3570</v>
+        <v>1900</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>788</v>
+        <v>368</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>103.5</v>
+        <v>115.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>156.6</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1500</v>
+        <v>950</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>306</v>
+        <v>178</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>2090</v>
+        <v>950</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>447</v>
+        <v>185</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>139.3</v>
+        <v>100</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>48.8</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="41">
@@ -3184,34 +3184,34 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2600</v>
+        <v>1500</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>577</v>
+        <v>269</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2527</v>
+        <v>1500</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>568</v>
+        <v>288</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>97.2</v>
+        <v>100</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>-73</v>
+        <v>0</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>62.5</v>
+        <v>50.1</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>158</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -3226,34 +3226,34 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1450</v>
+        <v>1000</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>207</v>
+        <v>168</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>300</v>
+        <v>168</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1490</v>
+        <v>900</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>300</v>
+        <v>169</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>102.8</v>
+        <v>90</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>40</v>
+        <v>-100</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>25.7</v>
+        <v>16.7</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>38.2</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="44">
@@ -3277,25 +3277,25 @@
         <v>0</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>23.6</v>
+        <v>1440</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
@@ -3310,34 +3310,34 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>333</v>
+        <v>266</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>250</v>
+        <v>133</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>365</v>
+        <v>288</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-270</v>
+        <v>-100</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>79.7</v>
+        <v>60.3</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>38.3</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="46">
@@ -3352,34 +3352,34 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>333</v>
+        <v>256</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>333</v>
+        <v>179</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>343</v>
+        <v>275</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>378</v>
+        <v>220</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>110</v>
+        <v>114.3</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>100</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>24.2</v>
+        <v>38</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>26.6</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="47">
@@ -3394,34 +3394,34 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>0</v>
+        <v>46.8</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>31</v>
+        <v>-101</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>34</v>
+        <v>2.6</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="48">
@@ -3436,34 +3436,34 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2400</v>
+        <v>1300</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>285</v>
+        <v>235</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>684</v>
+        <v>306</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2900</v>
+        <v>1250</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>313</v>
+        <v>260</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>906</v>
+        <v>325</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>120.8</v>
+        <v>96.2</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>500</v>
+        <v>-50</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>13.2</v>
+        <v>43.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>38.4</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="49">
@@ -3478,34 +3478,34 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1750</v>
+        <v>1020</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>279</v>
+        <v>234</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>488</v>
+        <v>239</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1730</v>
+        <v>1350</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>288</v>
+        <v>235</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>499</v>
+        <v>318</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>132.4</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>-20</v>
+        <v>330</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>14.2</v>
+        <v>31.9</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>24.6</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="50">
@@ -3529,25 +3529,25 @@
         <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>35.9</v>
+        <v>27.3</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="51">
@@ -3562,34 +3562,34 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3300</v>
+        <v>2500</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>891</v>
+        <v>543</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>3045</v>
+        <v>2000</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>294</v>
+        <v>232</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>896</v>
+        <v>464</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>92.3</v>
+        <v>80</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-255</v>
+        <v>-500</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>11.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>34.3</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="52">
@@ -3604,34 +3604,34 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2600</v>
+        <v>1500</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>262</v>
+        <v>199</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>680</v>
+        <v>299</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>2280</v>
+        <v>1570</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>279</v>
+        <v>220</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>636</v>
+        <v>346</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>87.7</v>
+        <v>104.7</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>-320</v>
+        <v>70</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>11.1</v>
+        <v>7.7</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>25.3</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="53">
@@ -3670,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>37.8</v>
       </c>
       <c r="L53" s="4" t="n">
         <v>0</v>
@@ -3688,34 +3688,34 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>214</v>
+        <v>184</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>257</v>
+        <v>166</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1170</v>
+        <v>900</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>273</v>
+        <v>193</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>320</v>
+        <v>174</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>7.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="55">
@@ -3730,34 +3730,34 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2300</v>
+        <v>1550</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>483</v>
+        <v>274</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>2060</v>
+        <v>1650</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>235</v>
+        <v>169</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>484</v>
+        <v>279</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>89.59999999999999</v>
+        <v>106.5</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-240</v>
+        <v>100</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="56">
@@ -3772,34 +3772,34 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>73</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>17</v>
+        <v>-45</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>23.8</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="57">
@@ -3814,34 +3814,34 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>570</v>
+        <v>650</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>815</v>
+        <v>670</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>288</v>
+        <v>235</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>235</v>
+        <v>157</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>143</v>
+        <v>103.1</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>245</v>
+        <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>24.7</v>
+        <v>19.2</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>20.1</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="58">
@@ -3856,34 +3856,34 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>680</v>
+        <v>710</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>284</v>
+        <v>245</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>1075</v>
+        <v>790</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>260</v>
+        <v>222</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>280</v>
+        <v>175</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>158.1</v>
+        <v>111.3</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>395</v>
+        <v>80</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>20.4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
@@ -3907,19 +3907,19 @@
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="K59" s="4" t="n">
         <v>0</v>
@@ -3940,34 +3940,34 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1700</v>
+        <v>1400</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>322</v>
+        <v>260</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>245</v>
+        <v>200</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>257</v>
+        <v>200</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>61.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-650</v>
+        <v>-400</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>14.3</v>
+        <v>17.3</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>15</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="61">
@@ -3982,34 +3982,34 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>471</v>
+        <v>515</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2350</v>
+        <v>2850</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>516</v>
+        <v>570</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>94</v>
+        <v>101.8</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>-150</v>
+        <v>50</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>2.7</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="62">
@@ -4033,25 +4033,25 @@
         <v>276</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2420</v>
+        <v>3000</v>
       </c>
       <c r="G62" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="I62" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H62" s="3" t="n">
-        <v>241</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>80.7</v>
-      </c>
       <c r="J62" s="3" t="n">
-        <v>-580</v>
+        <v>0</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>39.4</v>
+        <v>36.7</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>95.3</v>
+        <v>110</v>
       </c>
     </row>
     <row r="63">
@@ -4066,34 +4066,34 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>550</v>
+        <v>430</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>178</v>
+        <v>105</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>68.8</v>
+        <v>61.4</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-250</v>
+        <v>-270</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>37.1</v>
+        <v>30.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>20.4</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="64">
@@ -4108,34 +4108,34 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1790</v>
+        <v>1400</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>291</v>
+        <v>134</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>119.3</v>
+        <v>127.3</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>8.1</v>
+        <v>4.7</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>14.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="65">
@@ -4150,34 +4150,34 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1325</v>
+        <v>1002</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>189.3</v>
+        <v>125.2</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>625</v>
+        <v>202</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>30.2</v>
+        <v>3</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>40.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4192,34 +4192,34 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1860</v>
+        <v>1780</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>425</v>
+        <v>358</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>791</v>
+        <v>637</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2380</v>
+        <v>1500</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>409</v>
+        <v>343</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>972</v>
+        <v>515</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>128</v>
+        <v>84.3</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>520</v>
+        <v>-280</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="67">
@@ -4234,34 +4234,34 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>421</v>
+        <v>361</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>413</v>
+        <v>350</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1640</v>
+        <v>1400</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>398</v>
+        <v>348</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>652</v>
+        <v>487</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>167.3</v>
+        <v>144.3</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>660</v>
+        <v>430</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>22.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="68">
@@ -4318,34 +4318,34 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>380</v>
+        <v>273</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>304</v>
+        <v>137</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>925</v>
+        <v>600</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>356</v>
+        <v>252</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>329</v>
+        <v>151</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>115.6</v>
+        <v>120</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>12.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="70">
@@ -4360,34 +4360,34 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>550</v>
+        <v>355</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>381</v>
+        <v>272</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>210</v>
+        <v>97</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>335</v>
+        <v>217</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>87.3</v>
+        <v>128.2</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>-70</v>
+        <v>100</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="71">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>전년 2025-08 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-09 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>2410</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>15870</v>
+        <v>15876</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2566</v>
+        <v>2609</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>92.8</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>96.3</v>
+        <v>94.3</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2662.3</v>
+        <v>2703.3</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>833</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3091</v>
+        <v>3097</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>700</v>
+        <v>713</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>90.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>720.4</v>
+        <v>733.7</v>
       </c>
     </row>
     <row r="5">
@@ -624,16 +624,16 @@
         <v>341</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>93.8</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>722</v>
+        <v>720.5</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>1188</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4305</v>
+        <v>4307</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1257</v>
+        <v>1272</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>95.7</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>17.5</v>
+        <v>18.8</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1274.5</v>
+        <v>1290.8</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>841</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2651</v>
+        <v>2517</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>872</v>
+        <v>844</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>97</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10.2</v>
+        <v>8.6</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>882.2</v>
+        <v>852.6</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>430</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2913</v>
+        <v>2842</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>86.8</v>
+        <v>84.7</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>410.7</v>
+        <v>404.6</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>4445</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>19051</v>
+        <v>18635</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>230</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>4390</v>
+        <v>4286</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>93.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>123.2</v>
+        <v>117.3</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4513.2</v>
+        <v>4403.3</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>1924</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>9120</v>
+        <v>8964</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>194</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1768</v>
+        <v>1742</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>85.7</v>
+        <v>84.2</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>35.3</v>
+        <v>33.5</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1803.3</v>
+        <v>1775.5</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>3730</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>16350</v>
+        <v>16006</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3452</v>
+        <v>3350</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>91.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>63.3</v>
+        <v>63.1</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3515.3</v>
+        <v>3413.1</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>2051</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>10580</v>
+        <v>10625</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>177</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1872</v>
+        <v>1880</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>80.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1952.4</v>
+        <v>1959.6</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2109</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>10350</v>
+        <v>10430</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2423</v>
+        <v>2454</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>112.6</v>
+        <v>113.4</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2467.9</v>
+        <v>2499.1</v>
       </c>
     </row>
     <row r="14">
@@ -927,19 +927,19 @@
         <v>4360</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>102.6</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>772.8</v>
+        <v>778.1</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>1280</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7586</v>
+        <v>7800</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1341</v>
+        <v>1373</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>105.5</v>
+        <v>101.7</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1446.5</v>
+        <v>1474.7</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>1444</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7821</v>
+        <v>7719</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>176</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1379</v>
+        <v>1359</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>86.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>113.2</v>
+        <v>106.2</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1492.2</v>
+        <v>1465.2</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1204</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4500</v>
+        <v>4358</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1179</v>
+        <v>1167</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>92.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>54.8</v>
+        <v>51.8</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1233.8</v>
+        <v>1218.8</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>1769</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7050</v>
+        <v>6736</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1614</v>
+        <v>1597</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>82.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>97.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1711.3</v>
+        <v>1689.4</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>2176</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8375</v>
+        <v>8415</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1828</v>
+        <v>1842</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>76.3</v>
+        <v>76.7</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1856.5</v>
+        <v>1870.6</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>1515</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9320</v>
+        <v>9039</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>169</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1574</v>
+        <v>1526</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>101.7</v>
+        <v>98.7</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1585.3</v>
+        <v>1536.8</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1404</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>6340</v>
+        <v>6184</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1272</v>
+        <v>1215</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>91.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>27.9</v>
+        <v>24.6</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1299.9</v>
+        <v>1239.6</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2094</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>14460</v>
+        <v>14340</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2158</v>
+        <v>2169</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>94.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>133.5</v>
+        <v>122.8</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2291.5</v>
+        <v>2291.8</v>
       </c>
     </row>
     <row r="23">
@@ -1230,22 +1230,22 @@
         <v>572</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5500</v>
+        <v>5443</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>94.09999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>22.9</v>
+        <v>24.8</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>560.9</v>
+        <v>548.8</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>3451</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>8405</v>
+        <v>8265</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>323</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2717</v>
+        <v>2673</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2724.9</v>
+        <v>2681.2</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>542</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2000</v>
+        <v>2040</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>93</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>12.8</v>
+        <v>13.7</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>515.8</v>
+        <v>520.7</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>37274</v>
+        <v>36972</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1141.6</v>
+        <v>1099.8</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>38415.6</v>
+        <v>38071.8</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>6453</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>30904</v>
+        <v>30713</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>6512</v>
+        <v>6548</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>92.8</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>13972</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>64687</v>
+        <v>64070</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>13326</v>
+        <v>13138</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>90.3</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5013</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>30120</v>
+        <v>29563</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>166</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5004</v>
+        <v>4910</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>95.8</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>13382</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>56361</v>
+        <v>55726</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>12432</v>
+        <v>12376</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>88.40000000000001</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1555,25 +1555,25 @@
         <v>692</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3850</v>
+        <v>3750</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>670</v>
+        <v>661</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>88.5</v>
+        <v>86.2</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>60.1</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="4">
@@ -1600,10 +1600,10 @@
         <v>1350</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>90</v>
@@ -1639,25 +1639,25 @@
         <v>16</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>109</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>34.9</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="6">
@@ -1681,25 +1681,25 @@
         <v>231</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>95.7</v>
+        <v>97.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="7">
@@ -1726,10 +1726,10 @@
         <v>370</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>52.1</v>
@@ -1810,10 +1810,10 @@
         <v>600</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>92.3</v>
@@ -1849,25 +1849,25 @@
         <v>140</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>125</v>
+        <v>112.5</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="11">
@@ -1933,25 +1933,25 @@
         <v>266</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="G12" s="3" t="n">
+        <v>325</v>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>309</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>295</v>
-      </c>
       <c r="I12" s="4" t="n">
-        <v>100.6</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1978,10 +1978,10 @@
         <v>750</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>107.1</v>
@@ -2017,10 +2017,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>1</v>
@@ -2029,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>468.4</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -2059,25 +2059,25 @@
         <v>204</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>700</v>
+        <v>570</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>248</v>
+        <v>217</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>116.7</v>
+        <v>95</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>100</v>
+        <v>-30</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="16">
@@ -2101,25 +2101,25 @@
         <v>141</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>91.7</v>
+        <v>83.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-35</v>
+        <v>-70</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="17">
@@ -2185,25 +2185,25 @@
         <v>75</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>380</v>
+        <v>310</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>84.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-70</v>
+        <v>-140</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
@@ -2227,19 +2227,19 @@
         <v>50</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>165</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>110</v>
+        <v>116.7</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>0.1</v>
@@ -2311,25 +2311,25 @@
         <v>1009</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1088</v>
+        <v>1037</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>106.7</v>
+        <v>101.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>25.2</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>100.6</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2353,25 +2353,25 @@
         <v>652</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>766</v>
+        <v>726</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>106.9</v>
+        <v>103.4</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>7</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>21.6</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="23">
@@ -2395,7 +2395,7 @@
         <v>5</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>80</v>
@@ -2404,10 +2404,10 @@
         <v>2</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-26</v>
+        <v>-28</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>39</v>
@@ -2437,25 +2437,25 @@
         <v>320</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1550</v>
+        <v>1450</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>210</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>93.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>13.3</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>20.5</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="25">
@@ -2479,25 +2479,25 @@
         <v>282</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>87.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-200</v>
+        <v>-250</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>14.8</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="26">
@@ -2563,25 +2563,25 @@
         <v>799</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3450</v>
+        <v>3400</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>794</v>
+        <v>772</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>95.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-150</v>
+        <v>-200</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>12.8</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>44.1</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="28">
@@ -2605,25 +2605,25 @@
         <v>516</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2450</v>
+        <v>2500</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>102.1</v>
+        <v>104.2</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="29">
@@ -2692,10 +2692,10 @@
         <v>2500</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="I30" s="4" t="n">
         <v>67.59999999999999</v>
@@ -2734,10 +2734,10 @@
         <v>1850</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>90.2</v>
@@ -2773,25 +2773,25 @@
         <v>16</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>70</v>
+        <v>60.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-60</v>
+        <v>-79</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>42.5</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="33">
@@ -2818,10 +2818,10 @@
         <v>2100</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="I33" s="4" t="n">
         <v>143.8</v>
@@ -2857,25 +2857,25 @@
         <v>259</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>128.9</v>
+        <v>134</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>165</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1050</v>
+        <v>995</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>106.6</v>
+        <v>101</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>9.6</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="37">
@@ -2983,25 +2983,25 @@
         <v>93</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>121.7</v>
+        <v>120</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -3025,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>127</v>
@@ -3037,13 +3037,13 @@
         <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>45.4</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="39">
@@ -3067,25 +3067,25 @@
         <v>309</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>115.2</v>
+        <v>109.1</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
@@ -3109,25 +3109,25 @@
         <v>178</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>950</v>
+        <v>975</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>100</v>
+        <v>102.6</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="41">
@@ -3193,25 +3193,25 @@
         <v>269</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0</v>
+        <v>-150</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>50.1</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>75.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -3235,25 +3235,25 @@
         <v>168</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>900</v>
+        <v>930</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>-100</v>
+        <v>-70</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>16.7</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="44">
@@ -3319,25 +3319,25 @@
         <v>133</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-100</v>
+        <v>-150</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>24.1</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="46">
@@ -3364,10 +3364,10 @@
         <v>800</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>114.3</v>
@@ -3403,19 +3403,19 @@
         <v>28</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>46.8</v>
+        <v>45.8</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>-101</v>
+        <v>-103</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>2.6</v>
@@ -3445,25 +3445,25 @@
         <v>306</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1250</v>
+        <v>1100</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>96.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-50</v>
+        <v>-200</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>43.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>53.9</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>239</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>132.4</v>
+        <v>137.3</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>43.1</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>543</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>232</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>464</v>
+        <v>441</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>16.4</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="52">
@@ -3613,25 +3613,25 @@
         <v>299</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1570</v>
+        <v>1700</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>104.7</v>
+        <v>113.3</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>7.7</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="53">
@@ -3697,25 +3697,25 @@
         <v>166</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>5.7</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="55">
@@ -3739,25 +3739,25 @@
         <v>274</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>106.5</v>
+        <v>109.7</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K55" s="4" t="n">
         <v>2.9</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -3781,7 +3781,7 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>73</v>
@@ -3790,10 +3790,10 @@
         <v>4</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>23.8</v>
@@ -3823,25 +3823,25 @@
         <v>163</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>670</v>
+        <v>580</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>103.1</v>
+        <v>89.2</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>20</v>
+        <v>-70</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>12.9</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="58">
@@ -3865,25 +3865,25 @@
         <v>174</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>790</v>
+        <v>710</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>111.3</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>19</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="59">
@@ -3952,10 +3952,10 @@
         <v>1000</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>71.40000000000001</v>
@@ -3991,25 +3991,25 @@
         <v>515</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>2850</v>
+        <v>3000</v>
       </c>
       <c r="G61" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>606</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="J61" s="3" t="n">
         <v>200</v>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>570</v>
-      </c>
-      <c r="I61" s="4" t="n">
-        <v>101.8</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>50</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="62">
@@ -4033,25 +4033,25 @@
         <v>276</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>285</v>
+        <v>248</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>36.7</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63">
@@ -4075,25 +4075,25 @@
         <v>67</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>61.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-270</v>
+        <v>-200</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>30.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>13.2</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="64">
@@ -4117,25 +4117,25 @@
         <v>102</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>127.3</v>
+        <v>122.7</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>4.7</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="65">
@@ -4159,19 +4159,19 @@
         <v>56</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1002</v>
+        <v>987</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>74</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>125.2</v>
+        <v>123.4</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>3</v>
@@ -4201,25 +4201,25 @@
         <v>637</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1500</v>
+        <v>1420</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>515</v>
+        <v>494</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>84.3</v>
+        <v>79.8</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>-280</v>
+        <v>-360</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.1</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="67">
@@ -4243,25 +4243,25 @@
         <v>350</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>144.3</v>
+        <v>154.6</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>430</v>
+        <v>530</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="68">
@@ -4327,25 +4327,25 @@
         <v>137</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -4369,25 +4369,25 @@
         <v>97</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>128.2</v>
+        <v>135.2</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.08.25.pdf</t>
+          <t>Revenue Meeting_2026.09.01.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26T12:06:59.463747Z</t>
+          <t>2026-09-02T15:23:59.114903Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.08.25</t>
+          <t>2026.09.01</t>
         </is>
       </c>
     </row>

--- a/docs/data/RM_FCST_정리.xlsx
+++ b/docs/data/RM_FCST_정리.xlsx
@@ -550,22 +550,22 @@
         <v>2410</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>15876</v>
+        <v>15314</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2609</v>
+        <v>2599</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>92.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>94.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2703.3</v>
+        <v>2685.9</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         <v>833</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3097</v>
+        <v>3103</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>90.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>733.7</v>
+        <v>732.5</v>
       </c>
     </row>
     <row r="5">
@@ -618,22 +618,22 @@
         <v>752</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2074</v>
+        <v>1914</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>341</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>707</v>
+        <v>652</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>93.8</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>13.5</v>
+        <v>11.8</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>720.5</v>
+        <v>663.8</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +652,22 @@
         <v>1188</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4307</v>
+        <v>4310</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1272</v>
+        <v>1265</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1290.8</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="7">
@@ -689,19 +689,19 @@
         <v>2517</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>852.6</v>
+        <v>857.9</v>
       </c>
     </row>
     <row r="8">
@@ -720,22 +720,22 @@
         <v>430</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>84.7</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>404.6</v>
+        <v>403.5</v>
       </c>
     </row>
     <row r="9">
@@ -754,22 +754,22 @@
         <v>4445</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>18635</v>
+        <v>18075</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>4286</v>
+        <v>4100</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>91.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>117.3</v>
+        <v>104.8</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4403.3</v>
+        <v>4204.8</v>
       </c>
     </row>
     <row r="10">
@@ -788,22 +788,22 @@
         <v>1924</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>8964</v>
+        <v>8550</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>194</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1742</v>
+        <v>1659</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>84.2</v>
+        <v>80.3</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>33.5</v>
+        <v>28.6</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1775.5</v>
+        <v>1687.6</v>
       </c>
     </row>
     <row r="11">
@@ -822,22 +822,22 @@
         <v>3730</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>16006</v>
+        <v>15702</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3350</v>
+        <v>3308</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>89.5</v>
+        <v>87.8</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>63.1</v>
+        <v>61.1</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3413.1</v>
+        <v>3369.1</v>
       </c>
     </row>
     <row r="12">
@@ -856,22 +856,22 @@
         <v>2051</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>10625</v>
+        <v>10670</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1880</v>
+        <v>1842</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>82.8</v>
+        <v>83.2</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>79.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1959.6</v>
+        <v>1917.7</v>
       </c>
     </row>
     <row r="13">
@@ -890,22 +890,22 @@
         <v>2109</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>10430</v>
+        <v>10755</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>235</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2454</v>
+        <v>2528</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>113.4</v>
+        <v>117</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2499.1</v>
+        <v>2572.9</v>
       </c>
     </row>
     <row r="14">
@@ -927,19 +927,19 @@
         <v>4360</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>102.6</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>778.1</v>
+        <v>763.8</v>
       </c>
     </row>
     <row r="15">
@@ -958,22 +958,22 @@
         <v>1280</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7800</v>
+        <v>7867</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>176</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1373</v>
+        <v>1382</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>100</v>
+        <v>100.9</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>101.7</v>
+        <v>100.7</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1474.7</v>
+        <v>1482.7</v>
       </c>
     </row>
     <row r="16">
@@ -992,22 +992,22 @@
         <v>1444</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7719</v>
+        <v>7870</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1359</v>
+        <v>1372</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>85.8</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>106.2</v>
+        <v>102.9</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1465.2</v>
+        <v>1474.9</v>
       </c>
     </row>
     <row r="17">
@@ -1026,22 +1026,22 @@
         <v>1204</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4358</v>
+        <v>4300</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>268</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1167</v>
+        <v>1153</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>89.7</v>
+        <v>88.5</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>51.8</v>
+        <v>54.8</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1218.8</v>
+        <v>1207.8</v>
       </c>
     </row>
     <row r="18">
@@ -1060,22 +1060,22 @@
         <v>1769</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>6736</v>
+        <v>6518</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1597</v>
+        <v>1552</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>78.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>92.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1689.4</v>
+        <v>1647.1</v>
       </c>
     </row>
     <row r="19">
@@ -1094,22 +1094,22 @@
         <v>2176</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8415</v>
+        <v>8440</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1842</v>
+        <v>1817</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>76.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>28.6</v>
+        <v>27.2</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1870.6</v>
+        <v>1844.2</v>
       </c>
     </row>
     <row r="20">
@@ -1128,22 +1128,22 @@
         <v>1515</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9039</v>
+        <v>8862</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>169</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1526</v>
+        <v>1496</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>98.7</v>
+        <v>96.7</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>10.8</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1536.8</v>
+        <v>1506.8</v>
       </c>
     </row>
     <row r="21">
@@ -1162,22 +1162,22 @@
         <v>1404</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>6184</v>
+        <v>6056</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1215</v>
+        <v>1168</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>89.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24.6</v>
+        <v>22.7</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1239.6</v>
+        <v>1190.7</v>
       </c>
     </row>
     <row r="22">
@@ -1196,22 +1196,22 @@
         <v>2094</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>14340</v>
+        <v>13930</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2169</v>
+        <v>2145</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>122.8</v>
+        <v>115.5</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2291.8</v>
+        <v>2260.5</v>
       </c>
     </row>
     <row r="23">
@@ -1230,22 +1230,22 @@
         <v>572</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5443</v>
+        <v>5536</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>96</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>93.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>24.8</v>
+        <v>26.5</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>548.8</v>
+        <v>556.5</v>
       </c>
     </row>
     <row r="24">
@@ -1264,22 +1264,22 @@
         <v>3451</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>8265</v>
+        <v>8300</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2673</v>
+        <v>2658</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2681.2</v>
+        <v>2666.4</v>
       </c>
     </row>
     <row r="25">
@@ -1298,22 +1298,22 @@
         <v>542</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2040</v>
+        <v>2093</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>94.90000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>13.7</v>
+        <v>14.4</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>520.7</v>
+        <v>525.4</v>
       </c>
     </row>
     <row r="26">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>36972</v>
+        <v>36447</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1099.8</v>
+        <v>1058.5</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>38071.8</v>
+        <v>37505.5</v>
       </c>
     </row>
     <row r="27"/>
@@ -1349,16 +1349,16 @@
         <v>6453</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>30713</v>
+        <v>30001</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>6548</v>
+        <v>6481</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>92.2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29">
@@ -1377,16 +1377,16 @@
         <v>13972</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>64070</v>
+        <v>62957</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>13138</v>
+        <v>12802</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>89.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1405,16 +1405,16 @@
         <v>5013</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>29563</v>
+        <v>28848</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>4910</v>
+        <v>4809</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>94.09999999999999</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="31">
@@ -1433,16 +1433,16 @@
         <v>13382</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>55726</v>
+        <v>56079</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>12376</v>
+        <v>12356</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>87.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1555,25 +1555,25 @@
         <v>692</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>661</v>
+        <v>618</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>86.2</v>
+        <v>74.7</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-600</v>
+        <v>-1100</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>58.6</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="4">
@@ -1597,25 +1597,25 @@
         <v>236</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-150</v>
+        <v>-100</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="5">
@@ -1684,10 +1684,10 @@
         <v>900</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>97.8</v>
@@ -1723,25 +1723,25 @@
         <v>187</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>52.1</v>
+        <v>49.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-340</v>
+        <v>-360</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -1807,25 +1807,25 @@
         <v>234</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>92.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-50</v>
+        <v>-150</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="10">
@@ -1849,25 +1849,25 @@
         <v>140</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>112.5</v>
+        <v>107.5</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1933,25 +1933,25 @@
         <v>266</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>950</v>
+        <v>880</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>325</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>100</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="13">
@@ -1975,25 +1975,25 @@
         <v>199</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>315</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>107.1</v>
+        <v>104.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="14">
@@ -2059,25 +2059,25 @@
         <v>204</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>570</v>
+        <v>520</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>95</v>
+        <v>86.7</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-30</v>
+        <v>-80</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="16">
@@ -2101,25 +2101,25 @@
         <v>141</v>
       </c>
       <c r="F16" s="3" t="n">
+        <v>325</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>345</v>
-      </c>
       <c r="H16" s="3" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>83.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-70</v>
+        <v>-95</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17">
@@ -2185,19 +2185,19 @@
         <v>75</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>68.90000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-140</v>
+        <v>-170</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>2.1</v>
@@ -2230,10 +2230,10 @@
         <v>350</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>116.7</v>
@@ -2311,25 +2311,25 @@
         <v>1009</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3800</v>
+        <v>3300</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1037</v>
+        <v>908</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>101.3</v>
+        <v>88</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>50</v>
+        <v>-450</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>25.2</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>95.59999999999999</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22">
@@ -2356,10 +2356,10 @@
         <v>3000</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>726</v>
+        <v>693</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>103.4</v>
@@ -2395,7 +2395,7 @@
         <v>5</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>80</v>
@@ -2404,10 +2404,10 @@
         <v>2</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>39</v>
@@ -2437,25 +2437,25 @@
         <v>320</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1450</v>
+        <v>1250</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>210</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>13.3</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>19.2</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="25">
@@ -2479,25 +2479,25 @@
         <v>282</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>193</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>251</v>
+        <v>212</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>83.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-250</v>
+        <v>-450</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>14.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
@@ -2563,25 +2563,25 @@
         <v>799</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3400</v>
+        <v>3000</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>772</v>
+        <v>690</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>94.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-200</v>
+        <v>-600</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>12.8</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>43.5</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="28">
@@ -2605,25 +2605,25 @@
         <v>516</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>550</v>
+        <v>641</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>104.2</v>
+        <v>120.8</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>19.6</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="29">
@@ -2689,25 +2689,25 @@
         <v>652</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>508</v>
+        <v>462</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>67.59999999999999</v>
+        <v>62.2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1200</v>
+        <v>-1400</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>22.6</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>56.4</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="31">
@@ -2731,25 +2731,25 @@
         <v>353</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1850</v>
+        <v>1800</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>90.2</v>
+        <v>87.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-200</v>
+        <v>-250</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="32">
@@ -2773,25 +2773,25 @@
         <v>16</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>66</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>60.5</v>
+        <v>73.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-79</v>
+        <v>-53</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>42.5</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="33">
@@ -2815,25 +2815,25 @@
         <v>387</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2100</v>
+        <v>2050</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>143.8</v>
+        <v>140.4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>640</v>
+        <v>590</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>40.4</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="34">
@@ -2857,25 +2857,25 @@
         <v>259</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1300</v>
+        <v>1520</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>319</v>
+        <v>380</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>134</v>
+        <v>156.7</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>330</v>
+        <v>550</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="35">
@@ -2941,25 +2941,25 @@
         <v>165</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>995</v>
+        <v>925</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>101</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>10</v>
+        <v>-60</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>9.6</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2983,25 +2983,25 @@
         <v>93</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="38">
@@ -3067,25 +3067,25 @@
         <v>309</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1800</v>
+        <v>1750</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>109.1</v>
+        <v>106.1</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>79</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="40">
@@ -3109,25 +3109,25 @@
         <v>178</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>975</v>
+        <v>1025</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>102.6</v>
+        <v>107.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>22.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="41">
@@ -3193,25 +3193,25 @@
         <v>269</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1350</v>
+        <v>1250</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>90</v>
+        <v>83.3</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>-150</v>
+        <v>-250</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>50.1</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>67.59999999999999</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="43">
@@ -3235,25 +3235,25 @@
         <v>168</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>930</v>
+        <v>1030</v>
       </c>
       <c r="G43" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="H43" s="3" t="n">
         <v>185</v>
       </c>
-      <c r="H43" s="3" t="n">
-        <v>172</v>
-      </c>
       <c r="I43" s="4" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>-70</v>
+        <v>30</v>
       </c>
       <c r="K43" s="4" t="n">
         <v>16.7</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>15.6</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="44">
@@ -3280,7 +3280,7 @@
         <v>16</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>2</v>
@@ -3319,25 +3319,25 @@
         <v>133</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>-150</v>
+        <v>-100</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>21.1</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="46">
@@ -3364,10 +3364,10 @@
         <v>800</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>114.3</v>
@@ -3403,19 +3403,19 @@
         <v>28</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>45.8</v>
+        <v>41.6</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>-103</v>
+        <v>-111</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>2.6</v>
@@ -3445,25 +3445,25 @@
         <v>306</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>84.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>43.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>47.5</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="49">
@@ -3487,25 +3487,25 @@
         <v>239</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>137.3</v>
+        <v>132.4</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>44.7</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="50">
@@ -3571,25 +3571,25 @@
         <v>543</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1900</v>
+        <v>1630</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>441</v>
+        <v>367</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>76</v>
+        <v>65.2</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>-600</v>
+        <v>-870</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="52">
@@ -3613,25 +3613,25 @@
         <v>299</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>113.3</v>
+        <v>120</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>7.7</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>13.1</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="53">
@@ -3742,10 +3742,10 @@
         <v>1700</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I55" s="4" t="n">
         <v>109.7</v>
@@ -3823,25 +3823,25 @@
         <v>163</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>580</v>
+        <v>480</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>89.2</v>
+        <v>73.8</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>-70</v>
+        <v>-170</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>11.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -3868,10 +3868,10 @@
         <v>710</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>100</v>
@@ -3952,10 +3952,10 @@
         <v>1000</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>71.40000000000001</v>
@@ -3994,10 +3994,10 @@
         <v>3000</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="I61" s="4" t="n">
         <v>107.1</v>
@@ -4033,25 +4033,25 @@
         <v>276</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>92</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>90</v>
+        <v>83.3</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>36.7</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>99</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="63">
@@ -4075,25 +4075,25 @@
         <v>67</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-200</v>
+        <v>-170</v>
       </c>
       <c r="K63" s="4" t="n">
         <v>30.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>15.4</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="64">
@@ -4117,25 +4117,25 @@
         <v>102</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1350</v>
+        <v>1550</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>122.7</v>
+        <v>140.9</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="K64" s="4" t="n">
         <v>4.7</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="65">
@@ -4159,25 +4159,25 @@
         <v>56</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>987</v>
+        <v>949</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>74</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>123.4</v>
+        <v>118.6</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="K65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="66">
@@ -4201,19 +4201,19 @@
         <v>637</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1420</v>
+        <v>1400</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>79.8</v>
+        <v>78.7</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>-360</v>
+        <v>-380</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>1.1</v>
@@ -4243,25 +4243,25 @@
         <v>350</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>519</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>154.6</v>
+        <v>159.8</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>530</v>
+        <v>580</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="68">
@@ -4330,10 +4330,10 @@
         <v>650</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I69" s="4" t="n">
         <v>130</v>
@@ -4369,25 +4369,25 @@
         <v>97</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>480</v>
+        <v>550</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>135.2</v>
+        <v>154.9</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>125</v>
+        <v>195</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="71">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.01.pdf</t>
+          <t>Revenue Meeting_2026.09.08.pdf</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02T15:23:59.114903Z</t>
+          <t>2026-09-09T08:20:23.504634Z</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.09.01</t>
+          <t>2026.09.08</t>
         </is>
       </c>
     </row>
